--- a/data/台股_拐點掃描.xlsx
+++ b/data/台股_拐點掃描.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet name="潛在拐點觀察區" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="全部訊號" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="金融拐點候選" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="金融全部" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17087,4 +17089,857 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>分級</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>EPS5y%</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>EPS近3y%</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>EPS加速</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ROE</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>5年均ROE</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ROE回升</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>PBR位階</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>PBR便宜</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>PER</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>殖利率%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>分級</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>EPS5y%</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>EPS近3y%</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>EPS加速</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ROE</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>5年均ROE</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ROE回升</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>PBR位階</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>PBR便宜</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>PER</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>殖利率%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2889</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>國票金</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>-16.6</v>
+      </c>
+      <c r="E2" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>—金控0</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>56</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3.92</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2812</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>台中銀</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>—金控0</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>79</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="M3" t="n">
+        <v>5.39</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="E4" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>—金控0</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>88</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.91</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2850</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>新產</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>99</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5.08</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2851</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>中再保</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>99</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5.64</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2880</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>華南金</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>—金控0</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>99</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.86</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6005</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>群益證</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="H8" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>100</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2855</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>統一證</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>100</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4.04</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2881</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>富邦金</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>—金控0</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>100</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2890</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>永豐金</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>—金控0</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>100</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>元大金</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>—金控0</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>100</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>台新新光金</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>—金控0</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>100</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2891</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>中信金</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="E14" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>—金控0</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>100</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2882</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>國泰金</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>—金控0</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>100</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>16</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>凱基金</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>—金控0</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>100</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/台股_拐點掃描.xlsx
+++ b/data/台股_拐點掃描.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="潛在拐點觀察區" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="全部訊號" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="金融拐點候選" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="金融全部" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="潛在拐點觀察區" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部訊號" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="金融拐點候選" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="金融全部" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,97 +432,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>改善訊號數</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>A毛利拐頭</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>B月營收動能</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>C_EPS加速</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>D_ROE回升</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>近四季ROE</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>5年均ROE</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>循環</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>看哪個位階</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>估值位階</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
@@ -2449,97 +2461,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>改善訊號數</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>A毛利拐頭</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>B月營收動能</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>C_EPS加速</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>D_ROE回升</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>近四季ROE</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>5年均ROE</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>循環</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>看哪個位階</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>估值位階</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
@@ -17389,67 +17401,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>EPS加速</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>5年均ROE</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ROE回升</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>PBR便宜</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
@@ -17470,67 +17482,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>EPS加速</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>5年均ROE</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ROE回升</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>PBR便宜</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>

--- a/data/台股_拐點掃描.xlsx
+++ b/data/台股_拐點掃描.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="潛在拐點觀察區" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部訊號" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="金融拐點候選" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="金融全部" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="潛在拐點觀察區" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="全部訊號" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="金融拐點候選" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="金融全部" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,97 +420,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>改善訊號數</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>A毛利拐頭</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>B月營收動能</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>C_EPS加速</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>D_ROE回升</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>近四季ROE</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>5年均ROE</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>循環</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>看哪個位階</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>估值位階</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
@@ -2536,97 +2524,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>改善訊號數</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>A毛利拐頭</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>B月營收動能</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>C_EPS加速</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>D_ROE回升</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>近四季ROE</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>5年均ROE</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>循環</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>看哪個位階</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>估值位階</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
@@ -19129,67 +19117,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>EPS加速</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>5年均ROE</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ROE回升</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>PBR便宜</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
@@ -19210,67 +19198,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>EPS加速</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>5年均ROE</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ROE回升</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>PBR便宜</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>

--- a/data/台股_拐點掃描.xlsx
+++ b/data/台股_拐點掃描.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="潛在拐點觀察區" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="全部訊號" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="金融拐點候選" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="金融全部" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="潛在拐點觀察區" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部訊號" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="金融拐點候選" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="金融全部" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,101 +428,121 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S28"/>
+  <dimension ref="A1:W28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>改善訊號數</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>A毛利拐頭</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>B月營收動能</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>C_EPS加速</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>D_ROE回升</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>近四季ROE</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>5年均ROE</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>循環</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>看哪個位階</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>估值位階</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ForwardPE</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>PEG</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>未來估值</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>成長率g%</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
@@ -586,6 +618,20 @@
         <v>14.1</v>
       </c>
       <c r="S2" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="W2" t="n">
         <v>3.31</v>
       </c>
     </row>
@@ -660,7 +706,11 @@
       <c r="R3" t="n">
         <v>14.8</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
         <v>5.24</v>
       </c>
     </row>
@@ -734,6 +784,20 @@
         <v>11.8</v>
       </c>
       <c r="S4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>12</v>
+      </c>
+      <c r="W4" t="n">
         <v>7.5</v>
       </c>
     </row>
@@ -810,7 +874,11 @@
       <c r="R5" t="n">
         <v>27</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
         <v>2.81</v>
       </c>
     </row>
@@ -884,6 +952,20 @@
         <v>12.9</v>
       </c>
       <c r="S6" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="W6" t="n">
         <v>6.75</v>
       </c>
     </row>
@@ -957,6 +1039,20 @@
         <v>14.7</v>
       </c>
       <c r="S7" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="W7" t="n">
         <v>4.71</v>
       </c>
     </row>
@@ -1030,6 +1126,20 @@
         <v>13.9</v>
       </c>
       <c r="S8" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W8" t="n">
         <v>6.42</v>
       </c>
     </row>
@@ -1103,6 +1213,20 @@
         <v>19.1</v>
       </c>
       <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="W9" t="n">
         <v>4.95</v>
       </c>
     </row>
@@ -1176,6 +1300,20 @@
         <v>19.4</v>
       </c>
       <c r="S10" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="W10" t="n">
         <v>3.05</v>
       </c>
     </row>
@@ -1249,6 +1387,20 @@
         <v>17.5</v>
       </c>
       <c r="S11" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="W11" t="n">
         <v>3.49</v>
       </c>
     </row>
@@ -1322,6 +1474,20 @@
         <v>20.2</v>
       </c>
       <c r="S12" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="W12" t="n">
         <v>4.01</v>
       </c>
     </row>
@@ -1398,7 +1564,11 @@
       <c r="R13" t="n">
         <v>16.6</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="n">
         <v>6.66</v>
       </c>
     </row>
@@ -1472,6 +1642,20 @@
         <v>14.9</v>
       </c>
       <c r="S14" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="W14" t="n">
         <v>5.42</v>
       </c>
     </row>
@@ -1545,6 +1729,20 @@
         <v>16.4</v>
       </c>
       <c r="S15" t="n">
+        <v>16</v>
+      </c>
+      <c r="T15" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W15" t="n">
         <v>5.07</v>
       </c>
     </row>
@@ -1621,7 +1819,11 @@
       <c r="R16" t="n">
         <v>14.8</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="n">
         <v>5.13</v>
       </c>
     </row>
@@ -1695,6 +1897,20 @@
         <v>20.4</v>
       </c>
       <c r="S17" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W17" t="n">
         <v>2.83</v>
       </c>
     </row>
@@ -1769,7 +1985,11 @@
       <c r="R18" t="n">
         <v>14.2</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="n">
         <v>4.12</v>
       </c>
     </row>
@@ -1846,7 +2066,11 @@
       <c r="R19" t="n">
         <v>18.5</v>
       </c>
-      <c r="S19" t="n">
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="n">
         <v>5.71</v>
       </c>
     </row>
@@ -1920,6 +2144,20 @@
         <v>14.5</v>
       </c>
       <c r="S20" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>60</v>
+      </c>
+      <c r="W20" t="n">
         <v>3.19</v>
       </c>
     </row>
@@ -1993,6 +2231,20 @@
         <v>12.4</v>
       </c>
       <c r="S21" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="W21" t="n">
         <v>6.09</v>
       </c>
     </row>
@@ -2066,6 +2318,20 @@
         <v>17.9</v>
       </c>
       <c r="S22" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="W22" t="n">
         <v>3.1</v>
       </c>
     </row>
@@ -2139,6 +2405,20 @@
         <v>14.8</v>
       </c>
       <c r="S23" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="W23" t="n">
         <v>6.69</v>
       </c>
     </row>
@@ -2212,6 +2492,20 @@
         <v>11.8</v>
       </c>
       <c r="S24" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="W24" t="n">
         <v>5.89</v>
       </c>
     </row>
@@ -2288,7 +2582,11 @@
       <c r="R25" t="n">
         <v>14.4</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="n">
         <v>5.91</v>
       </c>
     </row>
@@ -2362,6 +2660,20 @@
         <v>24</v>
       </c>
       <c r="S26" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="W26" t="n">
         <v>4.05</v>
       </c>
     </row>
@@ -2435,6 +2747,20 @@
         <v>17.2</v>
       </c>
       <c r="S27" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W27" t="n">
         <v>5.32</v>
       </c>
     </row>
@@ -2506,6 +2832,20 @@
         <v>58.5</v>
       </c>
       <c r="S28" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="W28" t="n">
         <v>1.06</v>
       </c>
     </row>
@@ -2520,101 +2860,121 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S233"/>
+  <dimension ref="A1:W233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>改善訊號數</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>A毛利拐頭</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>B月營收動能</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>C_EPS加速</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>D_ROE回升</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>近四季ROE</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>5年均ROE</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>循環</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>看哪個位階</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>估值位階</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ForwardPE</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>PEG</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>未來估值</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>成長率g%</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
@@ -2686,6 +3046,20 @@
         <v>40</v>
       </c>
       <c r="S2" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -2755,6 +3129,20 @@
         <v>30.6</v>
       </c>
       <c r="S3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="W3" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -2827,7 +3215,11 @@
       <c r="R4" t="n">
         <v>72.7</v>
       </c>
-      <c r="S4" t="n">
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -2897,6 +3289,20 @@
         <v>39.3</v>
       </c>
       <c r="S5" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>60</v>
+      </c>
+      <c r="W5" t="n">
         <v>3.76</v>
       </c>
     </row>
@@ -2966,6 +3372,20 @@
         <v>30.1</v>
       </c>
       <c r="S6" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="W6" t="n">
         <v>2.12</v>
       </c>
     </row>
@@ -3038,7 +3458,11 @@
       <c r="R7" t="n">
         <v>8.4</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
         <v>3.92</v>
       </c>
     </row>
@@ -3108,6 +3532,20 @@
         <v>79.3</v>
       </c>
       <c r="S8" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="W8" t="n">
         <v>0.54</v>
       </c>
     </row>
@@ -3177,6 +3615,20 @@
         <v>27.5</v>
       </c>
       <c r="S9" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="W9" t="n">
         <v>2.24</v>
       </c>
     </row>
@@ -3249,7 +3701,11 @@
       <c r="R10" t="n">
         <v>310.9</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="n">
         <v>0.17</v>
       </c>
     </row>
@@ -3322,7 +3778,11 @@
       <c r="R11" t="n">
         <v>320</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="n">
         <v>0.23</v>
       </c>
     </row>
@@ -3395,7 +3855,11 @@
       <c r="R12" t="n">
         <v>35.8</v>
       </c>
-      <c r="S12" t="n">
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="n">
         <v>1.05</v>
       </c>
     </row>
@@ -3468,7 +3932,11 @@
       <c r="R13" t="n">
         <v>17.6</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="n">
         <v>2.57</v>
       </c>
     </row>
@@ -3538,6 +4006,20 @@
         <v>10</v>
       </c>
       <c r="S14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="W14" t="n">
         <v>3.81</v>
       </c>
     </row>
@@ -3610,7 +4092,11 @@
       <c r="R15" t="n">
         <v>135.1</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -3684,6 +4170,20 @@
         <v>14.1</v>
       </c>
       <c r="S16" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="W16" t="n">
         <v>3.31</v>
       </c>
     </row>
@@ -3756,7 +4256,11 @@
       <c r="R17" t="n">
         <v>24.5</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -3829,7 +4333,11 @@
       <c r="R18" t="n">
         <v>27.9</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="n">
         <v>2.79</v>
       </c>
     </row>
@@ -3906,7 +4414,11 @@
       <c r="R19" t="n">
         <v>27</v>
       </c>
-      <c r="S19" t="n">
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="n">
         <v>2.81</v>
       </c>
     </row>
@@ -3976,6 +4488,20 @@
         <v>49.1</v>
       </c>
       <c r="S20" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="W20" t="n">
         <v>0.58</v>
       </c>
     </row>
@@ -4049,6 +4575,20 @@
         <v>20.2</v>
       </c>
       <c r="S21" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="W21" t="n">
         <v>4.01</v>
       </c>
     </row>
@@ -4116,6 +4656,20 @@
         <v>62</v>
       </c>
       <c r="S22" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>60</v>
+      </c>
+      <c r="W22" t="n">
         <v>1.09</v>
       </c>
     </row>
@@ -4188,7 +4742,11 @@
       <c r="R23" t="n">
         <v>66.5</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="n">
         <v>0.68</v>
       </c>
     </row>
@@ -4258,6 +4816,20 @@
         <v>33.7</v>
       </c>
       <c r="S24" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="W24" t="n">
         <v>0.88</v>
       </c>
     </row>
@@ -4327,6 +4899,20 @@
         <v>61.5</v>
       </c>
       <c r="S25" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="W25" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -4399,7 +4985,11 @@
       <c r="R26" t="n">
         <v>12.3</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="n">
         <v>6.76</v>
       </c>
     </row>
@@ -4472,7 +5062,11 @@
       <c r="R27" t="n">
         <v>21</v>
       </c>
-      <c r="S27" t="n">
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="n">
         <v>2.24</v>
       </c>
     </row>
@@ -4546,6 +5140,20 @@
         <v>17.5</v>
       </c>
       <c r="S28" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="W28" t="n">
         <v>3.49</v>
       </c>
     </row>
@@ -4618,7 +5226,11 @@
       <c r="R29" t="n">
         <v>32.3</v>
       </c>
-      <c r="S29" t="n">
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="n">
         <v>2.15</v>
       </c>
     </row>
@@ -4691,7 +5303,11 @@
       <c r="R30" t="n">
         <v>49.5</v>
       </c>
-      <c r="S30" t="n">
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="n">
         <v>1.23</v>
       </c>
     </row>
@@ -4762,7 +5378,11 @@
       <c r="R31" t="n">
         <v>14.8</v>
       </c>
-      <c r="S31" t="n">
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="n">
         <v>6.54</v>
       </c>
     </row>
@@ -4836,6 +5456,20 @@
         <v>13.9</v>
       </c>
       <c r="S32" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W32" t="n">
         <v>6.42</v>
       </c>
     </row>
@@ -4908,7 +5542,11 @@
       <c r="R33" t="n">
         <v>83.40000000000001</v>
       </c>
-      <c r="S33" t="n">
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="n">
         <v>0.87</v>
       </c>
     </row>
@@ -4978,6 +5616,20 @@
         <v>120.3</v>
       </c>
       <c r="S34" t="n">
+        <v>86</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="W34" t="n">
         <v>4.97</v>
       </c>
     </row>
@@ -5047,6 +5699,20 @@
         <v>104.6</v>
       </c>
       <c r="S35" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="W35" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -5119,7 +5785,11 @@
       <c r="R36" t="n">
         <v>30.3</v>
       </c>
-      <c r="S36" t="n">
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5192,7 +5862,11 @@
       <c r="R37" t="n">
         <v>16.1</v>
       </c>
-      <c r="S37" t="n">
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="n">
         <v>4.99</v>
       </c>
     </row>
@@ -5266,6 +5940,20 @@
         <v>11.8</v>
       </c>
       <c r="S38" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V38" t="n">
+        <v>12</v>
+      </c>
+      <c r="W38" t="n">
         <v>7.5</v>
       </c>
     </row>
@@ -5339,6 +6027,20 @@
         <v>14.9</v>
       </c>
       <c r="S39" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V39" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="W39" t="n">
         <v>5.42</v>
       </c>
     </row>
@@ -5411,7 +6113,11 @@
       <c r="R40" t="n">
         <v>69.5</v>
       </c>
-      <c r="S40" t="n">
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -5481,6 +6187,20 @@
         <v>17.1</v>
       </c>
       <c r="S41" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="V41" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="W41" t="n">
         <v>4.45</v>
       </c>
     </row>
@@ -5550,6 +6270,20 @@
         <v>109.8</v>
       </c>
       <c r="S42" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="V42" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="W42" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -5623,6 +6357,20 @@
         <v>12.9</v>
       </c>
       <c r="S43" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="V43" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="W43" t="n">
         <v>6.75</v>
       </c>
     </row>
@@ -5695,7 +6443,11 @@
       <c r="R44" t="n">
         <v>129.2</v>
       </c>
-      <c r="S44" t="n">
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="n">
         <v>0.64</v>
       </c>
     </row>
@@ -5765,6 +6517,20 @@
         <v>100.7</v>
       </c>
       <c r="S45" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="T45" t="n">
+        <v>83.38</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="V45" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W45" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -5834,6 +6600,20 @@
         <v>89.7</v>
       </c>
       <c r="S46" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="T46" t="n">
+        <v>97.01000000000001</v>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="V46" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="W46" t="n">
         <v>0.5600000000000001</v>
       </c>
     </row>
@@ -5903,6 +6683,20 @@
         <v>167.3</v>
       </c>
       <c r="S47" t="n">
+        <v>121.7</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="V47" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="W47" t="n">
         <v>0.34</v>
       </c>
     </row>
@@ -5972,6 +6766,20 @@
         <v>27.3</v>
       </c>
       <c r="S48" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="V48" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W48" t="n">
         <v>3.53</v>
       </c>
     </row>
@@ -6048,7 +6856,11 @@
       <c r="R49" t="n">
         <v>16.6</v>
       </c>
-      <c r="S49" t="n">
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="n">
         <v>6.66</v>
       </c>
     </row>
@@ -6122,6 +6934,20 @@
         <v>19.1</v>
       </c>
       <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V50" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="W50" t="n">
         <v>4.95</v>
       </c>
     </row>
@@ -6195,6 +7021,20 @@
         <v>19.4</v>
       </c>
       <c r="S51" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="V51" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="W51" t="n">
         <v>3.05</v>
       </c>
     </row>
@@ -6269,7 +7109,11 @@
       <c r="R52" t="n">
         <v>14.8</v>
       </c>
-      <c r="S52" t="n">
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="n">
         <v>5.24</v>
       </c>
     </row>
@@ -6342,7 +7186,11 @@
       <c r="R53" t="n">
         <v>25.3</v>
       </c>
-      <c r="S53" t="n">
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="n">
         <v>3.48</v>
       </c>
     </row>
@@ -6415,7 +7263,11 @@
       <c r="R54" t="n">
         <v>115.6</v>
       </c>
-      <c r="S54" t="n">
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -6485,6 +7337,20 @@
         <v>24.4</v>
       </c>
       <c r="S55" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="V55" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="W55" t="n">
         <v>2.26</v>
       </c>
     </row>
@@ -6554,6 +7420,20 @@
         <v>25.2</v>
       </c>
       <c r="S56" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="V56" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="W56" t="n">
         <v>3.03</v>
       </c>
     </row>
@@ -6626,7 +7506,11 @@
       <c r="R57" t="n">
         <v>23.8</v>
       </c>
-      <c r="S57" t="n">
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="n">
         <v>2.82</v>
       </c>
     </row>
@@ -6696,6 +7580,20 @@
         <v>11.2</v>
       </c>
       <c r="S58" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V58" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="W58" t="n">
         <v>4.9</v>
       </c>
     </row>
@@ -6768,7 +7666,11 @@
       <c r="R59" t="n">
         <v>10.5</v>
       </c>
-      <c r="S59" t="n">
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="n">
         <v>2.09</v>
       </c>
     </row>
@@ -6836,6 +7738,20 @@
         <v>26.5</v>
       </c>
       <c r="S60" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="V60" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W60" t="n">
         <v>2.88</v>
       </c>
     </row>
@@ -6908,7 +7824,11 @@
       <c r="R61" t="n">
         <v>29.8</v>
       </c>
-      <c r="S61" t="n">
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="n">
         <v>1.61</v>
       </c>
     </row>
@@ -6981,7 +7901,11 @@
       <c r="R62" t="n">
         <v>20.2</v>
       </c>
-      <c r="S62" t="n">
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="n">
         <v>4.43</v>
       </c>
     </row>
@@ -7052,7 +7976,11 @@
       <c r="R63" t="n">
         <v>99.8</v>
       </c>
-      <c r="S63" t="n">
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="n">
         <v>0.39</v>
       </c>
     </row>
@@ -7121,7 +8049,11 @@
       <c r="R64" t="n">
         <v>222.9</v>
       </c>
-      <c r="S64" t="n">
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7194,7 +8126,11 @@
       <c r="R65" t="n">
         <v>65.90000000000001</v>
       </c>
-      <c r="S65" t="n">
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="n">
         <v>0.23</v>
       </c>
     </row>
@@ -7267,7 +8203,11 @@
       <c r="R66" t="n">
         <v>19.4</v>
       </c>
-      <c r="S66" t="n">
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="n">
         <v>2.24</v>
       </c>
     </row>
@@ -7328,7 +8268,11 @@
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
-      <c r="S67" t="n">
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7397,7 +8341,11 @@
       <c r="R68" t="n">
         <v>132.8</v>
       </c>
-      <c r="S68" t="n">
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7468,7 +8416,11 @@
       <c r="R69" t="n">
         <v>56.2</v>
       </c>
-      <c r="S69" t="n">
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -7537,7 +8489,11 @@
       <c r="R70" t="n">
         <v>46.4</v>
       </c>
-      <c r="S70" t="n">
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7606,7 +8562,11 @@
       <c r="R71" t="n">
         <v>94.8</v>
       </c>
-      <c r="S71" t="n">
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7679,7 +8639,11 @@
       <c r="R72" t="n">
         <v>24.2</v>
       </c>
-      <c r="S72" t="n">
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="n">
         <v>2.03</v>
       </c>
     </row>
@@ -7752,7 +8716,11 @@
       <c r="R73" t="n">
         <v>45.2</v>
       </c>
-      <c r="S73" t="n">
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="n">
         <v>0.27</v>
       </c>
     </row>
@@ -7822,6 +8790,20 @@
         <v>38.1</v>
       </c>
       <c r="S74" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="T74" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="V74" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W74" t="n">
         <v>1.57</v>
       </c>
     </row>
@@ -7894,7 +8876,11 @@
       <c r="R75" t="n">
         <v>14.2</v>
       </c>
-      <c r="S75" t="n">
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="n">
         <v>3.38</v>
       </c>
     </row>
@@ -7967,7 +8953,11 @@
       <c r="R76" t="n">
         <v>15.5</v>
       </c>
-      <c r="S76" t="n">
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="n">
         <v>3.47</v>
       </c>
     </row>
@@ -8036,7 +9026,11 @@
       <c r="R77" t="n">
         <v>7.3</v>
       </c>
-      <c r="S77" t="n">
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="n">
         <v>3.51</v>
       </c>
     </row>
@@ -8109,7 +9103,11 @@
       <c r="R78" t="n">
         <v>2.6</v>
       </c>
-      <c r="S78" t="n">
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="n">
         <v>6.03</v>
       </c>
     </row>
@@ -8180,7 +9178,11 @@
       <c r="R79" t="n">
         <v>23.3</v>
       </c>
-      <c r="S79" t="n">
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="n">
         <v>2.94</v>
       </c>
     </row>
@@ -8250,6 +9252,20 @@
         <v>36.5</v>
       </c>
       <c r="S80" t="n">
+        <v>31</v>
+      </c>
+      <c r="T80" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="V80" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="W80" t="n">
         <v>2.04</v>
       </c>
     </row>
@@ -8323,6 +9339,20 @@
         <v>14.7</v>
       </c>
       <c r="S81" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V81" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="W81" t="n">
         <v>4.71</v>
       </c>
     </row>
@@ -8395,7 +9425,11 @@
       <c r="R82" t="n">
         <v>24</v>
       </c>
-      <c r="S82" t="n">
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="n">
         <v>3.38</v>
       </c>
     </row>
@@ -8465,6 +9499,20 @@
         <v>21.9</v>
       </c>
       <c r="S83" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V83" t="n">
+        <v>60</v>
+      </c>
+      <c r="W83" t="n">
         <v>2.91</v>
       </c>
     </row>
@@ -8534,6 +9582,20 @@
         <v>21.3</v>
       </c>
       <c r="S84" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="T84" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="V84" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W84" t="n">
         <v>2.67</v>
       </c>
     </row>
@@ -8606,7 +9668,11 @@
       <c r="R85" t="n">
         <v>26</v>
       </c>
-      <c r="S85" t="n">
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
+      <c r="W85" t="n">
         <v>0.87</v>
       </c>
     </row>
@@ -8679,7 +9745,11 @@
       <c r="R86" t="n">
         <v>19.6</v>
       </c>
-      <c r="S86" t="n">
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="n">
         <v>4.54</v>
       </c>
     </row>
@@ -8752,7 +9822,11 @@
       <c r="R87" t="n">
         <v>163.5</v>
       </c>
-      <c r="S87" t="n">
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="n">
         <v>0.42</v>
       </c>
     </row>
@@ -8822,6 +9896,20 @@
         <v>23.8</v>
       </c>
       <c r="S88" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V88" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="W88" t="n">
         <v>3.13</v>
       </c>
     </row>
@@ -8891,6 +9979,20 @@
         <v>28.3</v>
       </c>
       <c r="S89" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="T89" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="V89" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="W89" t="n">
         <v>3.21</v>
       </c>
     </row>
@@ -8960,6 +10062,20 @@
         <v>54.5</v>
       </c>
       <c r="S90" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="T90" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="V90" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="W90" t="n">
         <v>3.5</v>
       </c>
     </row>
@@ -9029,6 +10145,20 @@
         <v>18.4</v>
       </c>
       <c r="S91" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="T91" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="V91" t="n">
+        <v>5</v>
+      </c>
+      <c r="W91" t="n">
         <v>5.05</v>
       </c>
     </row>
@@ -9102,6 +10232,20 @@
         <v>20.4</v>
       </c>
       <c r="S92" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="T92" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="V92" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W92" t="n">
         <v>2.83</v>
       </c>
     </row>
@@ -9171,6 +10315,20 @@
         <v>23.4</v>
       </c>
       <c r="S93" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="T93" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="V93" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W93" t="n">
         <v>2.2</v>
       </c>
     </row>
@@ -9247,7 +10405,11 @@
       <c r="R94" t="n">
         <v>14.4</v>
       </c>
-      <c r="S94" t="n">
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="inlineStr"/>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr"/>
+      <c r="W94" t="n">
         <v>5.91</v>
       </c>
     </row>
@@ -9317,6 +10479,18 @@
         <v>21.5</v>
       </c>
       <c r="S95" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="V95" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="W95" t="n">
         <v>3.34</v>
       </c>
     </row>
@@ -9389,7 +10563,11 @@
       <c r="R96" t="n">
         <v>192</v>
       </c>
-      <c r="S96" t="n">
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="inlineStr"/>
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr"/>
+      <c r="W96" t="n">
         <v>0.53</v>
       </c>
     </row>
@@ -9462,7 +10640,11 @@
       <c r="R97" t="n">
         <v>40.2</v>
       </c>
-      <c r="S97" t="n">
+      <c r="S97" t="inlineStr"/>
+      <c r="T97" t="inlineStr"/>
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr"/>
+      <c r="W97" t="n">
         <v>1.48</v>
       </c>
     </row>
@@ -9535,7 +10717,11 @@
       <c r="R98" t="n">
         <v>149.4</v>
       </c>
-      <c r="S98" t="n">
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr"/>
+      <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr"/>
+      <c r="W98" t="n">
         <v>1.32</v>
       </c>
     </row>
@@ -9608,7 +10794,11 @@
       <c r="R99" t="n">
         <v>36.1</v>
       </c>
-      <c r="S99" t="n">
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr"/>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr"/>
+      <c r="W99" t="n">
         <v>2.07</v>
       </c>
     </row>
@@ -9678,6 +10868,20 @@
         <v>26.1</v>
       </c>
       <c r="S100" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="T100" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="V100" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W100" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9747,6 +10951,20 @@
         <v>57.1</v>
       </c>
       <c r="S101" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="T101" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V101" t="n">
+        <v>60</v>
+      </c>
+      <c r="W101" t="n">
         <v>1.44</v>
       </c>
     </row>
@@ -9819,7 +11037,11 @@
       <c r="R102" t="n">
         <v>19.9</v>
       </c>
-      <c r="S102" t="n">
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr"/>
+      <c r="U102" t="inlineStr"/>
+      <c r="V102" t="inlineStr"/>
+      <c r="W102" t="n">
         <v>3.65</v>
       </c>
     </row>
@@ -9893,6 +11115,20 @@
         <v>16.4</v>
       </c>
       <c r="S103" t="n">
+        <v>16</v>
+      </c>
+      <c r="T103" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="V103" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W103" t="n">
         <v>5.07</v>
       </c>
     </row>
@@ -9962,6 +11198,20 @@
         <v>142.2</v>
       </c>
       <c r="S104" t="n">
+        <v>141.4</v>
+      </c>
+      <c r="T104" t="n">
+        <v>269.79</v>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="V104" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W104" t="n">
         <v>0.42</v>
       </c>
     </row>
@@ -10035,6 +11285,20 @@
         <v>17.2</v>
       </c>
       <c r="S105" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="T105" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="V105" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W105" t="n">
         <v>5.32</v>
       </c>
     </row>
@@ -10094,6 +11358,10 @@
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr"/>
+      <c r="T106" t="inlineStr"/>
+      <c r="U106" t="inlineStr"/>
+      <c r="V106" t="inlineStr"/>
+      <c r="W106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -10160,7 +11428,11 @@
       <c r="R107" t="n">
         <v>65.2</v>
       </c>
-      <c r="S107" t="n">
+      <c r="S107" t="inlineStr"/>
+      <c r="T107" t="inlineStr"/>
+      <c r="U107" t="inlineStr"/>
+      <c r="V107" t="inlineStr"/>
+      <c r="W107" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -10229,7 +11501,11 @@
       <c r="R108" t="n">
         <v>4.98045135262149e+17</v>
       </c>
-      <c r="S108" t="n">
+      <c r="S108" t="inlineStr"/>
+      <c r="T108" t="inlineStr"/>
+      <c r="U108" t="inlineStr"/>
+      <c r="V108" t="inlineStr"/>
+      <c r="W108" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10298,7 +11574,11 @@
       <c r="R109" t="n">
         <v>308.3</v>
       </c>
-      <c r="S109" t="n">
+      <c r="S109" t="inlineStr"/>
+      <c r="T109" t="inlineStr"/>
+      <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr"/>
+      <c r="W109" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10367,7 +11647,11 @@
       <c r="R110" t="n">
         <v>16</v>
       </c>
-      <c r="S110" t="n">
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" t="inlineStr"/>
+      <c r="U110" t="inlineStr"/>
+      <c r="V110" t="inlineStr"/>
+      <c r="W110" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10434,7 +11718,11 @@
         <v>25</v>
       </c>
       <c r="R111" t="inlineStr"/>
-      <c r="S111" t="n">
+      <c r="S111" t="inlineStr"/>
+      <c r="T111" t="inlineStr"/>
+      <c r="U111" t="inlineStr"/>
+      <c r="V111" t="inlineStr"/>
+      <c r="W111" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10504,6 +11792,20 @@
         <v>40.6</v>
       </c>
       <c r="S112" t="n">
+        <v>32</v>
+      </c>
+      <c r="T112" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="V112" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="W112" t="n">
         <v>0.87</v>
       </c>
     </row>
@@ -10572,7 +11874,11 @@
       <c r="R113" t="n">
         <v>589.2</v>
       </c>
-      <c r="S113" t="n">
+      <c r="S113" t="inlineStr"/>
+      <c r="T113" t="inlineStr"/>
+      <c r="U113" t="inlineStr"/>
+      <c r="V113" t="inlineStr"/>
+      <c r="W113" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10643,7 +11949,11 @@
       <c r="R114" t="n">
         <v>600</v>
       </c>
-      <c r="S114" t="n">
+      <c r="S114" t="inlineStr"/>
+      <c r="T114" t="inlineStr"/>
+      <c r="U114" t="inlineStr"/>
+      <c r="V114" t="inlineStr"/>
+      <c r="W114" t="n">
         <v>1.52</v>
       </c>
     </row>
@@ -10713,6 +12023,20 @@
         <v>36.4</v>
       </c>
       <c r="S115" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="T115" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="V115" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="W115" t="n">
         <v>2.81</v>
       </c>
     </row>
@@ -10785,7 +12109,11 @@
       <c r="R116" t="n">
         <v>27.2</v>
       </c>
-      <c r="S116" t="n">
+      <c r="S116" t="inlineStr"/>
+      <c r="T116" t="inlineStr"/>
+      <c r="U116" t="inlineStr"/>
+      <c r="V116" t="inlineStr"/>
+      <c r="W116" t="n">
         <v>1.32</v>
       </c>
     </row>
@@ -10858,7 +12186,11 @@
       <c r="R117" t="n">
         <v>75</v>
       </c>
-      <c r="S117" t="n">
+      <c r="S117" t="inlineStr"/>
+      <c r="T117" t="inlineStr"/>
+      <c r="U117" t="inlineStr"/>
+      <c r="V117" t="inlineStr"/>
+      <c r="W117" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -10931,7 +12263,11 @@
       <c r="R118" t="n">
         <v>30.2</v>
       </c>
-      <c r="S118" t="n">
+      <c r="S118" t="inlineStr"/>
+      <c r="T118" t="inlineStr"/>
+      <c r="U118" t="inlineStr"/>
+      <c r="V118" t="inlineStr"/>
+      <c r="W118" t="n">
         <v>2.86</v>
       </c>
     </row>
@@ -11002,7 +12338,11 @@
       <c r="R119" t="n">
         <v>20.2</v>
       </c>
-      <c r="S119" t="n">
+      <c r="S119" t="inlineStr"/>
+      <c r="T119" t="inlineStr"/>
+      <c r="U119" t="inlineStr"/>
+      <c r="V119" t="inlineStr"/>
+      <c r="W119" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -11071,7 +12411,11 @@
       <c r="R120" t="n">
         <v>35.4</v>
       </c>
-      <c r="S120" t="n">
+      <c r="S120" t="inlineStr"/>
+      <c r="T120" t="inlineStr"/>
+      <c r="U120" t="inlineStr"/>
+      <c r="V120" t="inlineStr"/>
+      <c r="W120" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -11144,7 +12488,11 @@
       <c r="R121" t="n">
         <v>77.8</v>
       </c>
-      <c r="S121" t="n">
+      <c r="S121" t="inlineStr"/>
+      <c r="T121" t="inlineStr"/>
+      <c r="U121" t="inlineStr"/>
+      <c r="V121" t="inlineStr"/>
+      <c r="W121" t="n">
         <v>0.58</v>
       </c>
     </row>
@@ -11217,7 +12565,11 @@
       <c r="R122" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="S122" t="n">
+      <c r="S122" t="inlineStr"/>
+      <c r="T122" t="inlineStr"/>
+      <c r="U122" t="inlineStr"/>
+      <c r="V122" t="inlineStr"/>
+      <c r="W122" t="n">
         <v>1.09</v>
       </c>
     </row>
@@ -11286,7 +12638,11 @@
       <c r="R123" t="n">
         <v>18</v>
       </c>
-      <c r="S123" t="n">
+      <c r="S123" t="inlineStr"/>
+      <c r="T123" t="inlineStr"/>
+      <c r="U123" t="inlineStr"/>
+      <c r="V123" t="inlineStr"/>
+      <c r="W123" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11363,7 +12719,11 @@
       <c r="R124" t="n">
         <v>18.5</v>
       </c>
-      <c r="S124" t="n">
+      <c r="S124" t="inlineStr"/>
+      <c r="T124" t="inlineStr"/>
+      <c r="U124" t="inlineStr"/>
+      <c r="V124" t="inlineStr"/>
+      <c r="W124" t="n">
         <v>5.71</v>
       </c>
     </row>
@@ -11436,7 +12796,11 @@
       <c r="R125" t="n">
         <v>339</v>
       </c>
-      <c r="S125" t="n">
+      <c r="S125" t="inlineStr"/>
+      <c r="T125" t="inlineStr"/>
+      <c r="U125" t="inlineStr"/>
+      <c r="V125" t="inlineStr"/>
+      <c r="W125" t="n">
         <v>0.36</v>
       </c>
     </row>
@@ -11506,6 +12870,20 @@
         <v>32.9</v>
       </c>
       <c r="S126" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="T126" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="V126" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W126" t="n">
         <v>2.24</v>
       </c>
     </row>
@@ -11578,7 +12956,11 @@
       <c r="R127" t="n">
         <v>192.6</v>
       </c>
-      <c r="S127" t="n">
+      <c r="S127" t="inlineStr"/>
+      <c r="T127" t="inlineStr"/>
+      <c r="U127" t="inlineStr"/>
+      <c r="V127" t="inlineStr"/>
+      <c r="W127" t="n">
         <v>0.22</v>
       </c>
     </row>
@@ -11651,7 +13033,11 @@
       <c r="R128" t="n">
         <v>142.3</v>
       </c>
-      <c r="S128" t="n">
+      <c r="S128" t="inlineStr"/>
+      <c r="T128" t="inlineStr"/>
+      <c r="U128" t="inlineStr"/>
+      <c r="V128" t="inlineStr"/>
+      <c r="W128" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -11724,7 +13110,11 @@
       <c r="R129" t="n">
         <v>16.9</v>
       </c>
-      <c r="S129" t="n">
+      <c r="S129" t="inlineStr"/>
+      <c r="T129" t="inlineStr"/>
+      <c r="U129" t="inlineStr"/>
+      <c r="V129" t="inlineStr"/>
+      <c r="W129" t="n">
         <v>5.04</v>
       </c>
     </row>
@@ -11792,6 +13182,20 @@
         <v>76.09999999999999</v>
       </c>
       <c r="S130" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="T130" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="V130" t="n">
+        <v>33</v>
+      </c>
+      <c r="W130" t="n">
         <v>0.83</v>
       </c>
     </row>
@@ -11864,7 +13268,11 @@
       <c r="R131" t="n">
         <v>77.09999999999999</v>
       </c>
-      <c r="S131" t="n">
+      <c r="S131" t="inlineStr"/>
+      <c r="T131" t="inlineStr"/>
+      <c r="U131" t="inlineStr"/>
+      <c r="V131" t="inlineStr"/>
+      <c r="W131" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -11937,7 +13345,11 @@
       <c r="R132" t="n">
         <v>25.5</v>
       </c>
-      <c r="S132" t="n">
+      <c r="S132" t="inlineStr"/>
+      <c r="T132" t="inlineStr"/>
+      <c r="U132" t="inlineStr"/>
+      <c r="V132" t="inlineStr"/>
+      <c r="W132" t="n">
         <v>3.23</v>
       </c>
     </row>
@@ -12010,7 +13422,11 @@
       <c r="R133" t="n">
         <v>22</v>
       </c>
-      <c r="S133" t="n">
+      <c r="S133" t="inlineStr"/>
+      <c r="T133" t="inlineStr"/>
+      <c r="U133" t="inlineStr"/>
+      <c r="V133" t="inlineStr"/>
+      <c r="W133" t="n">
         <v>3.31</v>
       </c>
     </row>
@@ -12080,6 +13496,20 @@
         <v>63.8</v>
       </c>
       <c r="S134" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="T134" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="V134" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="W134" t="n">
         <v>0.78</v>
       </c>
     </row>
@@ -12152,7 +13582,11 @@
       <c r="R135" t="n">
         <v>53.2</v>
       </c>
-      <c r="S135" t="n">
+      <c r="S135" t="inlineStr"/>
+      <c r="T135" t="inlineStr"/>
+      <c r="U135" t="inlineStr"/>
+      <c r="V135" t="inlineStr"/>
+      <c r="W135" t="n">
         <v>0.5600000000000001</v>
       </c>
     </row>
@@ -12222,6 +13656,18 @@
         <v>13.7</v>
       </c>
       <c r="S136" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="T136" t="inlineStr"/>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="V136" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="W136" t="n">
         <v>5.08</v>
       </c>
     </row>
@@ -12294,7 +13740,11 @@
       <c r="R137" t="n">
         <v>62.1</v>
       </c>
-      <c r="S137" t="n">
+      <c r="S137" t="inlineStr"/>
+      <c r="T137" t="inlineStr"/>
+      <c r="U137" t="inlineStr"/>
+      <c r="V137" t="inlineStr"/>
+      <c r="W137" t="n">
         <v>0.98</v>
       </c>
     </row>
@@ -12368,6 +13818,20 @@
         <v>12.4</v>
       </c>
       <c r="S138" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V138" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="W138" t="n">
         <v>6.09</v>
       </c>
     </row>
@@ -12437,6 +13901,18 @@
         <v>24.6</v>
       </c>
       <c r="S139" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="T139" t="inlineStr"/>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="V139" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="W139" t="n">
         <v>2.24</v>
       </c>
     </row>
@@ -12506,6 +13982,18 @@
         <v>38.6</v>
       </c>
       <c r="S140" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="T140" t="inlineStr"/>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="V140" t="n">
+        <v>-4</v>
+      </c>
+      <c r="W140" t="n">
         <v>2.24</v>
       </c>
     </row>
@@ -12578,7 +14066,11 @@
       <c r="R141" t="n">
         <v>44.3</v>
       </c>
-      <c r="S141" t="n">
+      <c r="S141" t="inlineStr"/>
+      <c r="T141" t="inlineStr"/>
+      <c r="U141" t="inlineStr"/>
+      <c r="V141" t="inlineStr"/>
+      <c r="W141" t="n">
         <v>2.41</v>
       </c>
     </row>
@@ -12648,6 +14140,20 @@
         <v>67.8</v>
       </c>
       <c r="S142" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="T142" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="V142" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="W142" t="n">
         <v>1.29</v>
       </c>
     </row>
@@ -12717,6 +14223,20 @@
         <v>15.6</v>
       </c>
       <c r="S143" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="T143" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="V143" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W143" t="n">
         <v>5.48</v>
       </c>
     </row>
@@ -12790,6 +14310,20 @@
         <v>14.8</v>
       </c>
       <c r="S144" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="T144" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="V144" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="W144" t="n">
         <v>6.69</v>
       </c>
     </row>
@@ -12859,6 +14393,20 @@
         <v>16.5</v>
       </c>
       <c r="S145" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="T145" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="V145" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W145" t="n">
         <v>5.25</v>
       </c>
     </row>
@@ -12932,6 +14480,20 @@
         <v>24</v>
       </c>
       <c r="S146" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="T146" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="V146" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="W146" t="n">
         <v>4.05</v>
       </c>
     </row>
@@ -13001,6 +14563,20 @@
         <v>19.8</v>
       </c>
       <c r="S147" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="T147" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="V147" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W147" t="n">
         <v>4.33</v>
       </c>
     </row>
@@ -13070,6 +14646,18 @@
         <v>43.6</v>
       </c>
       <c r="S148" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="T148" t="inlineStr"/>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="V148" t="n">
+        <v>-13.6</v>
+      </c>
+      <c r="W148" t="n">
         <v>1.23</v>
       </c>
     </row>
@@ -13142,7 +14730,11 @@
       <c r="R149" t="n">
         <v>27.6</v>
       </c>
-      <c r="S149" t="n">
+      <c r="S149" t="inlineStr"/>
+      <c r="T149" t="inlineStr"/>
+      <c r="U149" t="inlineStr"/>
+      <c r="V149" t="inlineStr"/>
+      <c r="W149" t="n">
         <v>4.45</v>
       </c>
     </row>
@@ -13216,6 +14808,20 @@
         <v>14.5</v>
       </c>
       <c r="S150" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="T150" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V150" t="n">
+        <v>60</v>
+      </c>
+      <c r="W150" t="n">
         <v>3.19</v>
       </c>
     </row>
@@ -13288,7 +14894,11 @@
       <c r="R151" t="n">
         <v>16.1</v>
       </c>
-      <c r="S151" t="n">
+      <c r="S151" t="inlineStr"/>
+      <c r="T151" t="inlineStr"/>
+      <c r="U151" t="inlineStr"/>
+      <c r="V151" t="inlineStr"/>
+      <c r="W151" t="n">
         <v>3.45</v>
       </c>
     </row>
@@ -13361,7 +14971,11 @@
       <c r="R152" t="n">
         <v>165.8</v>
       </c>
-      <c r="S152" t="n">
+      <c r="S152" t="inlineStr"/>
+      <c r="T152" t="inlineStr"/>
+      <c r="U152" t="inlineStr"/>
+      <c r="V152" t="inlineStr"/>
+      <c r="W152" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -13435,6 +15049,20 @@
         <v>11.8</v>
       </c>
       <c r="S153" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="T153" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V153" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="W153" t="n">
         <v>5.89</v>
       </c>
     </row>
@@ -13507,7 +15135,11 @@
       <c r="R154" t="n">
         <v>61.9</v>
       </c>
-      <c r="S154" t="n">
+      <c r="S154" t="inlineStr"/>
+      <c r="T154" t="inlineStr"/>
+      <c r="U154" t="inlineStr"/>
+      <c r="V154" t="inlineStr"/>
+      <c r="W154" t="n">
         <v>1.56</v>
       </c>
     </row>
@@ -13584,7 +15216,11 @@
       <c r="R155" t="n">
         <v>14.8</v>
       </c>
-      <c r="S155" t="n">
+      <c r="S155" t="inlineStr"/>
+      <c r="T155" t="inlineStr"/>
+      <c r="U155" t="inlineStr"/>
+      <c r="V155" t="inlineStr"/>
+      <c r="W155" t="n">
         <v>5.13</v>
       </c>
     </row>
@@ -13657,7 +15293,11 @@
       <c r="R156" t="n">
         <v>26.6</v>
       </c>
-      <c r="S156" t="n">
+      <c r="S156" t="inlineStr"/>
+      <c r="T156" t="inlineStr"/>
+      <c r="U156" t="inlineStr"/>
+      <c r="V156" t="inlineStr"/>
+      <c r="W156" t="n">
         <v>3.92</v>
       </c>
     </row>
@@ -13730,7 +15370,11 @@
       <c r="R157" t="n">
         <v>96.59999999999999</v>
       </c>
-      <c r="S157" t="n">
+      <c r="S157" t="inlineStr"/>
+      <c r="T157" t="inlineStr"/>
+      <c r="U157" t="inlineStr"/>
+      <c r="V157" t="inlineStr"/>
+      <c r="W157" t="n">
         <v>1.08</v>
       </c>
     </row>
@@ -13800,6 +15444,20 @@
         <v>28.7</v>
       </c>
       <c r="S158" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="T158" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="V158" t="n">
+        <v>2</v>
+      </c>
+      <c r="W158" t="n">
         <v>3.6</v>
       </c>
     </row>
@@ -13872,7 +15530,11 @@
       <c r="R159" t="n">
         <v>25.8</v>
       </c>
-      <c r="S159" t="n">
+      <c r="S159" t="inlineStr"/>
+      <c r="T159" t="inlineStr"/>
+      <c r="U159" t="inlineStr"/>
+      <c r="V159" t="inlineStr"/>
+      <c r="W159" t="n">
         <v>3.82</v>
       </c>
     </row>
@@ -13942,6 +15604,18 @@
         <v>34</v>
       </c>
       <c r="S160" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="T160" t="inlineStr"/>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="V160" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="W160" t="n">
         <v>2.12</v>
       </c>
     </row>
@@ -14014,7 +15688,11 @@
       <c r="R161" t="n">
         <v>14.1</v>
       </c>
-      <c r="S161" t="n">
+      <c r="S161" t="inlineStr"/>
+      <c r="T161" t="inlineStr"/>
+      <c r="U161" t="inlineStr"/>
+      <c r="V161" t="inlineStr"/>
+      <c r="W161" t="n">
         <v>5.33</v>
       </c>
     </row>
@@ -14089,7 +15767,11 @@
       <c r="R162" t="n">
         <v>14.2</v>
       </c>
-      <c r="S162" t="n">
+      <c r="S162" t="inlineStr"/>
+      <c r="T162" t="inlineStr"/>
+      <c r="U162" t="inlineStr"/>
+      <c r="V162" t="inlineStr"/>
+      <c r="W162" t="n">
         <v>4.12</v>
       </c>
     </row>
@@ -14162,7 +15844,11 @@
       <c r="R163" t="n">
         <v>58</v>
       </c>
-      <c r="S163" t="n">
+      <c r="S163" t="inlineStr"/>
+      <c r="T163" t="inlineStr"/>
+      <c r="U163" t="inlineStr"/>
+      <c r="V163" t="inlineStr"/>
+      <c r="W163" t="n">
         <v>1.51</v>
       </c>
     </row>
@@ -14234,6 +15920,20 @@
         <v>58.5</v>
       </c>
       <c r="S164" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="T164" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="V164" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="W164" t="n">
         <v>1.06</v>
       </c>
     </row>
@@ -14306,7 +16006,11 @@
       <c r="R165" t="n">
         <v>22.3</v>
       </c>
-      <c r="S165" t="n">
+      <c r="S165" t="inlineStr"/>
+      <c r="T165" t="inlineStr"/>
+      <c r="U165" t="inlineStr"/>
+      <c r="V165" t="inlineStr"/>
+      <c r="W165" t="n">
         <v>2.94</v>
       </c>
     </row>
@@ -14379,7 +16083,11 @@
       <c r="R166" t="n">
         <v>10.2</v>
       </c>
-      <c r="S166" t="n">
+      <c r="S166" t="inlineStr"/>
+      <c r="T166" t="inlineStr"/>
+      <c r="U166" t="inlineStr"/>
+      <c r="V166" t="inlineStr"/>
+      <c r="W166" t="n">
         <v>2.29</v>
       </c>
     </row>
@@ -14452,7 +16160,11 @@
       <c r="R167" t="n">
         <v>40.2</v>
       </c>
-      <c r="S167" t="n">
+      <c r="S167" t="inlineStr"/>
+      <c r="T167" t="inlineStr"/>
+      <c r="U167" t="inlineStr"/>
+      <c r="V167" t="inlineStr"/>
+      <c r="W167" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -14525,7 +16237,11 @@
       <c r="R168" t="n">
         <v>36.3</v>
       </c>
-      <c r="S168" t="n">
+      <c r="S168" t="inlineStr"/>
+      <c r="T168" t="inlineStr"/>
+      <c r="U168" t="inlineStr"/>
+      <c r="V168" t="inlineStr"/>
+      <c r="W168" t="n">
         <v>1.73</v>
       </c>
     </row>
@@ -14599,6 +16315,20 @@
         <v>17.9</v>
       </c>
       <c r="S169" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="T169" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V169" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="W169" t="n">
         <v>3.1</v>
       </c>
     </row>
@@ -14671,7 +16401,11 @@
       <c r="R170" t="n">
         <v>103.6</v>
       </c>
-      <c r="S170" t="n">
+      <c r="S170" t="inlineStr"/>
+      <c r="T170" t="inlineStr"/>
+      <c r="U170" t="inlineStr"/>
+      <c r="V170" t="inlineStr"/>
+      <c r="W170" t="n">
         <v>0.37</v>
       </c>
     </row>
@@ -14744,7 +16478,11 @@
       <c r="R171" t="n">
         <v>70.09999999999999</v>
       </c>
-      <c r="S171" t="n">
+      <c r="S171" t="inlineStr"/>
+      <c r="T171" t="inlineStr"/>
+      <c r="U171" t="inlineStr"/>
+      <c r="V171" t="inlineStr"/>
+      <c r="W171" t="n">
         <v>0.59</v>
       </c>
     </row>
@@ -14807,7 +16545,11 @@
       <c r="R172" t="n">
         <v>93.3</v>
       </c>
-      <c r="S172" t="n">
+      <c r="S172" t="inlineStr"/>
+      <c r="T172" t="inlineStr"/>
+      <c r="U172" t="inlineStr"/>
+      <c r="V172" t="inlineStr"/>
+      <c r="W172" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -14878,7 +16620,11 @@
       <c r="R173" t="n">
         <v>69.3</v>
       </c>
-      <c r="S173" t="n">
+      <c r="S173" t="inlineStr"/>
+      <c r="T173" t="inlineStr"/>
+      <c r="U173" t="inlineStr"/>
+      <c r="V173" t="inlineStr"/>
+      <c r="W173" t="n">
         <v>1.18</v>
       </c>
     </row>
@@ -14951,7 +16697,11 @@
       <c r="R174" t="n">
         <v>19.2</v>
       </c>
-      <c r="S174" t="n">
+      <c r="S174" t="inlineStr"/>
+      <c r="T174" t="inlineStr"/>
+      <c r="U174" t="inlineStr"/>
+      <c r="V174" t="inlineStr"/>
+      <c r="W174" t="n">
         <v>5.33</v>
       </c>
     </row>
@@ -15020,7 +16770,11 @@
       <c r="R175" t="n">
         <v>313.4</v>
       </c>
-      <c r="S175" t="n">
+      <c r="S175" t="inlineStr"/>
+      <c r="T175" t="inlineStr"/>
+      <c r="U175" t="inlineStr"/>
+      <c r="V175" t="inlineStr"/>
+      <c r="W175" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15093,7 +16847,11 @@
       <c r="R176" t="n">
         <v>1184.6</v>
       </c>
-      <c r="S176" t="n">
+      <c r="S176" t="inlineStr"/>
+      <c r="T176" t="inlineStr"/>
+      <c r="U176" t="inlineStr"/>
+      <c r="V176" t="inlineStr"/>
+      <c r="W176" t="n">
         <v>0.26</v>
       </c>
     </row>
@@ -15164,7 +16922,11 @@
       <c r="R177" t="n">
         <v>87.5</v>
       </c>
-      <c r="S177" t="n">
+      <c r="S177" t="inlineStr"/>
+      <c r="T177" t="inlineStr"/>
+      <c r="U177" t="inlineStr"/>
+      <c r="V177" t="inlineStr"/>
+      <c r="W177" t="n">
         <v>1.57</v>
       </c>
     </row>
@@ -15225,7 +16987,11 @@
       <c r="R178" t="n">
         <v>278.3</v>
       </c>
-      <c r="S178" t="n">
+      <c r="S178" t="inlineStr"/>
+      <c r="T178" t="inlineStr"/>
+      <c r="U178" t="inlineStr"/>
+      <c r="V178" t="inlineStr"/>
+      <c r="W178" t="n">
         <v>0.22</v>
       </c>
     </row>
@@ -15292,7 +17058,11 @@
         <v>100</v>
       </c>
       <c r="R179" t="inlineStr"/>
-      <c r="S179" t="n">
+      <c r="S179" t="inlineStr"/>
+      <c r="T179" t="inlineStr"/>
+      <c r="U179" t="inlineStr"/>
+      <c r="V179" t="inlineStr"/>
+      <c r="W179" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15362,6 +17132,20 @@
         <v>13.3</v>
       </c>
       <c r="S180" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="T180" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="V180" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="W180" t="n">
         <v>4.78</v>
       </c>
     </row>
@@ -15434,7 +17218,11 @@
       <c r="R181" t="n">
         <v>18.1</v>
       </c>
-      <c r="S181" t="n">
+      <c r="S181" t="inlineStr"/>
+      <c r="T181" t="inlineStr"/>
+      <c r="U181" t="inlineStr"/>
+      <c r="V181" t="inlineStr"/>
+      <c r="W181" t="n">
         <v>5.03</v>
       </c>
     </row>
@@ -15507,7 +17295,11 @@
       <c r="R182" t="n">
         <v>25.9</v>
       </c>
-      <c r="S182" t="n">
+      <c r="S182" t="inlineStr"/>
+      <c r="T182" t="inlineStr"/>
+      <c r="U182" t="inlineStr"/>
+      <c r="V182" t="inlineStr"/>
+      <c r="W182" t="n">
         <v>2.72</v>
       </c>
     </row>
@@ -15580,7 +17372,11 @@
       <c r="R183" t="n">
         <v>20.5</v>
       </c>
-      <c r="S183" t="n">
+      <c r="S183" t="inlineStr"/>
+      <c r="T183" t="inlineStr"/>
+      <c r="U183" t="inlineStr"/>
+      <c r="V183" t="inlineStr"/>
+      <c r="W183" t="n">
         <v>4.15</v>
       </c>
     </row>
@@ -15653,7 +17449,11 @@
       <c r="R184" t="n">
         <v>14.3</v>
       </c>
-      <c r="S184" t="n">
+      <c r="S184" t="inlineStr"/>
+      <c r="T184" t="inlineStr"/>
+      <c r="U184" t="inlineStr"/>
+      <c r="V184" t="inlineStr"/>
+      <c r="W184" t="n">
         <v>3.88</v>
       </c>
     </row>
@@ -15723,6 +17523,20 @@
         <v>60.2</v>
       </c>
       <c r="S185" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="T185" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="V185" t="n">
+        <v>25</v>
+      </c>
+      <c r="W185" t="n">
         <v>2.48</v>
       </c>
     </row>
@@ -15792,6 +17606,20 @@
         <v>116.2</v>
       </c>
       <c r="S186" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="T186" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="V186" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W186" t="n">
         <v>0.64</v>
       </c>
     </row>
@@ -15864,7 +17692,11 @@
       <c r="R187" t="n">
         <v>22.3</v>
       </c>
-      <c r="S187" t="n">
+      <c r="S187" t="inlineStr"/>
+      <c r="T187" t="inlineStr"/>
+      <c r="U187" t="inlineStr"/>
+      <c r="V187" t="inlineStr"/>
+      <c r="W187" t="n">
         <v>4.23</v>
       </c>
     </row>
@@ -15937,7 +17769,11 @@
       <c r="R188" t="n">
         <v>32.2</v>
       </c>
-      <c r="S188" t="n">
+      <c r="S188" t="inlineStr"/>
+      <c r="T188" t="inlineStr"/>
+      <c r="U188" t="inlineStr"/>
+      <c r="V188" t="inlineStr"/>
+      <c r="W188" t="n">
         <v>2.78</v>
       </c>
     </row>
@@ -16010,7 +17846,11 @@
       <c r="R189" t="n">
         <v>25</v>
       </c>
-      <c r="S189" t="n">
+      <c r="S189" t="inlineStr"/>
+      <c r="T189" t="inlineStr"/>
+      <c r="U189" t="inlineStr"/>
+      <c r="V189" t="inlineStr"/>
+      <c r="W189" t="n">
         <v>5.04</v>
       </c>
     </row>
@@ -16083,7 +17923,11 @@
       <c r="R190" t="n">
         <v>20.4</v>
       </c>
-      <c r="S190" t="n">
+      <c r="S190" t="inlineStr"/>
+      <c r="T190" t="inlineStr"/>
+      <c r="U190" t="inlineStr"/>
+      <c r="V190" t="inlineStr"/>
+      <c r="W190" t="n">
         <v>3.01</v>
       </c>
     </row>
@@ -16156,7 +18000,11 @@
       <c r="R191" t="n">
         <v>13</v>
       </c>
-      <c r="S191" t="n">
+      <c r="S191" t="inlineStr"/>
+      <c r="T191" t="inlineStr"/>
+      <c r="U191" t="inlineStr"/>
+      <c r="V191" t="inlineStr"/>
+      <c r="W191" t="n">
         <v>6.28</v>
       </c>
     </row>
@@ -16226,6 +18074,20 @@
         <v>13</v>
       </c>
       <c r="S192" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="T192" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="V192" t="n">
+        <v>3</v>
+      </c>
+      <c r="W192" t="n">
         <v>4.51</v>
       </c>
     </row>
@@ -16298,7 +18160,11 @@
       <c r="R193" t="n">
         <v>64.40000000000001</v>
       </c>
-      <c r="S193" t="n">
+      <c r="S193" t="inlineStr"/>
+      <c r="T193" t="inlineStr"/>
+      <c r="U193" t="inlineStr"/>
+      <c r="V193" t="inlineStr"/>
+      <c r="W193" t="n">
         <v>1.43</v>
       </c>
     </row>
@@ -16371,7 +18237,11 @@
       <c r="R194" t="n">
         <v>14.6</v>
       </c>
-      <c r="S194" t="n">
+      <c r="S194" t="inlineStr"/>
+      <c r="T194" t="inlineStr"/>
+      <c r="U194" t="inlineStr"/>
+      <c r="V194" t="inlineStr"/>
+      <c r="W194" t="n">
         <v>6.02</v>
       </c>
     </row>
@@ -16444,7 +18314,11 @@
       <c r="R195" t="n">
         <v>6</v>
       </c>
-      <c r="S195" t="n">
+      <c r="S195" t="inlineStr"/>
+      <c r="T195" t="inlineStr"/>
+      <c r="U195" t="inlineStr"/>
+      <c r="V195" t="inlineStr"/>
+      <c r="W195" t="n">
         <v>3.61</v>
       </c>
     </row>
@@ -16517,7 +18391,11 @@
       <c r="R196" t="n">
         <v>23.3</v>
       </c>
-      <c r="S196" t="n">
+      <c r="S196" t="inlineStr"/>
+      <c r="T196" t="inlineStr"/>
+      <c r="U196" t="inlineStr"/>
+      <c r="V196" t="inlineStr"/>
+      <c r="W196" t="n">
         <v>1.71</v>
       </c>
     </row>
@@ -16587,6 +18465,20 @@
         <v>18</v>
       </c>
       <c r="S197" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="T197" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="V197" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W197" t="n">
         <v>3.61</v>
       </c>
     </row>
@@ -16659,7 +18551,11 @@
       <c r="R198" t="n">
         <v>32.9</v>
       </c>
-      <c r="S198" t="n">
+      <c r="S198" t="inlineStr"/>
+      <c r="T198" t="inlineStr"/>
+      <c r="U198" t="inlineStr"/>
+      <c r="V198" t="inlineStr"/>
+      <c r="W198" t="n">
         <v>1.54</v>
       </c>
     </row>
@@ -16732,7 +18628,11 @@
       <c r="R199" t="n">
         <v>55.3</v>
       </c>
-      <c r="S199" t="n">
+      <c r="S199" t="inlineStr"/>
+      <c r="T199" t="inlineStr"/>
+      <c r="U199" t="inlineStr"/>
+      <c r="V199" t="inlineStr"/>
+      <c r="W199" t="n">
         <v>1.59</v>
       </c>
     </row>
@@ -16800,6 +18700,20 @@
         <v>27.2</v>
       </c>
       <c r="S200" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="T200" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="V200" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="W200" t="n">
         <v>3.29</v>
       </c>
     </row>
@@ -16872,7 +18786,11 @@
       <c r="R201" t="n">
         <v>45.8</v>
       </c>
-      <c r="S201" t="n">
+      <c r="S201" t="inlineStr"/>
+      <c r="T201" t="inlineStr"/>
+      <c r="U201" t="inlineStr"/>
+      <c r="V201" t="inlineStr"/>
+      <c r="W201" t="n">
         <v>1.08</v>
       </c>
     </row>
@@ -16941,7 +18859,11 @@
       <c r="R202" t="n">
         <v>253.5</v>
       </c>
-      <c r="S202" t="n">
+      <c r="S202" t="inlineStr"/>
+      <c r="T202" t="inlineStr"/>
+      <c r="U202" t="inlineStr"/>
+      <c r="V202" t="inlineStr"/>
+      <c r="W202" t="n">
         <v>0.59</v>
       </c>
     </row>
@@ -17010,7 +18932,11 @@
       <c r="R203" t="n">
         <v>34.1</v>
       </c>
-      <c r="S203" t="n">
+      <c r="S203" t="inlineStr"/>
+      <c r="T203" t="inlineStr"/>
+      <c r="U203" t="inlineStr"/>
+      <c r="V203" t="inlineStr"/>
+      <c r="W203" t="n">
         <v>1.09</v>
       </c>
     </row>
@@ -17081,7 +19007,11 @@
       <c r="R204" t="n">
         <v>18.8</v>
       </c>
-      <c r="S204" t="n">
+      <c r="S204" t="inlineStr"/>
+      <c r="T204" t="inlineStr"/>
+      <c r="U204" t="inlineStr"/>
+      <c r="V204" t="inlineStr"/>
+      <c r="W204" t="n">
         <v>5.22</v>
       </c>
     </row>
@@ -17154,7 +19084,11 @@
       <c r="R205" t="n">
         <v>68.8</v>
       </c>
-      <c r="S205" t="n">
+      <c r="S205" t="inlineStr"/>
+      <c r="T205" t="inlineStr"/>
+      <c r="U205" t="inlineStr"/>
+      <c r="V205" t="inlineStr"/>
+      <c r="W205" t="n">
         <v>1.31</v>
       </c>
     </row>
@@ -17227,7 +19161,11 @@
       <c r="R206" t="n">
         <v>24.7</v>
       </c>
-      <c r="S206" t="n">
+      <c r="S206" t="inlineStr"/>
+      <c r="T206" t="inlineStr"/>
+      <c r="U206" t="inlineStr"/>
+      <c r="V206" t="inlineStr"/>
+      <c r="W206" t="n">
         <v>5.29</v>
       </c>
     </row>
@@ -17300,7 +19238,11 @@
       <c r="R207" t="n">
         <v>86.5</v>
       </c>
-      <c r="S207" t="n">
+      <c r="S207" t="inlineStr"/>
+      <c r="T207" t="inlineStr"/>
+      <c r="U207" t="inlineStr"/>
+      <c r="V207" t="inlineStr"/>
+      <c r="W207" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -17370,6 +19312,20 @@
         <v>16.9</v>
       </c>
       <c r="S208" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="T208" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="V208" t="n">
+        <v>9</v>
+      </c>
+      <c r="W208" t="n">
         <v>5.03</v>
       </c>
     </row>
@@ -17442,7 +19398,11 @@
       <c r="R209" t="n">
         <v>195.6</v>
       </c>
-      <c r="S209" t="n">
+      <c r="S209" t="inlineStr"/>
+      <c r="T209" t="inlineStr"/>
+      <c r="U209" t="inlineStr"/>
+      <c r="V209" t="inlineStr"/>
+      <c r="W209" t="n">
         <v>0.22</v>
       </c>
     </row>
@@ -17513,7 +19473,11 @@
       <c r="R210" t="n">
         <v>194.5</v>
       </c>
-      <c r="S210" t="n">
+      <c r="S210" t="inlineStr"/>
+      <c r="T210" t="inlineStr"/>
+      <c r="U210" t="inlineStr"/>
+      <c r="V210" t="inlineStr"/>
+      <c r="W210" t="n">
         <v>0.5600000000000001</v>
       </c>
     </row>
@@ -17586,7 +19550,11 @@
       <c r="R211" t="n">
         <v>26.9</v>
       </c>
-      <c r="S211" t="n">
+      <c r="S211" t="inlineStr"/>
+      <c r="T211" t="inlineStr"/>
+      <c r="U211" t="inlineStr"/>
+      <c r="V211" t="inlineStr"/>
+      <c r="W211" t="n">
         <v>3.63</v>
       </c>
     </row>
@@ -17655,7 +19623,11 @@
       <c r="R212" t="n">
         <v>121.1</v>
       </c>
-      <c r="S212" t="n">
+      <c r="S212" t="inlineStr"/>
+      <c r="T212" t="inlineStr"/>
+      <c r="U212" t="inlineStr"/>
+      <c r="V212" t="inlineStr"/>
+      <c r="W212" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17724,7 +19696,11 @@
       <c r="R213" t="n">
         <v>251.2</v>
       </c>
-      <c r="S213" t="n">
+      <c r="S213" t="inlineStr"/>
+      <c r="T213" t="inlineStr"/>
+      <c r="U213" t="inlineStr"/>
+      <c r="V213" t="inlineStr"/>
+      <c r="W213" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17797,7 +19773,11 @@
       <c r="R214" t="n">
         <v>85.8</v>
       </c>
-      <c r="S214" t="n">
+      <c r="S214" t="inlineStr"/>
+      <c r="T214" t="inlineStr"/>
+      <c r="U214" t="inlineStr"/>
+      <c r="V214" t="inlineStr"/>
+      <c r="W214" t="n">
         <v>1.78</v>
       </c>
     </row>
@@ -17870,7 +19850,11 @@
       <c r="R215" t="n">
         <v>3883.3</v>
       </c>
-      <c r="S215" t="n">
+      <c r="S215" t="inlineStr"/>
+      <c r="T215" t="inlineStr"/>
+      <c r="U215" t="inlineStr"/>
+      <c r="V215" t="inlineStr"/>
+      <c r="W215" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17943,7 +19927,11 @@
       <c r="R216" t="n">
         <v>16.7</v>
       </c>
-      <c r="S216" t="n">
+      <c r="S216" t="inlineStr"/>
+      <c r="T216" t="inlineStr"/>
+      <c r="U216" t="inlineStr"/>
+      <c r="V216" t="inlineStr"/>
+      <c r="W216" t="n">
         <v>4.06</v>
       </c>
     </row>
@@ -18016,7 +20004,11 @@
       <c r="R217" t="n">
         <v>19</v>
       </c>
-      <c r="S217" t="n">
+      <c r="S217" t="inlineStr"/>
+      <c r="T217" t="inlineStr"/>
+      <c r="U217" t="inlineStr"/>
+      <c r="V217" t="inlineStr"/>
+      <c r="W217" t="n">
         <v>5.06</v>
       </c>
     </row>
@@ -18089,7 +20081,11 @@
       <c r="R218" t="n">
         <v>68.7</v>
       </c>
-      <c r="S218" t="n">
+      <c r="S218" t="inlineStr"/>
+      <c r="T218" t="inlineStr"/>
+      <c r="U218" t="inlineStr"/>
+      <c r="V218" t="inlineStr"/>
+      <c r="W218" t="n">
         <v>0.6899999999999999</v>
       </c>
     </row>
@@ -18162,7 +20158,11 @@
       <c r="R219" t="n">
         <v>27</v>
       </c>
-      <c r="S219" t="n">
+      <c r="S219" t="inlineStr"/>
+      <c r="T219" t="inlineStr"/>
+      <c r="U219" t="inlineStr"/>
+      <c r="V219" t="inlineStr"/>
+      <c r="W219" t="n">
         <v>3.46</v>
       </c>
     </row>
@@ -18232,6 +20232,20 @@
         <v>31.4</v>
       </c>
       <c r="S220" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="T220" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="V220" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="W220" t="n">
         <v>1.57</v>
       </c>
     </row>
@@ -18301,6 +20315,20 @@
         <v>36.9</v>
       </c>
       <c r="S221" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="T221" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="V221" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W221" t="n">
         <v>1.73</v>
       </c>
     </row>
@@ -18373,7 +20401,11 @@
       <c r="R222" t="n">
         <v>41.4</v>
       </c>
-      <c r="S222" t="n">
+      <c r="S222" t="inlineStr"/>
+      <c r="T222" t="inlineStr"/>
+      <c r="U222" t="inlineStr"/>
+      <c r="V222" t="inlineStr"/>
+      <c r="W222" t="n">
         <v>1.18</v>
       </c>
     </row>
@@ -18442,7 +20474,11 @@
       <c r="R223" t="n">
         <v>7.7</v>
       </c>
-      <c r="S223" t="n">
+      <c r="S223" t="inlineStr"/>
+      <c r="T223" t="inlineStr"/>
+      <c r="U223" t="inlineStr"/>
+      <c r="V223" t="inlineStr"/>
+      <c r="W223" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18515,7 +20551,11 @@
       <c r="R224" t="n">
         <v>127.5</v>
       </c>
-      <c r="S224" t="n">
+      <c r="S224" t="inlineStr"/>
+      <c r="T224" t="inlineStr"/>
+      <c r="U224" t="inlineStr"/>
+      <c r="V224" t="inlineStr"/>
+      <c r="W224" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -18584,7 +20624,11 @@
       <c r="R225" t="n">
         <v>65.8</v>
       </c>
-      <c r="S225" t="n">
+      <c r="S225" t="inlineStr"/>
+      <c r="T225" t="inlineStr"/>
+      <c r="U225" t="inlineStr"/>
+      <c r="V225" t="inlineStr"/>
+      <c r="W225" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18653,7 +20697,11 @@
       <c r="R226" t="n">
         <v>11.6</v>
       </c>
-      <c r="S226" t="n">
+      <c r="S226" t="inlineStr"/>
+      <c r="T226" t="inlineStr"/>
+      <c r="U226" t="inlineStr"/>
+      <c r="V226" t="inlineStr"/>
+      <c r="W226" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18726,7 +20774,11 @@
       <c r="R227" t="n">
         <v>5637.5</v>
       </c>
-      <c r="S227" t="n">
+      <c r="S227" t="inlineStr"/>
+      <c r="T227" t="inlineStr"/>
+      <c r="U227" t="inlineStr"/>
+      <c r="V227" t="inlineStr"/>
+      <c r="W227" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18799,7 +20851,11 @@
       <c r="R228" t="n">
         <v>2019.2</v>
       </c>
-      <c r="S228" t="n">
+      <c r="S228" t="inlineStr"/>
+      <c r="T228" t="inlineStr"/>
+      <c r="U228" t="inlineStr"/>
+      <c r="V228" t="inlineStr"/>
+      <c r="W228" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -18868,7 +20924,11 @@
       <c r="R229" t="n">
         <v>2725</v>
       </c>
-      <c r="S229" t="n">
+      <c r="S229" t="inlineStr"/>
+      <c r="T229" t="inlineStr"/>
+      <c r="U229" t="inlineStr"/>
+      <c r="V229" t="inlineStr"/>
+      <c r="W229" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18935,7 +20995,11 @@
         <v>3</v>
       </c>
       <c r="R230" t="inlineStr"/>
-      <c r="S230" t="n">
+      <c r="S230" t="inlineStr"/>
+      <c r="T230" t="inlineStr"/>
+      <c r="U230" t="inlineStr"/>
+      <c r="V230" t="inlineStr"/>
+      <c r="W230" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18989,6 +21053,10 @@
       <c r="Q231" t="inlineStr"/>
       <c r="R231" t="inlineStr"/>
       <c r="S231" t="inlineStr"/>
+      <c r="T231" t="inlineStr"/>
+      <c r="U231" t="inlineStr"/>
+      <c r="V231" t="inlineStr"/>
+      <c r="W231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -19040,6 +21108,10 @@
       <c r="Q232" t="inlineStr"/>
       <c r="R232" t="inlineStr"/>
       <c r="S232" t="inlineStr"/>
+      <c r="T232" t="inlineStr"/>
+      <c r="U232" t="inlineStr"/>
+      <c r="V232" t="inlineStr"/>
+      <c r="W232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -19101,6 +21173,10 @@
         <v>12.7</v>
       </c>
       <c r="S233" t="inlineStr"/>
+      <c r="T233" t="inlineStr"/>
+      <c r="U233" t="inlineStr"/>
+      <c r="V233" t="inlineStr"/>
+      <c r="W233" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19117,67 +21193,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>EPS加速</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>5年均ROE</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ROE回升</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>PBR便宜</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
@@ -19198,67 +21274,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>EPS加速</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>5年均ROE</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ROE回升</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>PBR便宜</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>

--- a/data/台股_拐點掃描.xlsx
+++ b/data/台股_拐點掃描.xlsx
@@ -708,7 +708,11 @@
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
         <v>5.24</v>
@@ -876,7 +880,11 @@
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
         <v>2.81</v>
@@ -1566,7 +1574,11 @@
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="n">
         <v>6.66</v>
@@ -1821,7 +1833,11 @@
       </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="n">
         <v>5.13</v>
@@ -1987,7 +2003,11 @@
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="n">
         <v>4.12</v>
@@ -2068,7 +2088,11 @@
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="n">
         <v>5.71</v>
@@ -2584,7 +2608,11 @@
       </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="n">
         <v>5.91</v>
@@ -3217,7 +3245,11 @@
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
         <v>0.84</v>
@@ -3460,7 +3492,11 @@
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
         <v>3.92</v>
@@ -3703,7 +3739,11 @@
       </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
         <v>0.17</v>
@@ -3780,7 +3820,11 @@
       </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="n">
         <v>0.23</v>
@@ -3857,7 +3901,11 @@
       </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="n">
         <v>1.05</v>
@@ -3934,7 +3982,11 @@
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="n">
         <v>2.57</v>
@@ -4094,7 +4146,11 @@
       </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="n">
         <v>0.4</v>
@@ -4258,7 +4314,11 @@
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="n">
         <v>0.9</v>
@@ -4335,7 +4395,11 @@
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="n">
         <v>2.79</v>
@@ -4416,7 +4480,11 @@
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="n">
         <v>2.81</v>
@@ -4744,7 +4812,11 @@
       </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="n">
         <v>0.68</v>
@@ -4987,7 +5059,11 @@
       </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="n">
         <v>6.76</v>
@@ -5064,7 +5140,11 @@
       </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="n">
         <v>2.24</v>
@@ -5228,7 +5308,11 @@
       </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="n">
         <v>2.15</v>
@@ -5305,7 +5389,11 @@
       </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="n">
         <v>1.23</v>
@@ -5380,7 +5468,11 @@
       </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="n">
         <v>6.54</v>
@@ -5544,7 +5636,11 @@
       </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="n">
         <v>0.87</v>
@@ -5787,7 +5883,11 @@
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="n">
         <v>2</v>
@@ -5864,7 +5964,11 @@
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="n">
         <v>4.99</v>
@@ -6115,7 +6219,11 @@
       </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="n">
         <v>0.7</v>
@@ -6445,7 +6553,11 @@
       </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="n">
         <v>0.64</v>
@@ -6858,7 +6970,11 @@
       </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V49" t="inlineStr"/>
       <c r="W49" t="n">
         <v>6.66</v>
@@ -7111,7 +7227,11 @@
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V52" t="inlineStr"/>
       <c r="W52" t="n">
         <v>5.24</v>
@@ -7188,7 +7308,11 @@
       </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V53" t="inlineStr"/>
       <c r="W53" t="n">
         <v>3.48</v>
@@ -7265,7 +7389,11 @@
       </c>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V54" t="inlineStr"/>
       <c r="W54" t="n">
         <v>0.65</v>
@@ -7508,7 +7636,11 @@
       </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="n">
         <v>2.82</v>
@@ -7668,7 +7800,11 @@
       </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr"/>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V59" t="inlineStr"/>
       <c r="W59" t="n">
         <v>2.09</v>
@@ -7826,7 +7962,11 @@
       </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V61" t="inlineStr"/>
       <c r="W61" t="n">
         <v>1.61</v>
@@ -7903,7 +8043,11 @@
       </c>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V62" t="inlineStr"/>
       <c r="W62" t="n">
         <v>4.43</v>
@@ -7978,7 +8122,11 @@
       </c>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V63" t="inlineStr"/>
       <c r="W63" t="n">
         <v>0.39</v>
@@ -8051,7 +8199,11 @@
       </c>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V64" t="inlineStr"/>
       <c r="W64" t="n">
         <v>0</v>
@@ -8128,7 +8280,11 @@
       </c>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V65" t="inlineStr"/>
       <c r="W65" t="n">
         <v>0.23</v>
@@ -8205,7 +8361,11 @@
       </c>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V66" t="inlineStr"/>
       <c r="W66" t="n">
         <v>2.24</v>
@@ -8270,7 +8430,11 @@
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr"/>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>⏸ 缺收盤/EPS</t>
+        </is>
+      </c>
       <c r="V67" t="inlineStr"/>
       <c r="W67" t="n">
         <v>0</v>
@@ -8343,7 +8507,11 @@
       </c>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
-      <c r="U68" t="inlineStr"/>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V68" t="inlineStr"/>
       <c r="W68" t="n">
         <v>0</v>
@@ -8418,7 +8586,11 @@
       </c>
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
-      <c r="U69" t="inlineStr"/>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V69" t="inlineStr"/>
       <c r="W69" t="n">
         <v>0.51</v>
@@ -8491,7 +8663,11 @@
       </c>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
-      <c r="U70" t="inlineStr"/>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V70" t="inlineStr"/>
       <c r="W70" t="n">
         <v>0</v>
@@ -8564,7 +8740,11 @@
       </c>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
-      <c r="U71" t="inlineStr"/>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V71" t="inlineStr"/>
       <c r="W71" t="n">
         <v>0</v>
@@ -8641,7 +8821,11 @@
       </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
-      <c r="U72" t="inlineStr"/>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V72" t="inlineStr"/>
       <c r="W72" t="n">
         <v>2.03</v>
@@ -8718,7 +8902,11 @@
       </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
-      <c r="U73" t="inlineStr"/>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V73" t="inlineStr"/>
       <c r="W73" t="n">
         <v>0.27</v>
@@ -8878,7 +9066,11 @@
       </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
-      <c r="U75" t="inlineStr"/>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V75" t="inlineStr"/>
       <c r="W75" t="n">
         <v>3.38</v>
@@ -8955,7 +9147,11 @@
       </c>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
-      <c r="U76" t="inlineStr"/>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V76" t="inlineStr"/>
       <c r="W76" t="n">
         <v>3.47</v>
@@ -9028,7 +9224,11 @@
       </c>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
-      <c r="U77" t="inlineStr"/>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V77" t="inlineStr"/>
       <c r="W77" t="n">
         <v>3.51</v>
@@ -9105,7 +9305,11 @@
       </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
-      <c r="U78" t="inlineStr"/>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V78" t="inlineStr"/>
       <c r="W78" t="n">
         <v>6.03</v>
@@ -9180,7 +9384,11 @@
       </c>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
-      <c r="U79" t="inlineStr"/>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V79" t="inlineStr"/>
       <c r="W79" t="n">
         <v>2.94</v>
@@ -9427,7 +9635,11 @@
       </c>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr"/>
-      <c r="U82" t="inlineStr"/>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V82" t="inlineStr"/>
       <c r="W82" t="n">
         <v>3.38</v>
@@ -9670,7 +9882,11 @@
       </c>
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr"/>
-      <c r="U85" t="inlineStr"/>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" t="n">
         <v>0.87</v>
@@ -9747,7 +9963,11 @@
       </c>
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="inlineStr"/>
-      <c r="U86" t="inlineStr"/>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V86" t="inlineStr"/>
       <c r="W86" t="n">
         <v>4.54</v>
@@ -9824,7 +10044,11 @@
       </c>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="inlineStr"/>
-      <c r="U87" t="inlineStr"/>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V87" t="inlineStr"/>
       <c r="W87" t="n">
         <v>0.42</v>
@@ -10407,7 +10631,11 @@
       </c>
       <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr"/>
-      <c r="U94" t="inlineStr"/>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V94" t="inlineStr"/>
       <c r="W94" t="n">
         <v>5.91</v>
@@ -10478,18 +10706,14 @@
       <c r="R95" t="n">
         <v>21.5</v>
       </c>
-      <c r="S95" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="S95" t="inlineStr"/>
       <c r="T95" t="inlineStr"/>
       <c r="U95" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
-        </is>
-      </c>
-      <c r="V95" t="n">
-        <v>-2.7</v>
-      </c>
+          <t>⏸ 成長為負(-3%)</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr"/>
       <c r="W95" t="n">
         <v>3.34</v>
       </c>
@@ -10565,7 +10789,11 @@
       </c>
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr"/>
-      <c r="U96" t="inlineStr"/>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V96" t="inlineStr"/>
       <c r="W96" t="n">
         <v>0.53</v>
@@ -10642,7 +10870,11 @@
       </c>
       <c r="S97" t="inlineStr"/>
       <c r="T97" t="inlineStr"/>
-      <c r="U97" t="inlineStr"/>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V97" t="inlineStr"/>
       <c r="W97" t="n">
         <v>1.48</v>
@@ -10719,7 +10951,11 @@
       </c>
       <c r="S98" t="inlineStr"/>
       <c r="T98" t="inlineStr"/>
-      <c r="U98" t="inlineStr"/>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V98" t="inlineStr"/>
       <c r="W98" t="n">
         <v>1.32</v>
@@ -10796,7 +11032,11 @@
       </c>
       <c r="S99" t="inlineStr"/>
       <c r="T99" t="inlineStr"/>
-      <c r="U99" t="inlineStr"/>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V99" t="inlineStr"/>
       <c r="W99" t="n">
         <v>2.07</v>
@@ -11039,7 +11279,11 @@
       </c>
       <c r="S102" t="inlineStr"/>
       <c r="T102" t="inlineStr"/>
-      <c r="U102" t="inlineStr"/>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V102" t="inlineStr"/>
       <c r="W102" t="n">
         <v>3.65</v>
@@ -11359,7 +11603,11 @@
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr"/>
       <c r="T106" t="inlineStr"/>
-      <c r="U106" t="inlineStr"/>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>⏸ 缺收盤/EPS</t>
+        </is>
+      </c>
       <c r="V106" t="inlineStr"/>
       <c r="W106" t="inlineStr"/>
     </row>
@@ -11430,7 +11678,11 @@
       </c>
       <c r="S107" t="inlineStr"/>
       <c r="T107" t="inlineStr"/>
-      <c r="U107" t="inlineStr"/>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V107" t="inlineStr"/>
       <c r="W107" t="n">
         <v>0.25</v>
@@ -11503,7 +11755,11 @@
       </c>
       <c r="S108" t="inlineStr"/>
       <c r="T108" t="inlineStr"/>
-      <c r="U108" t="inlineStr"/>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V108" t="inlineStr"/>
       <c r="W108" t="n">
         <v>0</v>
@@ -11576,7 +11832,11 @@
       </c>
       <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr"/>
-      <c r="U109" t="inlineStr"/>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V109" t="inlineStr"/>
       <c r="W109" t="n">
         <v>0</v>
@@ -11649,7 +11909,11 @@
       </c>
       <c r="S110" t="inlineStr"/>
       <c r="T110" t="inlineStr"/>
-      <c r="U110" t="inlineStr"/>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V110" t="inlineStr"/>
       <c r="W110" t="n">
         <v>0</v>
@@ -11720,7 +11984,11 @@
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr"/>
       <c r="T111" t="inlineStr"/>
-      <c r="U111" t="inlineStr"/>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V111" t="inlineStr"/>
       <c r="W111" t="n">
         <v>0</v>
@@ -11876,7 +12144,11 @@
       </c>
       <c r="S113" t="inlineStr"/>
       <c r="T113" t="inlineStr"/>
-      <c r="U113" t="inlineStr"/>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V113" t="inlineStr"/>
       <c r="W113" t="n">
         <v>0</v>
@@ -11951,7 +12223,11 @@
       </c>
       <c r="S114" t="inlineStr"/>
       <c r="T114" t="inlineStr"/>
-      <c r="U114" t="inlineStr"/>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V114" t="inlineStr"/>
       <c r="W114" t="n">
         <v>1.52</v>
@@ -12111,7 +12387,11 @@
       </c>
       <c r="S116" t="inlineStr"/>
       <c r="T116" t="inlineStr"/>
-      <c r="U116" t="inlineStr"/>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V116" t="inlineStr"/>
       <c r="W116" t="n">
         <v>1.32</v>
@@ -12188,7 +12468,11 @@
       </c>
       <c r="S117" t="inlineStr"/>
       <c r="T117" t="inlineStr"/>
-      <c r="U117" t="inlineStr"/>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V117" t="inlineStr"/>
       <c r="W117" t="n">
         <v>0.6</v>
@@ -12265,7 +12549,11 @@
       </c>
       <c r="S118" t="inlineStr"/>
       <c r="T118" t="inlineStr"/>
-      <c r="U118" t="inlineStr"/>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V118" t="inlineStr"/>
       <c r="W118" t="n">
         <v>2.86</v>
@@ -12340,7 +12628,11 @@
       </c>
       <c r="S119" t="inlineStr"/>
       <c r="T119" t="inlineStr"/>
-      <c r="U119" t="inlineStr"/>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V119" t="inlineStr"/>
       <c r="W119" t="n">
         <v>0.7</v>
@@ -12413,7 +12705,11 @@
       </c>
       <c r="S120" t="inlineStr"/>
       <c r="T120" t="inlineStr"/>
-      <c r="U120" t="inlineStr"/>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V120" t="inlineStr"/>
       <c r="W120" t="n">
         <v>0.25</v>
@@ -12490,7 +12786,11 @@
       </c>
       <c r="S121" t="inlineStr"/>
       <c r="T121" t="inlineStr"/>
-      <c r="U121" t="inlineStr"/>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V121" t="inlineStr"/>
       <c r="W121" t="n">
         <v>0.58</v>
@@ -12567,7 +12867,11 @@
       </c>
       <c r="S122" t="inlineStr"/>
       <c r="T122" t="inlineStr"/>
-      <c r="U122" t="inlineStr"/>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V122" t="inlineStr"/>
       <c r="W122" t="n">
         <v>1.09</v>
@@ -12640,7 +12944,11 @@
       </c>
       <c r="S123" t="inlineStr"/>
       <c r="T123" t="inlineStr"/>
-      <c r="U123" t="inlineStr"/>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V123" t="inlineStr"/>
       <c r="W123" t="n">
         <v>0</v>
@@ -12721,7 +13029,11 @@
       </c>
       <c r="S124" t="inlineStr"/>
       <c r="T124" t="inlineStr"/>
-      <c r="U124" t="inlineStr"/>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V124" t="inlineStr"/>
       <c r="W124" t="n">
         <v>5.71</v>
@@ -12798,7 +13110,11 @@
       </c>
       <c r="S125" t="inlineStr"/>
       <c r="T125" t="inlineStr"/>
-      <c r="U125" t="inlineStr"/>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V125" t="inlineStr"/>
       <c r="W125" t="n">
         <v>0.36</v>
@@ -12958,7 +13274,11 @@
       </c>
       <c r="S127" t="inlineStr"/>
       <c r="T127" t="inlineStr"/>
-      <c r="U127" t="inlineStr"/>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V127" t="inlineStr"/>
       <c r="W127" t="n">
         <v>0.22</v>
@@ -13035,7 +13355,11 @@
       </c>
       <c r="S128" t="inlineStr"/>
       <c r="T128" t="inlineStr"/>
-      <c r="U128" t="inlineStr"/>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V128" t="inlineStr"/>
       <c r="W128" t="n">
         <v>0.2</v>
@@ -13112,7 +13436,11 @@
       </c>
       <c r="S129" t="inlineStr"/>
       <c r="T129" t="inlineStr"/>
-      <c r="U129" t="inlineStr"/>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V129" t="inlineStr"/>
       <c r="W129" t="n">
         <v>5.04</v>
@@ -13270,7 +13598,11 @@
       </c>
       <c r="S131" t="inlineStr"/>
       <c r="T131" t="inlineStr"/>
-      <c r="U131" t="inlineStr"/>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V131" t="inlineStr"/>
       <c r="W131" t="n">
         <v>0.57</v>
@@ -13347,7 +13679,11 @@
       </c>
       <c r="S132" t="inlineStr"/>
       <c r="T132" t="inlineStr"/>
-      <c r="U132" t="inlineStr"/>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V132" t="inlineStr"/>
       <c r="W132" t="n">
         <v>3.23</v>
@@ -13424,7 +13760,11 @@
       </c>
       <c r="S133" t="inlineStr"/>
       <c r="T133" t="inlineStr"/>
-      <c r="U133" t="inlineStr"/>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V133" t="inlineStr"/>
       <c r="W133" t="n">
         <v>3.31</v>
@@ -13584,7 +13924,11 @@
       </c>
       <c r="S135" t="inlineStr"/>
       <c r="T135" t="inlineStr"/>
-      <c r="U135" t="inlineStr"/>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V135" t="inlineStr"/>
       <c r="W135" t="n">
         <v>0.5600000000000001</v>
@@ -13655,18 +13999,14 @@
       <c r="R136" t="n">
         <v>13.7</v>
       </c>
-      <c r="S136" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="S136" t="inlineStr"/>
       <c r="T136" t="inlineStr"/>
       <c r="U136" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
-        </is>
-      </c>
-      <c r="V136" t="n">
-        <v>-6.2</v>
-      </c>
+          <t>⏸ 成長為負(-6%)</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr"/>
       <c r="W136" t="n">
         <v>5.08</v>
       </c>
@@ -13742,7 +14082,11 @@
       </c>
       <c r="S137" t="inlineStr"/>
       <c r="T137" t="inlineStr"/>
-      <c r="U137" t="inlineStr"/>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V137" t="inlineStr"/>
       <c r="W137" t="n">
         <v>0.98</v>
@@ -13900,18 +14244,14 @@
       <c r="R139" t="n">
         <v>24.6</v>
       </c>
-      <c r="S139" t="n">
-        <v>25.4</v>
-      </c>
+      <c r="S139" t="inlineStr"/>
       <c r="T139" t="inlineStr"/>
       <c r="U139" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
-        </is>
-      </c>
-      <c r="V139" t="n">
-        <v>-2.9</v>
-      </c>
+          <t>⏸ 成長為負(-3%)</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr"/>
       <c r="W139" t="n">
         <v>2.24</v>
       </c>
@@ -13981,18 +14321,14 @@
       <c r="R140" t="n">
         <v>38.6</v>
       </c>
-      <c r="S140" t="n">
-        <v>40.2</v>
-      </c>
+      <c r="S140" t="inlineStr"/>
       <c r="T140" t="inlineStr"/>
       <c r="U140" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
-        </is>
-      </c>
-      <c r="V140" t="n">
-        <v>-4</v>
-      </c>
+          <t>⏸ 成長為負(-4%)</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr"/>
       <c r="W140" t="n">
         <v>2.24</v>
       </c>
@@ -14068,7 +14404,11 @@
       </c>
       <c r="S141" t="inlineStr"/>
       <c r="T141" t="inlineStr"/>
-      <c r="U141" t="inlineStr"/>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V141" t="inlineStr"/>
       <c r="W141" t="n">
         <v>2.41</v>
@@ -14645,18 +14985,14 @@
       <c r="R148" t="n">
         <v>43.6</v>
       </c>
-      <c r="S148" t="n">
-        <v>50.4</v>
-      </c>
+      <c r="S148" t="inlineStr"/>
       <c r="T148" t="inlineStr"/>
       <c r="U148" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
-        </is>
-      </c>
-      <c r="V148" t="n">
-        <v>-13.6</v>
-      </c>
+          <t>⏸ 成長為負(-14%)</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr"/>
       <c r="W148" t="n">
         <v>1.23</v>
       </c>
@@ -14732,7 +15068,11 @@
       </c>
       <c r="S149" t="inlineStr"/>
       <c r="T149" t="inlineStr"/>
-      <c r="U149" t="inlineStr"/>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V149" t="inlineStr"/>
       <c r="W149" t="n">
         <v>4.45</v>
@@ -14896,7 +15236,11 @@
       </c>
       <c r="S151" t="inlineStr"/>
       <c r="T151" t="inlineStr"/>
-      <c r="U151" t="inlineStr"/>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V151" t="inlineStr"/>
       <c r="W151" t="n">
         <v>3.45</v>
@@ -14973,7 +15317,11 @@
       </c>
       <c r="S152" t="inlineStr"/>
       <c r="T152" t="inlineStr"/>
-      <c r="U152" t="inlineStr"/>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V152" t="inlineStr"/>
       <c r="W152" t="n">
         <v>0.18</v>
@@ -15137,7 +15485,11 @@
       </c>
       <c r="S154" t="inlineStr"/>
       <c r="T154" t="inlineStr"/>
-      <c r="U154" t="inlineStr"/>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V154" t="inlineStr"/>
       <c r="W154" t="n">
         <v>1.56</v>
@@ -15218,7 +15570,11 @@
       </c>
       <c r="S155" t="inlineStr"/>
       <c r="T155" t="inlineStr"/>
-      <c r="U155" t="inlineStr"/>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V155" t="inlineStr"/>
       <c r="W155" t="n">
         <v>5.13</v>
@@ -15295,7 +15651,11 @@
       </c>
       <c r="S156" t="inlineStr"/>
       <c r="T156" t="inlineStr"/>
-      <c r="U156" t="inlineStr"/>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V156" t="inlineStr"/>
       <c r="W156" t="n">
         <v>3.92</v>
@@ -15372,7 +15732,11 @@
       </c>
       <c r="S157" t="inlineStr"/>
       <c r="T157" t="inlineStr"/>
-      <c r="U157" t="inlineStr"/>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V157" t="inlineStr"/>
       <c r="W157" t="n">
         <v>1.08</v>
@@ -15532,7 +15896,11 @@
       </c>
       <c r="S159" t="inlineStr"/>
       <c r="T159" t="inlineStr"/>
-      <c r="U159" t="inlineStr"/>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V159" t="inlineStr"/>
       <c r="W159" t="n">
         <v>3.82</v>
@@ -15603,18 +15971,14 @@
       <c r="R160" t="n">
         <v>34</v>
       </c>
-      <c r="S160" t="n">
-        <v>36.4</v>
-      </c>
+      <c r="S160" t="inlineStr"/>
       <c r="T160" t="inlineStr"/>
       <c r="U160" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
-        </is>
-      </c>
-      <c r="V160" t="n">
-        <v>-6.6</v>
-      </c>
+          <t>⏸ 成長為負(-7%)</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr"/>
       <c r="W160" t="n">
         <v>2.12</v>
       </c>
@@ -15690,7 +16054,11 @@
       </c>
       <c r="S161" t="inlineStr"/>
       <c r="T161" t="inlineStr"/>
-      <c r="U161" t="inlineStr"/>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V161" t="inlineStr"/>
       <c r="W161" t="n">
         <v>5.33</v>
@@ -15769,7 +16137,11 @@
       </c>
       <c r="S162" t="inlineStr"/>
       <c r="T162" t="inlineStr"/>
-      <c r="U162" t="inlineStr"/>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V162" t="inlineStr"/>
       <c r="W162" t="n">
         <v>4.12</v>
@@ -15846,7 +16218,11 @@
       </c>
       <c r="S163" t="inlineStr"/>
       <c r="T163" t="inlineStr"/>
-      <c r="U163" t="inlineStr"/>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V163" t="inlineStr"/>
       <c r="W163" t="n">
         <v>1.51</v>
@@ -16008,7 +16384,11 @@
       </c>
       <c r="S165" t="inlineStr"/>
       <c r="T165" t="inlineStr"/>
-      <c r="U165" t="inlineStr"/>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V165" t="inlineStr"/>
       <c r="W165" t="n">
         <v>2.94</v>
@@ -16085,7 +16465,11 @@
       </c>
       <c r="S166" t="inlineStr"/>
       <c r="T166" t="inlineStr"/>
-      <c r="U166" t="inlineStr"/>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V166" t="inlineStr"/>
       <c r="W166" t="n">
         <v>2.29</v>
@@ -16162,7 +16546,11 @@
       </c>
       <c r="S167" t="inlineStr"/>
       <c r="T167" t="inlineStr"/>
-      <c r="U167" t="inlineStr"/>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V167" t="inlineStr"/>
       <c r="W167" t="n">
         <v>0.75</v>
@@ -16239,7 +16627,11 @@
       </c>
       <c r="S168" t="inlineStr"/>
       <c r="T168" t="inlineStr"/>
-      <c r="U168" t="inlineStr"/>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V168" t="inlineStr"/>
       <c r="W168" t="n">
         <v>1.73</v>
@@ -16403,7 +16795,11 @@
       </c>
       <c r="S170" t="inlineStr"/>
       <c r="T170" t="inlineStr"/>
-      <c r="U170" t="inlineStr"/>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V170" t="inlineStr"/>
       <c r="W170" t="n">
         <v>0.37</v>
@@ -16480,7 +16876,11 @@
       </c>
       <c r="S171" t="inlineStr"/>
       <c r="T171" t="inlineStr"/>
-      <c r="U171" t="inlineStr"/>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V171" t="inlineStr"/>
       <c r="W171" t="n">
         <v>0.59</v>
@@ -16547,7 +16947,11 @@
       </c>
       <c r="S172" t="inlineStr"/>
       <c r="T172" t="inlineStr"/>
-      <c r="U172" t="inlineStr"/>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>⏸ 無成長率</t>
+        </is>
+      </c>
       <c r="V172" t="inlineStr"/>
       <c r="W172" t="n">
         <v>0.8</v>
@@ -16622,7 +17026,11 @@
       </c>
       <c r="S173" t="inlineStr"/>
       <c r="T173" t="inlineStr"/>
-      <c r="U173" t="inlineStr"/>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V173" t="inlineStr"/>
       <c r="W173" t="n">
         <v>1.18</v>
@@ -16699,7 +17107,11 @@
       </c>
       <c r="S174" t="inlineStr"/>
       <c r="T174" t="inlineStr"/>
-      <c r="U174" t="inlineStr"/>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V174" t="inlineStr"/>
       <c r="W174" t="n">
         <v>5.33</v>
@@ -16772,7 +17184,11 @@
       </c>
       <c r="S175" t="inlineStr"/>
       <c r="T175" t="inlineStr"/>
-      <c r="U175" t="inlineStr"/>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V175" t="inlineStr"/>
       <c r="W175" t="n">
         <v>0</v>
@@ -16849,7 +17265,11 @@
       </c>
       <c r="S176" t="inlineStr"/>
       <c r="T176" t="inlineStr"/>
-      <c r="U176" t="inlineStr"/>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V176" t="inlineStr"/>
       <c r="W176" t="n">
         <v>0.26</v>
@@ -16924,7 +17344,11 @@
       </c>
       <c r="S177" t="inlineStr"/>
       <c r="T177" t="inlineStr"/>
-      <c r="U177" t="inlineStr"/>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V177" t="inlineStr"/>
       <c r="W177" t="n">
         <v>1.57</v>
@@ -16989,7 +17413,11 @@
       </c>
       <c r="S178" t="inlineStr"/>
       <c r="T178" t="inlineStr"/>
-      <c r="U178" t="inlineStr"/>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>⏸ 無成長率</t>
+        </is>
+      </c>
       <c r="V178" t="inlineStr"/>
       <c r="W178" t="n">
         <v>0.22</v>
@@ -17060,7 +17488,11 @@
       <c r="R179" t="inlineStr"/>
       <c r="S179" t="inlineStr"/>
       <c r="T179" t="inlineStr"/>
-      <c r="U179" t="inlineStr"/>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V179" t="inlineStr"/>
       <c r="W179" t="n">
         <v>0</v>
@@ -17220,7 +17652,11 @@
       </c>
       <c r="S181" t="inlineStr"/>
       <c r="T181" t="inlineStr"/>
-      <c r="U181" t="inlineStr"/>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V181" t="inlineStr"/>
       <c r="W181" t="n">
         <v>5.03</v>
@@ -17297,7 +17733,11 @@
       </c>
       <c r="S182" t="inlineStr"/>
       <c r="T182" t="inlineStr"/>
-      <c r="U182" t="inlineStr"/>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V182" t="inlineStr"/>
       <c r="W182" t="n">
         <v>2.72</v>
@@ -17374,7 +17814,11 @@
       </c>
       <c r="S183" t="inlineStr"/>
       <c r="T183" t="inlineStr"/>
-      <c r="U183" t="inlineStr"/>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V183" t="inlineStr"/>
       <c r="W183" t="n">
         <v>4.15</v>
@@ -17451,7 +17895,11 @@
       </c>
       <c r="S184" t="inlineStr"/>
       <c r="T184" t="inlineStr"/>
-      <c r="U184" t="inlineStr"/>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V184" t="inlineStr"/>
       <c r="W184" t="n">
         <v>3.88</v>
@@ -17694,7 +18142,11 @@
       </c>
       <c r="S187" t="inlineStr"/>
       <c r="T187" t="inlineStr"/>
-      <c r="U187" t="inlineStr"/>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V187" t="inlineStr"/>
       <c r="W187" t="n">
         <v>4.23</v>
@@ -17771,7 +18223,11 @@
       </c>
       <c r="S188" t="inlineStr"/>
       <c r="T188" t="inlineStr"/>
-      <c r="U188" t="inlineStr"/>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V188" t="inlineStr"/>
       <c r="W188" t="n">
         <v>2.78</v>
@@ -17848,7 +18304,11 @@
       </c>
       <c r="S189" t="inlineStr"/>
       <c r="T189" t="inlineStr"/>
-      <c r="U189" t="inlineStr"/>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V189" t="inlineStr"/>
       <c r="W189" t="n">
         <v>5.04</v>
@@ -17925,7 +18385,11 @@
       </c>
       <c r="S190" t="inlineStr"/>
       <c r="T190" t="inlineStr"/>
-      <c r="U190" t="inlineStr"/>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V190" t="inlineStr"/>
       <c r="W190" t="n">
         <v>3.01</v>
@@ -18002,7 +18466,11 @@
       </c>
       <c r="S191" t="inlineStr"/>
       <c r="T191" t="inlineStr"/>
-      <c r="U191" t="inlineStr"/>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V191" t="inlineStr"/>
       <c r="W191" t="n">
         <v>6.28</v>
@@ -18162,7 +18630,11 @@
       </c>
       <c r="S193" t="inlineStr"/>
       <c r="T193" t="inlineStr"/>
-      <c r="U193" t="inlineStr"/>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V193" t="inlineStr"/>
       <c r="W193" t="n">
         <v>1.43</v>
@@ -18239,7 +18711,11 @@
       </c>
       <c r="S194" t="inlineStr"/>
       <c r="T194" t="inlineStr"/>
-      <c r="U194" t="inlineStr"/>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V194" t="inlineStr"/>
       <c r="W194" t="n">
         <v>6.02</v>
@@ -18316,7 +18792,11 @@
       </c>
       <c r="S195" t="inlineStr"/>
       <c r="T195" t="inlineStr"/>
-      <c r="U195" t="inlineStr"/>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V195" t="inlineStr"/>
       <c r="W195" t="n">
         <v>3.61</v>
@@ -18393,7 +18873,11 @@
       </c>
       <c r="S196" t="inlineStr"/>
       <c r="T196" t="inlineStr"/>
-      <c r="U196" t="inlineStr"/>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V196" t="inlineStr"/>
       <c r="W196" t="n">
         <v>1.71</v>
@@ -18553,7 +19037,11 @@
       </c>
       <c r="S198" t="inlineStr"/>
       <c r="T198" t="inlineStr"/>
-      <c r="U198" t="inlineStr"/>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V198" t="inlineStr"/>
       <c r="W198" t="n">
         <v>1.54</v>
@@ -18630,7 +19118,11 @@
       </c>
       <c r="S199" t="inlineStr"/>
       <c r="T199" t="inlineStr"/>
-      <c r="U199" t="inlineStr"/>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V199" t="inlineStr"/>
       <c r="W199" t="n">
         <v>1.59</v>
@@ -18788,7 +19280,11 @@
       </c>
       <c r="S201" t="inlineStr"/>
       <c r="T201" t="inlineStr"/>
-      <c r="U201" t="inlineStr"/>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V201" t="inlineStr"/>
       <c r="W201" t="n">
         <v>1.08</v>
@@ -18861,7 +19357,11 @@
       </c>
       <c r="S202" t="inlineStr"/>
       <c r="T202" t="inlineStr"/>
-      <c r="U202" t="inlineStr"/>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V202" t="inlineStr"/>
       <c r="W202" t="n">
         <v>0.59</v>
@@ -18934,7 +19434,11 @@
       </c>
       <c r="S203" t="inlineStr"/>
       <c r="T203" t="inlineStr"/>
-      <c r="U203" t="inlineStr"/>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V203" t="inlineStr"/>
       <c r="W203" t="n">
         <v>1.09</v>
@@ -19009,7 +19513,11 @@
       </c>
       <c r="S204" t="inlineStr"/>
       <c r="T204" t="inlineStr"/>
-      <c r="U204" t="inlineStr"/>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V204" t="inlineStr"/>
       <c r="W204" t="n">
         <v>5.22</v>
@@ -19086,7 +19594,11 @@
       </c>
       <c r="S205" t="inlineStr"/>
       <c r="T205" t="inlineStr"/>
-      <c r="U205" t="inlineStr"/>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V205" t="inlineStr"/>
       <c r="W205" t="n">
         <v>1.31</v>
@@ -19163,7 +19675,11 @@
       </c>
       <c r="S206" t="inlineStr"/>
       <c r="T206" t="inlineStr"/>
-      <c r="U206" t="inlineStr"/>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V206" t="inlineStr"/>
       <c r="W206" t="n">
         <v>5.29</v>
@@ -19240,7 +19756,11 @@
       </c>
       <c r="S207" t="inlineStr"/>
       <c r="T207" t="inlineStr"/>
-      <c r="U207" t="inlineStr"/>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V207" t="inlineStr"/>
       <c r="W207" t="n">
         <v>0.4</v>
@@ -19400,7 +19920,11 @@
       </c>
       <c r="S209" t="inlineStr"/>
       <c r="T209" t="inlineStr"/>
-      <c r="U209" t="inlineStr"/>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V209" t="inlineStr"/>
       <c r="W209" t="n">
         <v>0.22</v>
@@ -19475,7 +19999,11 @@
       </c>
       <c r="S210" t="inlineStr"/>
       <c r="T210" t="inlineStr"/>
-      <c r="U210" t="inlineStr"/>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V210" t="inlineStr"/>
       <c r="W210" t="n">
         <v>0.5600000000000001</v>
@@ -19552,7 +20080,11 @@
       </c>
       <c r="S211" t="inlineStr"/>
       <c r="T211" t="inlineStr"/>
-      <c r="U211" t="inlineStr"/>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V211" t="inlineStr"/>
       <c r="W211" t="n">
         <v>3.63</v>
@@ -19625,7 +20157,11 @@
       </c>
       <c r="S212" t="inlineStr"/>
       <c r="T212" t="inlineStr"/>
-      <c r="U212" t="inlineStr"/>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V212" t="inlineStr"/>
       <c r="W212" t="n">
         <v>0</v>
@@ -19698,7 +20234,11 @@
       </c>
       <c r="S213" t="inlineStr"/>
       <c r="T213" t="inlineStr"/>
-      <c r="U213" t="inlineStr"/>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V213" t="inlineStr"/>
       <c r="W213" t="n">
         <v>0</v>
@@ -19775,7 +20315,11 @@
       </c>
       <c r="S214" t="inlineStr"/>
       <c r="T214" t="inlineStr"/>
-      <c r="U214" t="inlineStr"/>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V214" t="inlineStr"/>
       <c r="W214" t="n">
         <v>1.78</v>
@@ -19852,7 +20396,11 @@
       </c>
       <c r="S215" t="inlineStr"/>
       <c r="T215" t="inlineStr"/>
-      <c r="U215" t="inlineStr"/>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V215" t="inlineStr"/>
       <c r="W215" t="n">
         <v>0</v>
@@ -19929,7 +20477,11 @@
       </c>
       <c r="S216" t="inlineStr"/>
       <c r="T216" t="inlineStr"/>
-      <c r="U216" t="inlineStr"/>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V216" t="inlineStr"/>
       <c r="W216" t="n">
         <v>4.06</v>
@@ -20006,7 +20558,11 @@
       </c>
       <c r="S217" t="inlineStr"/>
       <c r="T217" t="inlineStr"/>
-      <c r="U217" t="inlineStr"/>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V217" t="inlineStr"/>
       <c r="W217" t="n">
         <v>5.06</v>
@@ -20083,7 +20639,11 @@
       </c>
       <c r="S218" t="inlineStr"/>
       <c r="T218" t="inlineStr"/>
-      <c r="U218" t="inlineStr"/>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V218" t="inlineStr"/>
       <c r="W218" t="n">
         <v>0.6899999999999999</v>
@@ -20160,7 +20720,11 @@
       </c>
       <c r="S219" t="inlineStr"/>
       <c r="T219" t="inlineStr"/>
-      <c r="U219" t="inlineStr"/>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V219" t="inlineStr"/>
       <c r="W219" t="n">
         <v>3.46</v>
@@ -20403,7 +20967,11 @@
       </c>
       <c r="S222" t="inlineStr"/>
       <c r="T222" t="inlineStr"/>
-      <c r="U222" t="inlineStr"/>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V222" t="inlineStr"/>
       <c r="W222" t="n">
         <v>1.18</v>
@@ -20476,7 +21044,11 @@
       </c>
       <c r="S223" t="inlineStr"/>
       <c r="T223" t="inlineStr"/>
-      <c r="U223" t="inlineStr"/>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V223" t="inlineStr"/>
       <c r="W223" t="n">
         <v>0</v>
@@ -20553,7 +21125,11 @@
       </c>
       <c r="S224" t="inlineStr"/>
       <c r="T224" t="inlineStr"/>
-      <c r="U224" t="inlineStr"/>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V224" t="inlineStr"/>
       <c r="W224" t="n">
         <v>0.65</v>
@@ -20626,7 +21202,11 @@
       </c>
       <c r="S225" t="inlineStr"/>
       <c r="T225" t="inlineStr"/>
-      <c r="U225" t="inlineStr"/>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V225" t="inlineStr"/>
       <c r="W225" t="n">
         <v>0</v>
@@ -20699,7 +21279,11 @@
       </c>
       <c r="S226" t="inlineStr"/>
       <c r="T226" t="inlineStr"/>
-      <c r="U226" t="inlineStr"/>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V226" t="inlineStr"/>
       <c r="W226" t="n">
         <v>0</v>
@@ -20776,7 +21360,11 @@
       </c>
       <c r="S227" t="inlineStr"/>
       <c r="T227" t="inlineStr"/>
-      <c r="U227" t="inlineStr"/>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V227" t="inlineStr"/>
       <c r="W227" t="n">
         <v>0</v>
@@ -20853,7 +21441,11 @@
       </c>
       <c r="S228" t="inlineStr"/>
       <c r="T228" t="inlineStr"/>
-      <c r="U228" t="inlineStr"/>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V228" t="inlineStr"/>
       <c r="W228" t="n">
         <v>0.04</v>
@@ -20926,7 +21518,11 @@
       </c>
       <c r="S229" t="inlineStr"/>
       <c r="T229" t="inlineStr"/>
-      <c r="U229" t="inlineStr"/>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V229" t="inlineStr"/>
       <c r="W229" t="n">
         <v>0</v>
@@ -20997,7 +21593,11 @@
       <c r="R230" t="inlineStr"/>
       <c r="S230" t="inlineStr"/>
       <c r="T230" t="inlineStr"/>
-      <c r="U230" t="inlineStr"/>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="V230" t="inlineStr"/>
       <c r="W230" t="n">
         <v>0</v>
@@ -21054,7 +21654,11 @@
       <c r="R231" t="inlineStr"/>
       <c r="S231" t="inlineStr"/>
       <c r="T231" t="inlineStr"/>
-      <c r="U231" t="inlineStr"/>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>⏸ 缺收盤/EPS</t>
+        </is>
+      </c>
       <c r="V231" t="inlineStr"/>
       <c r="W231" t="inlineStr"/>
     </row>
@@ -21109,7 +21713,11 @@
       <c r="R232" t="inlineStr"/>
       <c r="S232" t="inlineStr"/>
       <c r="T232" t="inlineStr"/>
-      <c r="U232" t="inlineStr"/>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>⏸ 缺收盤/EPS</t>
+        </is>
+      </c>
       <c r="V232" t="inlineStr"/>
       <c r="W232" t="inlineStr"/>
     </row>
@@ -21174,7 +21782,11 @@
       </c>
       <c r="S233" t="inlineStr"/>
       <c r="T233" t="inlineStr"/>
-      <c r="U233" t="inlineStr"/>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>⏸ 無成長率</t>
+        </is>
+      </c>
       <c r="V233" t="inlineStr"/>
       <c r="W233" t="inlineStr"/>
     </row>

--- a/data/台股_拐點掃描.xlsx
+++ b/data/台股_拐點掃描.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W28"/>
+  <dimension ref="A1:W27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R8" t="n">
-        <v>13.9</v>
+        <v>14.1</v>
       </c>
       <c r="S8" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>6.42</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="9">
@@ -1415,12 +1415,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>寶島科</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1448,66 +1448,64 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>12.5</v>
+        <v>7.3</v>
       </c>
       <c r="J12" t="n">
-        <v>13.3</v>
+        <v>31.3</v>
       </c>
       <c r="K12" t="n">
-        <v>52.4</v>
+        <v>9.1</v>
       </c>
       <c r="L12" t="n">
-        <v>40.9</v>
+        <v>11.5</v>
       </c>
       <c r="M12" t="n">
-        <v>19.2</v>
+        <v>17.4</v>
       </c>
       <c r="N12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="O12" t="inlineStr"/>
+        <v>2.38</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="Q12" t="n">
         <v>42</v>
       </c>
       <c r="R12" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="S12" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.52</v>
-      </c>
+        <v>16.6</v>
+      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
-        </is>
-      </c>
-      <c r="V12" t="n">
-        <v>13.3</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="n">
-        <v>4.01</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5312</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>寶島科</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1520,7 +1518,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1535,82 +1533,84 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>7.3</v>
+        <v>11.5</v>
       </c>
       <c r="J13" t="n">
-        <v>31.3</v>
+        <v>17.5</v>
       </c>
       <c r="K13" t="n">
-        <v>9.1</v>
+        <v>20.9</v>
       </c>
       <c r="L13" t="n">
-        <v>11.5</v>
+        <v>16.1</v>
       </c>
       <c r="M13" t="n">
-        <v>17.4</v>
+        <v>27.4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+        <v>1.31</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="R13" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
+        <v>14.9</v>
+      </c>
+      <c r="S13" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.85</v>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr"/>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>17.5</v>
+      </c>
       <c r="W13" t="n">
-        <v>6.66</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥強拐點</t>
+          <t>🌱初拐點</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1620,26 +1620,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
-        <v>17.5</v>
+        <v>2.5</v>
       </c>
       <c r="K14" t="n">
-        <v>20.9</v>
+        <v>22.2</v>
       </c>
       <c r="L14" t="n">
-        <v>16.1</v>
+        <v>24.5</v>
       </c>
       <c r="M14" t="n">
-        <v>27.4</v>
+        <v>9.9</v>
       </c>
       <c r="N14" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -1648,38 +1648,38 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>14.9</v>
+        <v>16.4</v>
       </c>
       <c r="S14" t="n">
-        <v>12.7</v>
+        <v>16</v>
       </c>
       <c r="T14" t="n">
-        <v>0.85</v>
+        <v>6.56</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>17.5</v>
+        <v>2.5</v>
       </c>
       <c r="W14" t="n">
-        <v>5.42</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>9931</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>欣高</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1711,62 +1711,60 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5</v>
+        <v>15.7</v>
       </c>
       <c r="K15" t="n">
-        <v>22.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>24.5</v>
+        <v>9</v>
       </c>
       <c r="M15" t="n">
-        <v>9.9</v>
+        <v>13.2</v>
       </c>
       <c r="N15" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="O15" t="inlineStr"/>
+        <v>2.04</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="S15" t="n">
-        <v>16</v>
-      </c>
-      <c r="T15" t="n">
-        <v>6.56</v>
-      </c>
+        <v>14.8</v>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
-        </is>
-      </c>
-      <c r="V15" t="n">
-        <v>2.5</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="n">
-        <v>5.07</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>欣高</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1779,12 +1777,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1798,60 +1796,62 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.4</v>
+        <v>6.1</v>
       </c>
       <c r="J16" t="n">
-        <v>15.7</v>
+        <v>6.5</v>
       </c>
       <c r="K16" t="n">
-        <v>8.300000000000001</v>
+        <v>23.6</v>
       </c>
       <c r="L16" t="n">
-        <v>9</v>
+        <v>26.2</v>
       </c>
       <c r="M16" t="n">
-        <v>13.2</v>
+        <v>5.3</v>
       </c>
       <c r="N16" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+        <v>2.85</v>
+      </c>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
+        <v>20.5</v>
+      </c>
+      <c r="S16" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.17</v>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr"/>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>6.5</v>
+      </c>
       <c r="W16" t="n">
-        <v>5.13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1864,81 +1864,77 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>待逐季</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>6.5</v>
-      </c>
+        <v>3.4</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="n">
-        <v>23.6</v>
+        <v>19.5</v>
       </c>
       <c r="L17" t="n">
-        <v>26.2</v>
+        <v>14.3</v>
       </c>
       <c r="M17" t="n">
-        <v>5.3</v>
+        <v>15.7</v>
       </c>
       <c r="N17" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O17" t="inlineStr"/>
+        <v>2.32</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="S17" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.15</v>
-      </c>
+        <v>14.2</v>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
-        </is>
-      </c>
-      <c r="V17" t="n">
-        <v>6.5</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="n">
-        <v>2.83</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>和泰車</t>
+          <t>台耀</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1951,39 +1947,41 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>待逐季</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J18" t="inlineStr"/>
+        <v>-25.2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.7</v>
+      </c>
       <c r="K18" t="n">
-        <v>19.5</v>
+        <v>3.6</v>
       </c>
       <c r="L18" t="n">
-        <v>14.3</v>
+        <v>4.3</v>
       </c>
       <c r="M18" t="n">
-        <v>15.7</v>
+        <v>-4.9</v>
       </c>
       <c r="N18" t="n">
-        <v>2.32</v>
+        <v>3.32</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1999,7 +1997,7 @@
         <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>14.2</v>
+        <v>18.5</v>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
@@ -2010,18 +2008,18 @@
       </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="n">
-        <v>4.12</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>台耀</t>
+          <t>喬山</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2044,69 +2042,71 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>-25.2</v>
+        <v>189</v>
       </c>
       <c r="J19" t="n">
-        <v>2.7</v>
+        <v>85.5</v>
       </c>
       <c r="K19" t="n">
-        <v>3.6</v>
+        <v>17.7</v>
       </c>
       <c r="L19" t="n">
-        <v>4.3</v>
+        <v>10.3</v>
       </c>
       <c r="M19" t="n">
-        <v>-4.9</v>
+        <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+        <v>1.09</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R19" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
+        <v>14.5</v>
+      </c>
+      <c r="S19" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.24</v>
+      </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr"/>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>60</v>
+      </c>
       <c r="W19" t="n">
-        <v>5.71</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>喬山</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2138,22 +2138,22 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>189</v>
+        <v>19.7</v>
       </c>
       <c r="J20" t="n">
-        <v>85.5</v>
+        <v>23.3</v>
       </c>
       <c r="K20" t="n">
-        <v>17.7</v>
+        <v>24.9</v>
       </c>
       <c r="L20" t="n">
-        <v>10.3</v>
+        <v>19.8</v>
       </c>
       <c r="M20" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="N20" t="n">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2162,16 +2162,16 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R20" t="n">
-        <v>14.5</v>
+        <v>12.4</v>
       </c>
       <c r="S20" t="n">
-        <v>9.1</v>
+        <v>10.1</v>
       </c>
       <c r="T20" t="n">
-        <v>0.24</v>
+        <v>0.53</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -2179,21 +2179,21 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>60</v>
+        <v>23.3</v>
       </c>
       <c r="W20" t="n">
-        <v>3.19</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2225,22 +2225,22 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>19.7</v>
+        <v>12</v>
       </c>
       <c r="J21" t="n">
-        <v>23.3</v>
+        <v>24.3</v>
       </c>
       <c r="K21" t="n">
-        <v>24.9</v>
+        <v>16.3</v>
       </c>
       <c r="L21" t="n">
-        <v>19.8</v>
+        <v>15.3</v>
       </c>
       <c r="M21" t="n">
-        <v>1.7</v>
+        <v>-19.4</v>
       </c>
       <c r="N21" t="n">
-        <v>1.24</v>
+        <v>0.9</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -2252,13 +2252,13 @@
         <v>10</v>
       </c>
       <c r="R21" t="n">
-        <v>12.4</v>
+        <v>17.9</v>
       </c>
       <c r="S21" t="n">
-        <v>10.1</v>
+        <v>14.4</v>
       </c>
       <c r="T21" t="n">
-        <v>0.53</v>
+        <v>0.74</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -2266,21 +2266,21 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>23.3</v>
+        <v>24.3</v>
       </c>
       <c r="W21" t="n">
-        <v>6.09</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>一零四</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2293,41 +2293,41 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>12</v>
+        <v>7.2</v>
       </c>
       <c r="J22" t="n">
-        <v>24.3</v>
+        <v>3.1</v>
       </c>
       <c r="K22" t="n">
-        <v>16.3</v>
+        <v>27.5</v>
       </c>
       <c r="L22" t="n">
-        <v>15.3</v>
+        <v>27.9</v>
       </c>
       <c r="M22" t="n">
-        <v>-19.4</v>
+        <v>10.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0.9</v>
+        <v>1.55</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -2336,38 +2336,38 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R22" t="n">
-        <v>17.9</v>
+        <v>14.8</v>
       </c>
       <c r="S22" t="n">
         <v>14.4</v>
       </c>
       <c r="T22" t="n">
-        <v>0.74</v>
+        <v>4.82</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="V22" t="n">
-        <v>24.3</v>
+        <v>3.1</v>
       </c>
       <c r="W22" t="n">
-        <v>3.1</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>6721</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>一零四</t>
+          <t>信實</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2395,26 +2395,26 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>7.2</v>
+        <v>14.7</v>
       </c>
       <c r="J23" t="n">
-        <v>3.1</v>
+        <v>14.7</v>
       </c>
       <c r="K23" t="n">
-        <v>27.5</v>
+        <v>15.4</v>
       </c>
       <c r="L23" t="n">
-        <v>27.9</v>
+        <v>14.5</v>
       </c>
       <c r="M23" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>1.55</v>
+        <v>0.87</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -2423,38 +2423,38 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="R23" t="n">
-        <v>14.8</v>
+        <v>11.8</v>
       </c>
       <c r="S23" t="n">
-        <v>14.4</v>
+        <v>10.3</v>
       </c>
       <c r="T23" t="n">
-        <v>4.82</v>
+        <v>0.8</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="V23" t="n">
-        <v>3.1</v>
+        <v>14.7</v>
       </c>
       <c r="W23" t="n">
-        <v>6.69</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>9942</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>信實</t>
+          <t>茂順</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2482,66 +2482,64 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>14.7</v>
+        <v>5.9</v>
       </c>
       <c r="J24" t="n">
-        <v>14.7</v>
+        <v>1.4</v>
       </c>
       <c r="K24" t="n">
-        <v>15.4</v>
+        <v>15.1</v>
       </c>
       <c r="L24" t="n">
-        <v>14.5</v>
+        <v>19.6</v>
       </c>
       <c r="M24" t="n">
-        <v>9.199999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="O24" t="inlineStr"/>
+        <v>1.47</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R24" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0.8</v>
-      </c>
+        <v>14.4</v>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
-        </is>
-      </c>
-      <c r="V24" t="n">
-        <v>14.7</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr"/>
       <c r="W24" t="n">
-        <v>5.89</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9942</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>茂順</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2559,12 +2557,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2573,60 +2571,62 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="J25" t="n">
-        <v>1.4</v>
+        <v>6.9</v>
       </c>
       <c r="K25" t="n">
-        <v>15.1</v>
+        <v>16.6</v>
       </c>
       <c r="L25" t="n">
-        <v>19.6</v>
+        <v>18.4</v>
       </c>
       <c r="M25" t="n">
-        <v>10.8</v>
+        <v>3.9</v>
       </c>
       <c r="N25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+        <v>2.36</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R25" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="S25" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.51</v>
+      </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr"/>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>6.9</v>
+      </c>
       <c r="W25" t="n">
-        <v>5.91</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2658,22 +2658,22 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="J26" t="n">
-        <v>6.9</v>
+        <v>4.9</v>
       </c>
       <c r="K26" t="n">
-        <v>16.6</v>
+        <v>20.6</v>
       </c>
       <c r="L26" t="n">
-        <v>18.4</v>
+        <v>21.8</v>
       </c>
       <c r="M26" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="N26" t="n">
-        <v>2.36</v>
+        <v>1.3</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
@@ -2682,38 +2682,38 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="R26" t="n">
-        <v>24</v>
+        <v>17.2</v>
       </c>
       <c r="S26" t="n">
-        <v>22.5</v>
+        <v>16.4</v>
       </c>
       <c r="T26" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="V26" t="n">
-        <v>6.9</v>
+        <v>4.9</v>
       </c>
       <c r="W26" t="n">
-        <v>4.05</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>台特化</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2726,41 +2726,39 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J27" t="n">
-        <v>4.9</v>
-      </c>
+        <v>53.6</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="L27" t="n">
-        <v>21.8</v>
+        <v>14.1</v>
       </c>
       <c r="M27" t="n">
-        <v>1.4</v>
+        <v>241.2</v>
       </c>
       <c r="N27" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -2769,111 +2767,26 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="R27" t="n">
-        <v>17.2</v>
+        <v>58.5</v>
       </c>
       <c r="S27" t="n">
-        <v>16.4</v>
+        <v>38.1</v>
       </c>
       <c r="T27" t="n">
-        <v>3.49</v>
+        <v>1.09</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
       <c r="V27" t="n">
-        <v>4.9</v>
+        <v>53.6</v>
       </c>
       <c r="W27" t="n">
-        <v>5.32</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>4772</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>台特化</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>🌱初拐點</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>2</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="L28" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="M28" t="n">
-        <v>241.2</v>
-      </c>
-      <c r="N28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>PE</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>41</v>
-      </c>
-      <c r="R28" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="S28" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>🔴未來過熱</t>
-        </is>
-      </c>
-      <c r="V28" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="W28" t="n">
         <v>1.06</v>
       </c>
     </row>
@@ -4584,11 +4497,7 @@
           <t>寶雅</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>🔥強拐點</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
         <v>3</v>
       </c>
@@ -4637,16 +4546,16 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="R21" t="n">
-        <v>20.2</v>
+        <v>20.9</v>
       </c>
       <c r="S21" t="n">
-        <v>17.8</v>
+        <v>18.5</v>
       </c>
       <c r="T21" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -4657,7 +4566,7 @@
         <v>13.3</v>
       </c>
       <c r="W21" t="n">
-        <v>4.01</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="22">
@@ -5052,10 +4961,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R26" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
@@ -5066,7 +4975,7 @@
       </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="n">
-        <v>6.76</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="27">
@@ -5542,16 +5451,16 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R32" t="n">
-        <v>13.9</v>
+        <v>14.1</v>
       </c>
       <c r="S32" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="T32" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -5562,7 +5471,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="W32" t="n">
-        <v>6.42</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="33">
@@ -6298,7 +6207,7 @@
         <v>15.4</v>
       </c>
       <c r="T41" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -6309,7 +6218,7 @@
         <v>10.9</v>
       </c>
       <c r="W41" t="n">
-        <v>4.45</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="42">
@@ -7301,10 +7210,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="R53" t="n">
-        <v>25.3</v>
+        <v>25.6</v>
       </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
@@ -7315,7 +7224,7 @@
       </c>
       <c r="V53" t="inlineStr"/>
       <c r="W53" t="n">
-        <v>3.48</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="54">
@@ -10450,16 +10359,16 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R92" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="S92" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="T92" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="U92" t="inlineStr">
         <is>
@@ -10470,7 +10379,7 @@
         <v>6.5</v>
       </c>
       <c r="W92" t="n">
-        <v>2.83</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">

--- a/data/台股_拐點掃描.xlsx
+++ b/data/台股_拐點掃描.xlsx
@@ -20,16 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,117 +420,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>改善訊號數</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>A毛利拐頭</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>B月營收動能</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>C_EPS加速</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>D_ROE回升</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>近四季ROE</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>5年均ROE</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>循環</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>看哪個位階</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>估值位階</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
@@ -3058,117 +3046,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>改善訊號數</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>A毛利拐頭</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>B月營收動能</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>C_EPS加速</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>D_ROE回升</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>近四季ROE</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>5年均ROE</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>循環</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>看哪個位階</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>估值位階</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
@@ -23843,67 +23831,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>EPS加速</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>5年均ROE</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ROE回升</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>PBR便宜</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
@@ -23924,67 +23912,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>EPS加速</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>5年均ROE</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ROE回升</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>PBR便宜</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>

--- a/data/台股_拐點掃描.xlsx
+++ b/data/台股_拐點掃描.xlsx
@@ -20,13 +20,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,117 +432,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>改善訊號數</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>A毛利拐頭</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>B月營收動能</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>C_EPS加速</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>D_ROE回升</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>近四季ROE</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>5年均ROE</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>循環</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>看哪個位階</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>估值位階</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
@@ -3046,117 +3058,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>改善訊號數</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>A毛利拐頭</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>B月營收動能</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>C_EPS加速</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>D_ROE回升</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>近四季ROE</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>5年均ROE</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>循環</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>看哪個位階</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>估值位階</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
@@ -4969,21 +4981,25 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>高技</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>建準</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>🔥強拐點</t>
+        </is>
+      </c>
       <c r="D24" t="n">
         <v>3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4993,7 +5009,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -5002,73 +5018,71 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>31.4</v>
+        <v>46.8</v>
       </c>
       <c r="J24" t="n">
-        <v>51.1</v>
+        <v>22.3</v>
       </c>
       <c r="K24" t="n">
-        <v>33.3</v>
+        <v>20.7</v>
       </c>
       <c r="L24" t="n">
         <v>19.9</v>
       </c>
       <c r="M24" t="n">
-        <v>58.3</v>
+        <v>14.9</v>
       </c>
       <c r="N24" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+        <v>1.16</v>
+      </c>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="R24" t="n">
-        <v>21</v>
-      </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
+        <v>17.5</v>
+      </c>
+      <c r="S24" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.78</v>
+      </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr"/>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>22.3</v>
+      </c>
       <c r="W24" t="n">
-        <v>2.24</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>建準</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>🔥強拐點</t>
-        </is>
-      </c>
+          <t>高技</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="n">
         <v>3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5078,7 +5092,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -5087,51 +5101,49 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>46.8</v>
+        <v>31.4</v>
       </c>
       <c r="J25" t="n">
-        <v>22.3</v>
+        <v>51.1</v>
       </c>
       <c r="K25" t="n">
-        <v>20.7</v>
+        <v>33.3</v>
       </c>
       <c r="L25" t="n">
         <v>19.9</v>
       </c>
       <c r="M25" t="n">
-        <v>14.9</v>
+        <v>58.3</v>
       </c>
       <c r="N25" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="O25" t="inlineStr"/>
+        <v>0.92</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="R25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="S25" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.78</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
-        </is>
-      </c>
-      <c r="V25" t="n">
-        <v>22.3</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr"/>
       <c r="W25" t="n">
-        <v>3.49</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="26">
@@ -5791,12 +5803,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -5810,7 +5822,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5820,53 +5832,55 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5.7</v>
+        <v>10.4</v>
       </c>
       <c r="J34" t="n">
-        <v>6</v>
+        <v>10.9</v>
       </c>
       <c r="K34" t="n">
-        <v>14.1</v>
+        <v>19.8</v>
       </c>
       <c r="L34" t="n">
         <v>18</v>
       </c>
       <c r="M34" t="n">
-        <v>74.59999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="N34" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+        <v>1.28</v>
+      </c>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="R34" t="n">
-        <v>83.40000000000001</v>
-      </c>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
+        <v>17.1</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.56</v>
+      </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr"/>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>10.9</v>
+      </c>
       <c r="W34" t="n">
-        <v>0.87</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="35">
@@ -5953,12 +5967,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6683</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -5977,31 +5991,31 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>-0.1</v>
+        <v>45.7</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9</v>
+        <v>37.5</v>
       </c>
       <c r="K36" t="n">
-        <v>16.8</v>
+        <v>23.4</v>
       </c>
       <c r="L36" t="n">
         <v>19</v>
       </c>
       <c r="M36" t="n">
-        <v>12.3</v>
+        <v>57.8</v>
       </c>
       <c r="N36" t="n">
-        <v>1.45</v>
+        <v>0.63</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
@@ -6010,16 +6024,16 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="R36" t="n">
-        <v>89.7</v>
+        <v>167.3</v>
       </c>
       <c r="S36" t="n">
-        <v>88.90000000000001</v>
+        <v>121.7</v>
       </c>
       <c r="T36" t="n">
-        <v>97.01000000000001</v>
+        <v>4.46</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -6027,10 +6041,10 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>0.9</v>
+        <v>37.5</v>
       </c>
       <c r="W36" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="37">
@@ -6117,12 +6131,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6683</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -6141,31 +6155,31 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>45.7</v>
+        <v>-0.1</v>
       </c>
       <c r="J38" t="n">
-        <v>37.5</v>
+        <v>0.9</v>
       </c>
       <c r="K38" t="n">
-        <v>23.4</v>
+        <v>16.8</v>
       </c>
       <c r="L38" t="n">
         <v>19</v>
       </c>
       <c r="M38" t="n">
-        <v>57.8</v>
+        <v>12.3</v>
       </c>
       <c r="N38" t="n">
-        <v>0.63</v>
+        <v>1.45</v>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
@@ -6174,16 +6188,16 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="R38" t="n">
-        <v>167.3</v>
+        <v>89.7</v>
       </c>
       <c r="S38" t="n">
-        <v>121.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="T38" t="n">
-        <v>4.46</v>
+        <v>97.01000000000001</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -6191,28 +6205,24 @@
         </is>
       </c>
       <c r="V38" t="n">
-        <v>37.5</v>
+        <v>0.9</v>
       </c>
       <c r="W38" t="n">
-        <v>0.34</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2727</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>八方雲集</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>🔥強拐點</t>
-        </is>
-      </c>
+          <t>王品</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="n">
         <v>3</v>
       </c>
@@ -6236,66 +6246,66 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I39" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
-        <v>8.699999999999999</v>
+        <v>45.9</v>
       </c>
       <c r="K39" t="n">
-        <v>22.1</v>
+        <v>33.6</v>
       </c>
       <c r="L39" t="n">
         <v>17.9</v>
       </c>
       <c r="M39" t="n">
-        <v>13.3</v>
+        <v>15</v>
       </c>
       <c r="N39" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="O39" t="inlineStr"/>
+        <v>2.56</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="R39" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="S39" t="n">
-        <v>13</v>
-      </c>
-      <c r="T39" t="n">
-        <v>1.62</v>
-      </c>
+        <v>14.8</v>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
-        </is>
-      </c>
-      <c r="V39" t="n">
-        <v>8.699999999999999</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr"/>
       <c r="W39" t="n">
-        <v>6.32</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>王品</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>八方雲集</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>🔥強拐點</t>
+        </is>
+      </c>
       <c r="D40" t="n">
         <v>3</v>
       </c>
@@ -6319,48 +6329,52 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="n">
+        <v>10.1</v>
+      </c>
       <c r="J40" t="n">
-        <v>45.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>33.6</v>
+        <v>22.1</v>
       </c>
       <c r="L40" t="n">
         <v>17.9</v>
       </c>
       <c r="M40" t="n">
-        <v>15</v>
+        <v>13.3</v>
       </c>
       <c r="N40" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+        <v>1.93</v>
+      </c>
+      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="R40" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
+        <v>14.1</v>
+      </c>
+      <c r="S40" t="n">
+        <v>13</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1.62</v>
+      </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr"/>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="V40" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="W40" t="n">
-        <v>6.54</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="41">
@@ -6777,12 +6791,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -6796,7 +6810,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6806,55 +6820,53 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>10.4</v>
+        <v>5.7</v>
       </c>
       <c r="J46" t="n">
-        <v>10.9</v>
+        <v>6</v>
       </c>
       <c r="K46" t="n">
-        <v>19.8</v>
+        <v>14.1</v>
       </c>
       <c r="L46" t="n">
         <v>18</v>
       </c>
       <c r="M46" t="n">
-        <v>0.6</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="N46" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="O46" t="inlineStr"/>
+        <v>1.43</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="R46" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="S46" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="T46" t="n">
-        <v>1.56</v>
-      </c>
+        <v>83.40000000000001</v>
+      </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
-        </is>
-      </c>
-      <c r="V46" t="n">
-        <v>10.9</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr"/>
       <c r="W46" t="n">
-        <v>4.47</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="47">
@@ -7194,15 +7206,19 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>6712</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>宜鼎</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>長聖</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>🔥強拐點</t>
+        </is>
+      </c>
       <c r="D51" t="n">
         <v>3</v>
       </c>
@@ -7218,31 +7234,31 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.6</v>
+        <v>-4.6</v>
       </c>
       <c r="J51" t="n">
-        <v>0.1</v>
+        <v>19</v>
       </c>
       <c r="K51" t="n">
-        <v>48.8</v>
+        <v>16.7</v>
       </c>
       <c r="L51" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="M51" t="n">
-        <v>640.8</v>
+        <v>25</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.36</v>
+        <v>1.16</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -7255,10 +7271,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="R51" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
@@ -7269,7 +7285,7 @@
       </c>
       <c r="V51" t="inlineStr"/>
       <c r="W51" t="n">
-        <v>0.87</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="52">
@@ -7358,19 +7374,15 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6712</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>長聖</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>🔥強拐點</t>
-        </is>
-      </c>
+          <t>宜鼎</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="n">
         <v>3</v>
       </c>
@@ -7386,31 +7398,31 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>-4.6</v>
+        <v>3.6</v>
       </c>
       <c r="J53" t="n">
-        <v>19</v>
+        <v>0.1</v>
       </c>
       <c r="K53" t="n">
-        <v>16.7</v>
+        <v>48.8</v>
       </c>
       <c r="L53" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="M53" t="n">
-        <v>25</v>
+        <v>640.8</v>
       </c>
       <c r="N53" t="n">
-        <v>1.16</v>
+        <v>-0.36</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -7423,10 +7435,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="R53" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
@@ -7437,7 +7449,7 @@
       </c>
       <c r="V53" t="inlineStr"/>
       <c r="W53" t="n">
-        <v>2.81</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="54">
@@ -7854,19 +7866,15 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>漢來美食</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>🔥強拐點</t>
-        </is>
-      </c>
+          <t>臺慶科</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="n">
         <v>3</v>
       </c>
@@ -7882,60 +7890,58 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>49.8</v>
+        <v>-3.9</v>
       </c>
       <c r="J59" t="n">
-        <v>48.7</v>
+        <v>0.5</v>
       </c>
       <c r="K59" t="n">
-        <v>19.2</v>
+        <v>10.8</v>
       </c>
       <c r="L59" t="n">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
       <c r="M59" t="n">
-        <v>10.9</v>
+        <v>37.8</v>
       </c>
       <c r="N59" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="O59" t="inlineStr"/>
+        <v>0.76</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>5</v>
+        <v>97</v>
       </c>
       <c r="R59" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="S59" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0.3</v>
-      </c>
+        <v>29.8</v>
+      </c>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
-        </is>
-      </c>
-      <c r="V59" t="n">
-        <v>48.7</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr"/>
       <c r="W59" t="n">
-        <v>4.71</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="60">
@@ -8603,25 +8609,21 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5312</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>寶島科</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>🔥強拐點</t>
-        </is>
-      </c>
+          <t>文曄</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="n">
         <v>3</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -8636,26 +8638,26 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>7.3</v>
+        <v>3.9</v>
       </c>
       <c r="J68" t="n">
-        <v>31.3</v>
+        <v>10.3</v>
       </c>
       <c r="K68" t="n">
-        <v>9.1</v>
+        <v>15.8</v>
       </c>
       <c r="L68" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="M68" t="n">
-        <v>17.4</v>
+        <v>152.7</v>
       </c>
       <c r="N68" t="n">
-        <v>2.38</v>
+        <v>-0.2</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -8668,10 +8670,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="R68" t="n">
-        <v>16.6</v>
+        <v>15.5</v>
       </c>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
@@ -8682,7 +8684,7 @@
       </c>
       <c r="V68" t="inlineStr"/>
       <c r="W68" t="n">
-        <v>6.66</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="69">
@@ -9164,12 +9166,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>豐達科</t>
+          <t>亞昕</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -9188,29 +9190,31 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>43.5</v>
+      </c>
       <c r="J75" t="n">
-        <v>27.1</v>
+        <v>67.3</v>
       </c>
       <c r="K75" t="n">
-        <v>9.4</v>
+        <v>6.4</v>
       </c>
       <c r="L75" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="M75" t="n">
-        <v>56.2</v>
+        <v>211.3</v>
       </c>
       <c r="N75" t="n">
-        <v>0.04</v>
+        <v>-3.1</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -9223,10 +9227,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="R75" t="n">
-        <v>23.3</v>
+        <v>15.3</v>
       </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
@@ -9237,7 +9241,7 @@
       </c>
       <c r="V75" t="inlineStr"/>
       <c r="W75" t="n">
-        <v>2.94</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="76">
@@ -9411,25 +9415,21 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>台汽電</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>🔥強拐點</t>
-        </is>
-      </c>
+          <t>豐達科</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="n">
         <v>3</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -9447,52 +9447,48 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I78" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="n">
-        <v>16.7</v>
+        <v>27.1</v>
       </c>
       <c r="K78" t="n">
-        <v>11.3</v>
+        <v>9.4</v>
       </c>
       <c r="L78" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="M78" t="n">
-        <v>768.2</v>
+        <v>56.2</v>
       </c>
       <c r="N78" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="O78" t="inlineStr"/>
+        <v>0.04</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="R78" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="S78" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="T78" t="n">
-        <v>1.16</v>
-      </c>
+        <v>23.3</v>
+      </c>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
-        </is>
-      </c>
-      <c r="V78" t="n">
-        <v>16.7</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr"/>
       <c r="W78" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="79">
@@ -9581,21 +9577,25 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>亞昕</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
+          <t>台汽電</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>🔥強拐點</t>
+        </is>
+      </c>
       <c r="D80" t="n">
         <v>3</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -9610,53 +9610,55 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>43.5</v>
+        <v>12.5</v>
       </c>
       <c r="J80" t="n">
-        <v>67.3</v>
+        <v>16.7</v>
       </c>
       <c r="K80" t="n">
-        <v>6.4</v>
+        <v>11.3</v>
       </c>
       <c r="L80" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M80" t="n">
-        <v>211.3</v>
+        <v>768.2</v>
       </c>
       <c r="N80" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+        <v>1.15</v>
+      </c>
+      <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="R80" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr"/>
+        <v>19.4</v>
+      </c>
+      <c r="S80" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1.16</v>
+      </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr"/>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="V80" t="n">
+        <v>16.7</v>
+      </c>
       <c r="W80" t="n">
-        <v>12.47</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="81">
@@ -9739,15 +9741,19 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>臺慶科</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
+          <t>漢來美食</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>🔥強拐點</t>
+        </is>
+      </c>
       <c r="D82" t="n">
         <v>3</v>
       </c>
@@ -9763,69 +9769,71 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>-3.9</v>
+        <v>49.8</v>
       </c>
       <c r="J82" t="n">
-        <v>0.5</v>
+        <v>48.7</v>
       </c>
       <c r="K82" t="n">
-        <v>10.8</v>
+        <v>19.2</v>
       </c>
       <c r="L82" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="M82" t="n">
-        <v>37.8</v>
+        <v>10.9</v>
       </c>
       <c r="N82" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+        <v>2.54</v>
+      </c>
+      <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>97</v>
+        <v>5</v>
       </c>
       <c r="R82" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr"/>
+        <v>14.7</v>
+      </c>
+      <c r="S82" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0.3</v>
+      </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr"/>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V82" t="n">
+        <v>48.7</v>
+      </c>
       <c r="W82" t="n">
-        <v>1.61</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>6449</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -9844,69 +9852,71 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>-3.3</v>
+        <v>20.7</v>
       </c>
       <c r="J83" t="n">
-        <v>-1.4</v>
+        <v>24.4</v>
       </c>
       <c r="K83" t="n">
-        <v>15.5</v>
+        <v>11.7</v>
       </c>
       <c r="L83" t="n">
-        <v>12.1</v>
+        <v>12.5</v>
       </c>
       <c r="M83" t="n">
-        <v>82.90000000000001</v>
+        <v>12.3</v>
       </c>
       <c r="N83" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+        <v>1.24</v>
+      </c>
+      <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="R83" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="S83" t="inlineStr"/>
-      <c r="T83" t="inlineStr"/>
+        <v>54.5</v>
+      </c>
+      <c r="S83" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="T83" t="n">
+        <v>2.23</v>
+      </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr"/>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="V83" t="n">
+        <v>24.4</v>
+      </c>
       <c r="W83" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>6449</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -9925,80 +9935,82 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>20.7</v>
+        <v>-3.3</v>
       </c>
       <c r="J84" t="n">
-        <v>24.4</v>
+        <v>-1.4</v>
       </c>
       <c r="K84" t="n">
-        <v>11.7</v>
+        <v>15.5</v>
       </c>
       <c r="L84" t="n">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="M84" t="n">
-        <v>12.3</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="N84" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="O84" t="inlineStr"/>
+        <v>-0.89</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R84" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="S84" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="T84" t="n">
-        <v>2.23</v>
-      </c>
+        <v>14.2</v>
+      </c>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr"/>
       <c r="U84" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
-        </is>
-      </c>
-      <c r="V84" t="n">
-        <v>24.4</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr"/>
       <c r="W84" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>文曄</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr"/>
+          <t>寶島科</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>🔥強拐點</t>
+        </is>
+      </c>
       <c r="D85" t="n">
         <v>3</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -10013,26 +10025,26 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.9</v>
+        <v>7.3</v>
       </c>
       <c r="J85" t="n">
-        <v>10.3</v>
+        <v>31.3</v>
       </c>
       <c r="K85" t="n">
-        <v>15.8</v>
+        <v>9.1</v>
       </c>
       <c r="L85" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="M85" t="n">
-        <v>152.7</v>
+        <v>17.4</v>
       </c>
       <c r="N85" t="n">
-        <v>-0.2</v>
+        <v>2.38</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -10045,10 +10057,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="R85" t="n">
-        <v>15.5</v>
+        <v>16.6</v>
       </c>
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr"/>
@@ -10059,18 +10071,18 @@
       </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" t="n">
-        <v>3.47</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>亞光</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -10079,7 +10091,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -10089,7 +10101,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -10098,22 +10110,22 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>-14.6</v>
+        <v>5.4</v>
       </c>
       <c r="J86" t="n">
-        <v>-5.5</v>
+        <v>26.1</v>
       </c>
       <c r="K86" t="n">
-        <v>12.4</v>
+        <v>13.1</v>
       </c>
       <c r="L86" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="M86" t="n">
-        <v>21.3</v>
+        <v>16.2</v>
       </c>
       <c r="N86" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
@@ -10126,10 +10138,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="R86" t="n">
-        <v>115.6</v>
+        <v>23.8</v>
       </c>
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="inlineStr"/>
@@ -10140,18 +10152,18 @@
       </c>
       <c r="V86" t="inlineStr"/>
       <c r="W86" t="n">
-        <v>0.65</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>亞光</t>
+          <t>世禾</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -10160,7 +10172,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -10175,64 +10187,66 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>5.4</v>
+        <v>3.9</v>
       </c>
       <c r="J87" t="n">
-        <v>26.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K87" t="n">
-        <v>13.1</v>
+        <v>10</v>
       </c>
       <c r="L87" t="n">
         <v>10.5</v>
       </c>
       <c r="M87" t="n">
-        <v>16.2</v>
+        <v>21.5</v>
       </c>
       <c r="N87" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+        <v>-0.79</v>
+      </c>
+      <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="R87" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="S87" t="inlineStr"/>
-      <c r="T87" t="inlineStr"/>
+        <v>24.4</v>
+      </c>
+      <c r="S87" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="T87" t="n">
+        <v>2.63</v>
+      </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr"/>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="V87" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="W87" t="n">
-        <v>2.82</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>世禾</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -10241,7 +10255,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -10256,26 +10270,26 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.9</v>
+        <v>7.3</v>
       </c>
       <c r="J88" t="n">
-        <v>9.300000000000001</v>
+        <v>12.1</v>
       </c>
       <c r="K88" t="n">
-        <v>10</v>
+        <v>13.6</v>
       </c>
       <c r="L88" t="n">
-        <v>10.5</v>
+        <v>10.8</v>
       </c>
       <c r="M88" t="n">
-        <v>21.5</v>
+        <v>35.3</v>
       </c>
       <c r="N88" t="n">
-        <v>-0.79</v>
+        <v>1.09</v>
       </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
@@ -10284,16 +10298,16 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="R88" t="n">
-        <v>24.4</v>
+        <v>25.2</v>
       </c>
       <c r="S88" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="T88" t="n">
-        <v>2.63</v>
+        <v>2.08</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
@@ -10301,21 +10315,21 @@
         </is>
       </c>
       <c r="V88" t="n">
-        <v>9.300000000000001</v>
+        <v>12.1</v>
       </c>
       <c r="W88" t="n">
-        <v>2.26</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -10324,7 +10338,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -10334,7 +10348,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -10343,51 +10357,49 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>7.3</v>
+        <v>-14.6</v>
       </c>
       <c r="J89" t="n">
-        <v>12.1</v>
+        <v>-5.5</v>
       </c>
       <c r="K89" t="n">
-        <v>13.6</v>
+        <v>12.4</v>
       </c>
       <c r="L89" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="M89" t="n">
-        <v>35.3</v>
+        <v>21.3</v>
       </c>
       <c r="N89" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="O89" t="inlineStr"/>
+        <v>0.99</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="R89" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="S89" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="T89" t="n">
-        <v>2.08</v>
-      </c>
+        <v>115.6</v>
+      </c>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
-        </is>
-      </c>
-      <c r="V89" t="n">
-        <v>12.1</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr"/>
       <c r="W89" t="n">
-        <v>3.03</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="90">
@@ -10942,12 +10954,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6776</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -10961,12 +10973,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10975,22 +10987,22 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>34.2</v>
+        <v>-0.4</v>
       </c>
       <c r="J97" t="n">
-        <v>39.1</v>
+        <v>-6.2</v>
       </c>
       <c r="K97" t="n">
-        <v>12.9</v>
+        <v>12.1</v>
       </c>
       <c r="L97" t="n">
         <v>16.5</v>
       </c>
       <c r="M97" t="n">
-        <v>-33.5</v>
+        <v>52.1</v>
       </c>
       <c r="N97" t="n">
-        <v>0.26</v>
+        <v>-2.58</v>
       </c>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
@@ -10999,38 +11011,32 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="R97" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="S97" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="T97" t="n">
-        <v>1.63</v>
-      </c>
+        <v>13.7</v>
+      </c>
+      <c r="S97" t="inlineStr"/>
+      <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
-        </is>
-      </c>
-      <c r="V97" t="n">
-        <v>39.1</v>
-      </c>
+          <t>⏸ 成長為負(-6%)</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr"/>
       <c r="W97" t="n">
-        <v>0.78</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>5493</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>世豐</t>
+          <t>三聯</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -11058,22 +11064,22 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>-32.9</v>
+        <v>-2.6</v>
       </c>
       <c r="J98" t="n">
-        <v>-45.3</v>
+        <v>-0.5</v>
       </c>
       <c r="K98" t="n">
-        <v>4.4</v>
+        <v>13.1</v>
       </c>
       <c r="L98" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="M98" t="n">
         <v>18.6</v>
       </c>
       <c r="N98" t="n">
-        <v>1.53</v>
+        <v>1.03</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -11086,10 +11092,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="R98" t="n">
-        <v>27.6</v>
+        <v>22.3</v>
       </c>
       <c r="S98" t="inlineStr"/>
       <c r="T98" t="inlineStr"/>
@@ -11100,21 +11106,25 @@
       </c>
       <c r="V98" t="inlineStr"/>
       <c r="W98" t="n">
-        <v>4.45</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6721</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>力成</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
+          <t>信實</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>🌱初拐點</t>
+        </is>
+      </c>
       <c r="D99" t="n">
         <v>2</v>
       </c>
@@ -11125,7 +11135,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -11135,26 +11145,26 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>-10.3</v>
+        <v>14.7</v>
       </c>
       <c r="J99" t="n">
-        <v>-13.6</v>
+        <v>14.7</v>
       </c>
       <c r="K99" t="n">
-        <v>10.9</v>
+        <v>15.4</v>
       </c>
       <c r="L99" t="n">
         <v>14.5</v>
       </c>
       <c r="M99" t="n">
-        <v>30.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="N99" t="n">
-        <v>2.01</v>
+        <v>0.87</v>
       </c>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
@@ -11163,21 +11173,27 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="R99" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="S99" t="inlineStr"/>
-      <c r="T99" t="inlineStr"/>
+        <v>11.8</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="T99" t="n">
+        <v>0.8</v>
+      </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-14%)</t>
-        </is>
-      </c>
-      <c r="V99" t="inlineStr"/>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V99" t="n">
+        <v>14.7</v>
+      </c>
       <c r="W99" t="n">
-        <v>1.23</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="100">
@@ -11264,12 +11280,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>中碳</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -11297,22 +11313,22 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>-10.9</v>
+        <v>-13.5</v>
       </c>
       <c r="J101" t="n">
-        <v>-13.6</v>
+        <v>-28.8</v>
       </c>
       <c r="K101" t="n">
-        <v>12.8</v>
+        <v>7.2</v>
       </c>
       <c r="L101" t="n">
         <v>15.5</v>
       </c>
       <c r="M101" t="n">
-        <v>28.6</v>
+        <v>58.4</v>
       </c>
       <c r="N101" t="n">
-        <v>3.26</v>
+        <v>1.42</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -11325,10 +11341,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="R101" t="n">
-        <v>62.1</v>
+        <v>36.1</v>
       </c>
       <c r="S101" t="inlineStr"/>
       <c r="T101" t="inlineStr"/>
@@ -11339,18 +11355,18 @@
       </c>
       <c r="V101" t="inlineStr"/>
       <c r="W101" t="n">
-        <v>0.98</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>中碳</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -11378,22 +11394,22 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>-13.5</v>
+        <v>-10.9</v>
       </c>
       <c r="J102" t="n">
-        <v>-28.8</v>
+        <v>-13.6</v>
       </c>
       <c r="K102" t="n">
-        <v>7.2</v>
+        <v>12.8</v>
       </c>
       <c r="L102" t="n">
         <v>15.5</v>
       </c>
       <c r="M102" t="n">
-        <v>58.4</v>
+        <v>28.6</v>
       </c>
       <c r="N102" t="n">
-        <v>1.42</v>
+        <v>3.26</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
@@ -11406,10 +11422,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="R102" t="n">
-        <v>36.1</v>
+        <v>62.1</v>
       </c>
       <c r="S102" t="inlineStr"/>
       <c r="T102" t="inlineStr"/>
@@ -11420,7 +11436,7 @@
       </c>
       <c r="V102" t="inlineStr"/>
       <c r="W102" t="n">
-        <v>2.07</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="103">
@@ -11507,19 +11523,15 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>信實</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>🌱初拐點</t>
-        </is>
-      </c>
+          <t>力成</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
       <c r="D104" t="n">
         <v>2</v>
       </c>
@@ -11530,7 +11542,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -11540,26 +11552,26 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>14.7</v>
+        <v>-10.3</v>
       </c>
       <c r="J104" t="n">
-        <v>14.7</v>
+        <v>-13.6</v>
       </c>
       <c r="K104" t="n">
-        <v>15.4</v>
+        <v>10.9</v>
       </c>
       <c r="L104" t="n">
         <v>14.5</v>
       </c>
       <c r="M104" t="n">
-        <v>9.199999999999999</v>
+        <v>30.2</v>
       </c>
       <c r="N104" t="n">
-        <v>0.87</v>
+        <v>2.01</v>
       </c>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
@@ -11568,27 +11580,21 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="R104" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="S104" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="T104" t="n">
-        <v>0.8</v>
-      </c>
+        <v>43.6</v>
+      </c>
+      <c r="S104" t="inlineStr"/>
+      <c r="T104" t="inlineStr"/>
       <c r="U104" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
-        </is>
-      </c>
-      <c r="V104" t="n">
-        <v>14.7</v>
-      </c>
+          <t>⏸ 成長為負(-14%)</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr"/>
       <c r="W104" t="n">
-        <v>5.89</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="105">
@@ -11756,12 +11762,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -11770,7 +11776,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -11785,26 +11791,26 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>97</v>
+        <v>-14.7</v>
       </c>
       <c r="J107" t="n">
-        <v>69.2</v>
+        <v>-16.6</v>
       </c>
       <c r="K107" t="n">
-        <v>29.3</v>
+        <v>13.1</v>
       </c>
       <c r="L107" t="n">
         <v>17.1</v>
       </c>
       <c r="M107" t="n">
-        <v>116</v>
+        <v>35.3</v>
       </c>
       <c r="N107" t="n">
-        <v>1.02</v>
+        <v>1.95</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
@@ -11817,10 +11823,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="R107" t="n">
-        <v>77.09999999999999</v>
+        <v>16.9</v>
       </c>
       <c r="S107" t="inlineStr"/>
       <c r="T107" t="inlineStr"/>
@@ -11831,7 +11837,7 @@
       </c>
       <c r="V107" t="inlineStr"/>
       <c r="W107" t="n">
-        <v>0.57</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="108">
@@ -12165,59 +12171,55 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>卜蜂</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>🌱初拐點</t>
-        </is>
-      </c>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
       <c r="D112" t="n">
         <v>2</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>19.7</v>
+        <v>17</v>
       </c>
       <c r="J112" t="n">
-        <v>23.3</v>
+        <v>10.8</v>
       </c>
       <c r="K112" t="n">
-        <v>24.9</v>
+        <v>19.2</v>
       </c>
       <c r="L112" t="n">
         <v>19.8</v>
       </c>
       <c r="M112" t="n">
-        <v>1.7</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="N112" t="n">
-        <v>1.24</v>
+        <v>1.94</v>
       </c>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
@@ -12226,27 +12228,27 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="R112" t="n">
-        <v>12.4</v>
+        <v>34.7</v>
       </c>
       <c r="S112" t="n">
-        <v>10.1</v>
+        <v>31.3</v>
       </c>
       <c r="T112" t="n">
-        <v>0.53</v>
+        <v>3.22</v>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
       <c r="V112" t="n">
-        <v>23.3</v>
+        <v>10.8</v>
       </c>
       <c r="W112" t="n">
-        <v>6.09</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="113">
@@ -12580,19 +12582,15 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>大統益</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>🌱初拐點</t>
-        </is>
-      </c>
+          <t>矽創</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="n">
         <v>2</v>
       </c>
@@ -12603,12 +12601,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -12617,51 +12615,49 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.5</v>
+        <v>-26.4</v>
       </c>
       <c r="J117" t="n">
-        <v>2.5</v>
+        <v>-21.3</v>
       </c>
       <c r="K117" t="n">
-        <v>22.2</v>
+        <v>15.4</v>
       </c>
       <c r="L117" t="n">
-        <v>24.5</v>
+        <v>24.7</v>
       </c>
       <c r="M117" t="n">
-        <v>9.9</v>
+        <v>39.8</v>
       </c>
       <c r="N117" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="O117" t="inlineStr"/>
+        <v>1.55</v>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="R117" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="S117" t="n">
-        <v>16</v>
-      </c>
-      <c r="T117" t="n">
-        <v>6.56</v>
-      </c>
+        <v>19.9</v>
+      </c>
+      <c r="S117" t="inlineStr"/>
+      <c r="T117" t="inlineStr"/>
       <c r="U117" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
-        </is>
-      </c>
-      <c r="V117" t="n">
-        <v>2.5</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr"/>
       <c r="W117" t="n">
-        <v>5.07</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="118">
@@ -12833,15 +12829,19 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>矽創</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>大統益</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>🌱初拐點</t>
+        </is>
+      </c>
       <c r="D120" t="n">
         <v>2</v>
       </c>
@@ -12852,12 +12852,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -12866,49 +12866,51 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>-26.4</v>
+        <v>1.5</v>
       </c>
       <c r="J120" t="n">
-        <v>-21.3</v>
+        <v>2.5</v>
       </c>
       <c r="K120" t="n">
-        <v>15.4</v>
+        <v>22.2</v>
       </c>
       <c r="L120" t="n">
-        <v>24.7</v>
+        <v>24.5</v>
       </c>
       <c r="M120" t="n">
-        <v>39.8</v>
+        <v>9.9</v>
       </c>
       <c r="N120" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="O120" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+        <v>1.39</v>
+      </c>
+      <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="R120" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="S120" t="inlineStr"/>
-      <c r="T120" t="inlineStr"/>
+        <v>16.4</v>
+      </c>
+      <c r="S120" t="n">
+        <v>16</v>
+      </c>
+      <c r="T120" t="n">
+        <v>6.56</v>
+      </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="V120" t="inlineStr"/>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="V120" t="n">
+        <v>2.5</v>
+      </c>
       <c r="W120" t="n">
-        <v>3.65</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="121">
@@ -13001,55 +13003,59 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>帆宣</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr"/>
+          <t>卜蜂</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>🌱初拐點</t>
+        </is>
+      </c>
       <c r="D122" t="n">
         <v>2</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>17</v>
+        <v>19.7</v>
       </c>
       <c r="J122" t="n">
-        <v>10.8</v>
+        <v>23.3</v>
       </c>
       <c r="K122" t="n">
-        <v>19.2</v>
+        <v>24.9</v>
       </c>
       <c r="L122" t="n">
         <v>19.8</v>
       </c>
       <c r="M122" t="n">
-        <v>64.90000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="N122" t="n">
-        <v>1.94</v>
+        <v>1.24</v>
       </c>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
@@ -13058,27 +13064,27 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="R122" t="n">
-        <v>34.7</v>
+        <v>12.4</v>
       </c>
       <c r="S122" t="n">
-        <v>31.3</v>
+        <v>10.1</v>
       </c>
       <c r="T122" t="n">
-        <v>3.22</v>
+        <v>0.53</v>
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="V122" t="n">
-        <v>10.8</v>
+        <v>23.3</v>
       </c>
       <c r="W122" t="n">
-        <v>1.15</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="123">
@@ -13418,12 +13424,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -13451,56 +13457,60 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.5</v>
+        <v>34.2</v>
       </c>
       <c r="J127" t="n">
-        <v>-4</v>
+        <v>13.4</v>
       </c>
       <c r="K127" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="L127" t="n">
         <v>22.4</v>
       </c>
-      <c r="L127" t="n">
-        <v>21.7</v>
-      </c>
       <c r="M127" t="n">
-        <v>32.1</v>
+        <v>119.8</v>
       </c>
       <c r="N127" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="O127" t="inlineStr"/>
+        <v>0.63</v>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="R127" t="n">
-        <v>38.6</v>
+        <v>192</v>
       </c>
       <c r="S127" t="inlineStr"/>
       <c r="T127" t="inlineStr"/>
       <c r="U127" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-4%)</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
       <c r="V127" t="inlineStr"/>
       <c r="W127" t="n">
-        <v>2.24</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -13528,49 +13538,45 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>34.2</v>
+        <v>3.5</v>
       </c>
       <c r="J128" t="n">
-        <v>13.4</v>
+        <v>-4</v>
       </c>
       <c r="K128" t="n">
-        <v>27.1</v>
+        <v>22.4</v>
       </c>
       <c r="L128" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="M128" t="n">
-        <v>119.8</v>
+        <v>32.1</v>
       </c>
       <c r="N128" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="O128" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+        <v>0.77</v>
+      </c>
+      <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="R128" t="n">
-        <v>192</v>
+        <v>38.6</v>
       </c>
       <c r="S128" t="inlineStr"/>
       <c r="T128" t="inlineStr"/>
       <c r="U128" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 成長為負(-4%)</t>
         </is>
       </c>
       <c r="V128" t="inlineStr"/>
       <c r="W128" t="n">
-        <v>0.53</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="129">
@@ -14662,12 +14668,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>7730</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>嘉晶</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -14681,7 +14687,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -14691,53 +14697,43 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="I143" t="n">
-        <v>-52.3</v>
-      </c>
-      <c r="J143" t="n">
-        <v>-69.09999999999999</v>
-      </c>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
       <c r="K143" t="n">
-        <v>2.4</v>
+        <v>7.3</v>
       </c>
       <c r="L143" t="n">
         <v>6.1</v>
       </c>
-      <c r="M143" t="n">
-        <v>37.3</v>
-      </c>
+      <c r="M143" t="inlineStr"/>
       <c r="N143" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="O143" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+        <v>0.51</v>
+      </c>
+      <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="R143" t="n">
-        <v>339</v>
+        <v>93.3</v>
       </c>
       <c r="S143" t="inlineStr"/>
       <c r="T143" t="inlineStr"/>
       <c r="U143" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 無成長率</t>
         </is>
       </c>
       <c r="V143" t="inlineStr"/>
       <c r="W143" t="n">
-        <v>0.36</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="144">
@@ -14824,12 +14820,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>7730</t>
+          <t>3016</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>嘉晶</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -14843,7 +14839,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -14853,43 +14849,53 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>-52.3</v>
+      </c>
+      <c r="J145" t="n">
+        <v>-69.09999999999999</v>
+      </c>
       <c r="K145" t="n">
-        <v>7.3</v>
+        <v>2.4</v>
       </c>
       <c r="L145" t="n">
         <v>6.1</v>
       </c>
-      <c r="M145" t="inlineStr"/>
+      <c r="M145" t="n">
+        <v>37.3</v>
+      </c>
       <c r="N145" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="O145" t="inlineStr"/>
+        <v>5.23</v>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="R145" t="n">
-        <v>93.3</v>
+        <v>339</v>
       </c>
       <c r="S145" t="inlineStr"/>
       <c r="T145" t="inlineStr"/>
       <c r="U145" t="inlineStr">
         <is>
-          <t>⏸ 無成長率</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
       <c r="V145" t="inlineStr"/>
       <c r="W145" t="n">
-        <v>0.8</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="146">
@@ -15221,12 +15227,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>系統電</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -15254,22 +15260,22 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>-18.4</v>
+        <v>-8.6</v>
       </c>
       <c r="J150" t="n">
-        <v>-49.9</v>
+        <v>-1.6</v>
       </c>
       <c r="K150" t="n">
-        <v>-0.1</v>
+        <v>6.4</v>
       </c>
       <c r="L150" t="n">
-        <v>8.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M150" t="n">
-        <v>15.3</v>
+        <v>12</v>
       </c>
       <c r="N150" t="n">
-        <v>-15.71</v>
+        <v>2.28</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
@@ -15282,10 +15288,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="R150" t="n">
-        <v>275</v>
+        <v>19.8</v>
       </c>
       <c r="S150" t="inlineStr"/>
       <c r="T150" t="inlineStr"/>
@@ -15296,18 +15302,18 @@
       </c>
       <c r="V150" t="inlineStr"/>
       <c r="W150" t="n">
-        <v>0.76</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>漢翔</t>
+          <t>晟銘電</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -15321,7 +15327,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -15331,26 +15337,24 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="I151" t="n">
-        <v>7.2</v>
-      </c>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
       <c r="J151" t="n">
-        <v>-23.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="K151" t="n">
-        <v>4.2</v>
+        <v>17</v>
       </c>
       <c r="L151" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="M151" t="n">
-        <v>18.9</v>
+        <v>1.7</v>
       </c>
       <c r="N151" t="n">
-        <v>3.15</v>
+        <v>0.68</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
@@ -15363,10 +15367,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="R151" t="n">
-        <v>61.9</v>
+        <v>20.2</v>
       </c>
       <c r="S151" t="inlineStr"/>
       <c r="T151" t="inlineStr"/>
@@ -15377,7 +15381,7 @@
       </c>
       <c r="V151" t="inlineStr"/>
       <c r="W151" t="n">
-        <v>1.56</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="152">
@@ -15458,19 +15462,15 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>9933</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>家登</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>🌱初拐點</t>
-        </is>
-      </c>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
       <c r="D153" t="n">
         <v>2</v>
       </c>
@@ -15481,7 +15481,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -15491,26 +15491,26 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>23.6</v>
+        <v>-4.5</v>
       </c>
       <c r="J153" t="n">
-        <v>-5.3</v>
+        <v>-16.5</v>
       </c>
       <c r="K153" t="n">
-        <v>8.199999999999999</v>
+        <v>18.9</v>
       </c>
       <c r="L153" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="M153" t="n">
-        <v>16</v>
+        <v>-2.6</v>
       </c>
       <c r="N153" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
@@ -15523,10 +15523,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="R153" t="n">
-        <v>51.6</v>
+        <v>10.2</v>
       </c>
       <c r="S153" t="inlineStr"/>
       <c r="T153" t="inlineStr"/>
@@ -15537,7 +15537,7 @@
       </c>
       <c r="V153" t="inlineStr"/>
       <c r="W153" t="n">
-        <v>1.37</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="154">
@@ -15875,12 +15875,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -15889,7 +15889,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -15904,26 +15904,26 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>-14.7</v>
+        <v>97</v>
       </c>
       <c r="J158" t="n">
-        <v>-16.6</v>
+        <v>69.2</v>
       </c>
       <c r="K158" t="n">
-        <v>13.1</v>
+        <v>29.3</v>
       </c>
       <c r="L158" t="n">
         <v>17.1</v>
       </c>
       <c r="M158" t="n">
-        <v>35.3</v>
+        <v>116</v>
       </c>
       <c r="N158" t="n">
-        <v>1.95</v>
+        <v>1.02</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
@@ -15936,10 +15936,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="R158" t="n">
-        <v>16.9</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="S158" t="inlineStr"/>
       <c r="T158" t="inlineStr"/>
@@ -15950,7 +15950,7 @@
       </c>
       <c r="V158" t="inlineStr"/>
       <c r="W158" t="n">
-        <v>5.04</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="159">
@@ -16039,12 +16039,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>5493</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>三聯</t>
+          <t>世豐</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -16072,22 +16072,22 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>-2.6</v>
+        <v>-32.9</v>
       </c>
       <c r="J160" t="n">
-        <v>-0.5</v>
+        <v>-45.3</v>
       </c>
       <c r="K160" t="n">
-        <v>13.1</v>
+        <v>4.4</v>
       </c>
       <c r="L160" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="M160" t="n">
         <v>18.6</v>
       </c>
       <c r="N160" t="n">
-        <v>1.03</v>
+        <v>1.53</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
@@ -16100,10 +16100,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="R160" t="n">
-        <v>22.3</v>
+        <v>27.6</v>
       </c>
       <c r="S160" t="inlineStr"/>
       <c r="T160" t="inlineStr"/>
@@ -16114,7 +16114,7 @@
       </c>
       <c r="V160" t="inlineStr"/>
       <c r="W160" t="n">
-        <v>2.94</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="161">
@@ -16699,12 +16699,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>6776</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -16718,12 +16718,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -16732,22 +16732,22 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>-0.4</v>
+        <v>34.2</v>
       </c>
       <c r="J168" t="n">
-        <v>-6.2</v>
+        <v>39.1</v>
       </c>
       <c r="K168" t="n">
-        <v>12.1</v>
+        <v>12.9</v>
       </c>
       <c r="L168" t="n">
         <v>16.5</v>
       </c>
       <c r="M168" t="n">
-        <v>52.1</v>
+        <v>-33.5</v>
       </c>
       <c r="N168" t="n">
-        <v>-2.58</v>
+        <v>0.26</v>
       </c>
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
@@ -16756,21 +16756,27 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="R168" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="S168" t="inlineStr"/>
-      <c r="T168" t="inlineStr"/>
+        <v>63.8</v>
+      </c>
+      <c r="S168" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="T168" t="n">
+        <v>1.63</v>
+      </c>
       <c r="U168" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-6%)</t>
-        </is>
-      </c>
-      <c r="V168" t="inlineStr"/>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="V168" t="n">
+        <v>39.1</v>
+      </c>
       <c r="W168" t="n">
-        <v>5.08</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="169">
@@ -16938,21 +16944,25 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>9931</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>和碩</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr"/>
+          <t>欣高</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>🌱初拐點</t>
+        </is>
+      </c>
       <c r="D171" t="n">
         <v>2</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -16962,7 +16972,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -16971,22 +16981,22 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>-8.6</v>
+        <v>3.4</v>
       </c>
       <c r="J171" t="n">
-        <v>-1.6</v>
+        <v>15.7</v>
       </c>
       <c r="K171" t="n">
-        <v>6.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L171" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="M171" t="n">
-        <v>12</v>
+        <v>13.2</v>
       </c>
       <c r="N171" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="O171" t="inlineStr">
         <is>
@@ -16999,10 +17009,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="R171" t="n">
-        <v>19.8</v>
+        <v>14.8</v>
       </c>
       <c r="S171" t="inlineStr"/>
       <c r="T171" t="inlineStr"/>
@@ -17013,31 +17023,27 @@
       </c>
       <c r="V171" t="inlineStr"/>
       <c r="W171" t="n">
-        <v>4.66</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>欣高</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>🌱初拐點</t>
-        </is>
-      </c>
+          <t>漢翔</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
       <c r="D172" t="n">
         <v>2</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -17047,7 +17053,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -17056,22 +17062,22 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>3.4</v>
+        <v>7.2</v>
       </c>
       <c r="J172" t="n">
-        <v>15.7</v>
+        <v>-23.3</v>
       </c>
       <c r="K172" t="n">
-        <v>8.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="L172" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M172" t="n">
-        <v>13.2</v>
+        <v>18.9</v>
       </c>
       <c r="N172" t="n">
-        <v>2.04</v>
+        <v>3.15</v>
       </c>
       <c r="O172" t="inlineStr">
         <is>
@@ -17084,10 +17090,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="R172" t="n">
-        <v>14.8</v>
+        <v>61.9</v>
       </c>
       <c r="S172" t="inlineStr"/>
       <c r="T172" t="inlineStr"/>
@@ -17098,18 +17104,18 @@
       </c>
       <c r="V172" t="inlineStr"/>
       <c r="W172" t="n">
-        <v>5.13</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>振宇五金</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -17137,22 +17143,22 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>-14.9</v>
+        <v>-23.3</v>
       </c>
       <c r="J173" t="n">
-        <v>-1.8</v>
+        <v>-9</v>
       </c>
       <c r="K173" t="n">
-        <v>7.9</v>
+        <v>6.6</v>
       </c>
       <c r="L173" t="n">
-        <v>9.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M173" t="n">
-        <v>10.9</v>
+        <v>36.5</v>
       </c>
       <c r="N173" t="n">
-        <v>4.84</v>
+        <v>-2.99</v>
       </c>
       <c r="O173" t="inlineStr">
         <is>
@@ -17165,10 +17171,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="R173" t="n">
-        <v>26.6</v>
+        <v>25.8</v>
       </c>
       <c r="S173" t="inlineStr"/>
       <c r="T173" t="inlineStr"/>
@@ -17179,18 +17185,18 @@
       </c>
       <c r="V173" t="inlineStr"/>
       <c r="W173" t="n">
-        <v>3.92</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -17204,12 +17210,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -17218,60 +17224,62 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>-23.3</v>
+        <v>2</v>
       </c>
       <c r="J174" t="n">
-        <v>-9</v>
+        <v>2</v>
       </c>
       <c r="K174" t="n">
-        <v>6.6</v>
+        <v>9.9</v>
       </c>
       <c r="L174" t="n">
-        <v>9.199999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="M174" t="n">
-        <v>36.5</v>
+        <v>5.4</v>
       </c>
       <c r="N174" t="n">
-        <v>-2.99</v>
-      </c>
-      <c r="O174" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+        <v>1.85</v>
+      </c>
+      <c r="O174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="R174" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="S174" t="inlineStr"/>
-      <c r="T174" t="inlineStr"/>
+        <v>28.7</v>
+      </c>
+      <c r="S174" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="T174" t="n">
+        <v>14.25</v>
+      </c>
       <c r="U174" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="V174" t="inlineStr"/>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="V174" t="n">
+        <v>2</v>
+      </c>
       <c r="W174" t="n">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2947</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>振宇五金</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -17285,12 +17293,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -17299,51 +17307,49 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2</v>
+        <v>-14.9</v>
       </c>
       <c r="J175" t="n">
-        <v>2</v>
+        <v>-1.8</v>
       </c>
       <c r="K175" t="n">
-        <v>9.9</v>
+        <v>7.9</v>
       </c>
       <c r="L175" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="M175" t="n">
-        <v>5.4</v>
+        <v>10.9</v>
       </c>
       <c r="N175" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="O175" t="inlineStr"/>
+        <v>4.84</v>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="R175" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="S175" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="T175" t="n">
-        <v>14.25</v>
-      </c>
+        <v>26.6</v>
+      </c>
+      <c r="S175" t="inlineStr"/>
+      <c r="T175" t="inlineStr"/>
       <c r="U175" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
-        </is>
-      </c>
-      <c r="V175" t="n">
-        <v>2</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr"/>
       <c r="W175" t="n">
-        <v>3.6</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="176">
@@ -17752,12 +17758,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>晟銘電</t>
+          <t>系統電</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -17771,7 +17777,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -17781,24 +17787,26 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr"/>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I181" t="n">
+        <v>-18.4</v>
+      </c>
       <c r="J181" t="n">
-        <v>65.59999999999999</v>
+        <v>-49.9</v>
       </c>
       <c r="K181" t="n">
-        <v>17</v>
+        <v>-0.1</v>
       </c>
       <c r="L181" t="n">
         <v>8.6</v>
       </c>
       <c r="M181" t="n">
-        <v>1.7</v>
+        <v>15.3</v>
       </c>
       <c r="N181" t="n">
-        <v>0.68</v>
+        <v>-15.71</v>
       </c>
       <c r="O181" t="inlineStr">
         <is>
@@ -17811,10 +17819,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="R181" t="n">
-        <v>20.2</v>
+        <v>275</v>
       </c>
       <c r="S181" t="inlineStr"/>
       <c r="T181" t="inlineStr"/>
@@ -17825,18 +17833,18 @@
       </c>
       <c r="V181" t="inlineStr"/>
       <c r="W181" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>台星科</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -17850,12 +17858,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -17864,60 +17872,56 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0</v>
+        <v>17.3</v>
       </c>
       <c r="J182" t="n">
-        <v>44.7</v>
+        <v>-6.6</v>
       </c>
       <c r="K182" t="n">
-        <v>14.4</v>
+        <v>12.9</v>
       </c>
       <c r="L182" t="n">
-        <v>12.3</v>
+        <v>12.8</v>
       </c>
       <c r="M182" t="n">
-        <v>9.300000000000001</v>
+        <v>22.1</v>
       </c>
       <c r="N182" t="n">
-        <v>-0.64</v>
-      </c>
-      <c r="O182" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+        <v>1.67</v>
+      </c>
+      <c r="O182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="R182" t="n">
-        <v>14.1</v>
+        <v>34</v>
       </c>
       <c r="S182" t="inlineStr"/>
       <c r="T182" t="inlineStr"/>
       <c r="U182" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 成長為負(-7%)</t>
         </is>
       </c>
       <c r="V182" t="inlineStr"/>
       <c r="W182" t="n">
-        <v>5.33</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>台星科</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -17931,12 +17935,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -17945,59 +17949,67 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>17.3</v>
+        <v>0</v>
       </c>
       <c r="J183" t="n">
-        <v>-6.6</v>
+        <v>44.7</v>
       </c>
       <c r="K183" t="n">
-        <v>12.9</v>
+        <v>14.4</v>
       </c>
       <c r="L183" t="n">
-        <v>12.8</v>
+        <v>12.3</v>
       </c>
       <c r="M183" t="n">
-        <v>22.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="N183" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O183" t="inlineStr"/>
+        <v>-0.64</v>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="R183" t="n">
-        <v>34</v>
+        <v>14.1</v>
       </c>
       <c r="S183" t="inlineStr"/>
       <c r="T183" t="inlineStr"/>
       <c r="U183" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-7%)</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
       <c r="V183" t="inlineStr"/>
       <c r="W183" t="n">
-        <v>2.12</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>台半</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr"/>
+          <t>家登</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>🌱初拐點</t>
+        </is>
+      </c>
       <c r="D184" t="n">
         <v>2</v>
       </c>
@@ -18022,22 +18034,22 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>-12.5</v>
+        <v>23.6</v>
       </c>
       <c r="J184" t="n">
-        <v>-30.8</v>
+        <v>-5.3</v>
       </c>
       <c r="K184" t="n">
-        <v>10.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L184" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="M184" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="N184" t="n">
-        <v>2.14</v>
+        <v>1.4</v>
       </c>
       <c r="O184" t="inlineStr">
         <is>
@@ -18050,10 +18062,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="R184" t="n">
-        <v>58</v>
+        <v>51.6</v>
       </c>
       <c r="S184" t="inlineStr"/>
       <c r="T184" t="inlineStr"/>
@@ -18064,18 +18076,18 @@
       </c>
       <c r="V184" t="inlineStr"/>
       <c r="W184" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>9933</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>中鼎</t>
+          <t>台半</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -18089,7 +18101,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -18099,26 +18111,26 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="I185" t="n">
-        <v>-4.5</v>
+        <v>-12.5</v>
       </c>
       <c r="J185" t="n">
-        <v>-16.5</v>
+        <v>-30.8</v>
       </c>
       <c r="K185" t="n">
-        <v>18.9</v>
+        <v>10.4</v>
       </c>
       <c r="L185" t="n">
-        <v>12.6</v>
+        <v>13.5</v>
       </c>
       <c r="M185" t="n">
-        <v>-2.6</v>
+        <v>11.8</v>
       </c>
       <c r="N185" t="n">
-        <v>3.9</v>
+        <v>2.14</v>
       </c>
       <c r="O185" t="inlineStr">
         <is>
@@ -18131,10 +18143,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="R185" t="n">
-        <v>10.2</v>
+        <v>58</v>
       </c>
       <c r="S185" t="inlineStr"/>
       <c r="T185" t="inlineStr"/>
@@ -18145,7 +18157,7 @@
       </c>
       <c r="V185" t="inlineStr"/>
       <c r="W185" t="n">
-        <v>2.29</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="186">
@@ -18319,12 +18331,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -18333,7 +18345,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -18343,7 +18355,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -18352,22 +18364,22 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>18.4</v>
+        <v>-19.8</v>
       </c>
       <c r="J188" t="n">
-        <v>56</v>
+        <v>-23.7</v>
       </c>
       <c r="K188" t="n">
-        <v>10.7</v>
+        <v>5.4</v>
       </c>
       <c r="L188" t="n">
-        <v>11.4</v>
+        <v>10.9</v>
       </c>
       <c r="M188" t="n">
-        <v>49.9</v>
+        <v>19.1</v>
       </c>
       <c r="N188" t="n">
-        <v>1.73</v>
+        <v>1.05</v>
       </c>
       <c r="O188" t="inlineStr">
         <is>
@@ -18380,10 +18392,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R188" t="n">
-        <v>165.8</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="S188" t="inlineStr"/>
       <c r="T188" t="inlineStr"/>
@@ -18394,18 +18406,18 @@
       </c>
       <c r="V188" t="inlineStr"/>
       <c r="W188" t="n">
-        <v>0.18</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -18414,7 +18426,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -18424,7 +18436,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -18433,22 +18445,22 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>-19.8</v>
+        <v>18.4</v>
       </c>
       <c r="J189" t="n">
-        <v>-23.7</v>
+        <v>56</v>
       </c>
       <c r="K189" t="n">
-        <v>5.4</v>
+        <v>10.7</v>
       </c>
       <c r="L189" t="n">
-        <v>10.9</v>
+        <v>11.4</v>
       </c>
       <c r="M189" t="n">
-        <v>19.1</v>
+        <v>49.9</v>
       </c>
       <c r="N189" t="n">
-        <v>1.05</v>
+        <v>1.73</v>
       </c>
       <c r="O189" t="inlineStr">
         <is>
@@ -18461,10 +18473,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="R189" t="n">
-        <v>75.40000000000001</v>
+        <v>165.8</v>
       </c>
       <c r="S189" t="inlineStr"/>
       <c r="T189" t="inlineStr"/>
@@ -18475,7 +18487,7 @@
       </c>
       <c r="V189" t="inlineStr"/>
       <c r="W189" t="n">
-        <v>1.09</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="190">
@@ -20721,12 +20733,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>3715</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>定穎投控</t>
+          <t>三福化</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -20735,12 +20747,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -20754,20 +20766,22 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>-13.4</v>
-      </c>
-      <c r="J218" t="inlineStr"/>
+        <v>-13.8</v>
+      </c>
+      <c r="J218" t="n">
+        <v>-24</v>
+      </c>
       <c r="K218" t="n">
-        <v>2</v>
+        <v>5.9</v>
       </c>
       <c r="L218" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="M218" t="n">
-        <v>69.09999999999999</v>
+        <v>-5.8</v>
       </c>
       <c r="N218" t="n">
-        <v>-1.6</v>
+        <v>2.91</v>
       </c>
       <c r="O218" t="inlineStr">
         <is>
@@ -20780,10 +20794,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="R218" t="n">
-        <v>194.5</v>
+        <v>38.4</v>
       </c>
       <c r="S218" t="inlineStr"/>
       <c r="T218" t="inlineStr"/>
@@ -20794,18 +20808,18 @@
       </c>
       <c r="V218" t="inlineStr"/>
       <c r="W218" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>2453</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>三福化</t>
+          <t>凌群</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -20814,7 +20828,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -20829,53 +20843,55 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I219" t="n">
-        <v>-13.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J219" t="n">
-        <v>-24</v>
+        <v>7.6</v>
       </c>
       <c r="K219" t="n">
-        <v>5.9</v>
+        <v>15.2</v>
       </c>
       <c r="L219" t="n">
-        <v>12.2</v>
+        <v>13.1</v>
       </c>
       <c r="M219" t="n">
-        <v>-5.8</v>
+        <v>6.8</v>
       </c>
       <c r="N219" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="O219" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="O219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="R219" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="S219" t="inlineStr"/>
-      <c r="T219" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="S219" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="T219" t="n">
+        <v>2.36</v>
+      </c>
       <c r="U219" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="V219" t="inlineStr"/>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="V219" t="n">
+        <v>7.6</v>
+      </c>
       <c r="W219" t="n">
-        <v>2.67</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="220">
@@ -20962,12 +20978,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -20981,7 +20997,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -20991,53 +21007,53 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="I221" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="J221" t="inlineStr"/>
+        <v>-43.2</v>
+      </c>
+      <c r="J221" t="n">
+        <v>-39.2</v>
+      </c>
       <c r="K221" t="n">
-        <v>13.8</v>
+        <v>7.6</v>
       </c>
       <c r="L221" t="n">
-        <v>12.9</v>
+        <v>11.7</v>
       </c>
       <c r="M221" t="n">
-        <v>-5.3</v>
+        <v>31.6</v>
       </c>
       <c r="N221" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="O221" t="inlineStr"/>
+        <v>0.36</v>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="R221" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="S221" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="T221" t="n">
-        <v>1.54</v>
-      </c>
+        <v>86.5</v>
+      </c>
+      <c r="S221" t="inlineStr"/>
+      <c r="T221" t="inlineStr"/>
       <c r="U221" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
-        </is>
-      </c>
-      <c r="V221" t="n">
-        <v>17.7</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr"/>
       <c r="W221" t="n">
-        <v>3.29</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="222">
@@ -21126,12 +21142,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>定穎投控</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -21159,22 +21175,20 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>-43.2</v>
-      </c>
-      <c r="J223" t="n">
-        <v>-39.2</v>
-      </c>
+        <v>-13.4</v>
+      </c>
+      <c r="J223" t="inlineStr"/>
       <c r="K223" t="n">
-        <v>7.6</v>
+        <v>2</v>
       </c>
       <c r="L223" t="n">
-        <v>11.7</v>
+        <v>12.1</v>
       </c>
       <c r="M223" t="n">
-        <v>31.6</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="N223" t="n">
-        <v>0.36</v>
+        <v>-1.6</v>
       </c>
       <c r="O223" t="inlineStr">
         <is>
@@ -21187,10 +21201,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="R223" t="n">
-        <v>86.5</v>
+        <v>194.5</v>
       </c>
       <c r="S223" t="inlineStr"/>
       <c r="T223" t="inlineStr"/>
@@ -21201,7 +21215,7 @@
       </c>
       <c r="V223" t="inlineStr"/>
       <c r="W223" t="n">
-        <v>0.4</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="224">
@@ -21288,12 +21302,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>凌群</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -21321,22 +21335,20 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J225" t="n">
-        <v>7.6</v>
-      </c>
+        <v>17.7</v>
+      </c>
+      <c r="J225" t="inlineStr"/>
       <c r="K225" t="n">
-        <v>15.2</v>
+        <v>13.8</v>
       </c>
       <c r="L225" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="M225" t="n">
-        <v>6.8</v>
+        <v>-5.3</v>
       </c>
       <c r="N225" t="n">
-        <v>0.9</v>
+        <v>0.58</v>
       </c>
       <c r="O225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
@@ -21345,27 +21357,27 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="R225" t="n">
-        <v>18</v>
+        <v>27.2</v>
       </c>
       <c r="S225" t="n">
-        <v>16.7</v>
+        <v>23.1</v>
       </c>
       <c r="T225" t="n">
-        <v>2.36</v>
+        <v>1.54</v>
       </c>
       <c r="U225" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
       <c r="V225" t="n">
-        <v>7.6</v>
+        <v>17.7</v>
       </c>
       <c r="W225" t="n">
-        <v>3.61</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="226">
@@ -23831,67 +23843,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>EPS加速</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>5年均ROE</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ROE回升</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>PBR便宜</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
@@ -23912,67 +23924,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>EPS加速</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>5年均ROE</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ROE回升</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>PBR便宜</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
@@ -24447,20 +24459,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>8.1</v>
       </c>
       <c r="E12" t="n">
-        <v>20.6</v>
+        <v>12.1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -24483,29 +24495,29 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>16.8</v>
+        <v>20.2</v>
       </c>
       <c r="M12" t="n">
-        <v>3.43</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>10.6</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>38.1</v>
+        <v>20.6</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -24528,10 +24540,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>17.3</v>
+        <v>16.8</v>
       </c>
       <c r="M13" t="n">
-        <v>3.55</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="14">
@@ -24582,20 +24594,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>-9.1</v>
+        <v>-7.1</v>
       </c>
       <c r="E15" t="n">
-        <v>39.9</v>
+        <v>21.1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -24618,29 +24630,29 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.03</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>8.1</v>
+        <v>-9.5</v>
       </c>
       <c r="E16" t="n">
-        <v>12.1</v>
+        <v>33.2</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -24663,29 +24675,29 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>20.2</v>
+        <v>16.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.27</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>-9.5</v>
+        <v>10.6</v>
       </c>
       <c r="E17" t="n">
-        <v>33.2</v>
+        <v>38.1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -24708,29 +24720,29 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>16.6</v>
+        <v>17.3</v>
       </c>
       <c r="M17" t="n">
-        <v>3.08</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>-7.1</v>
+        <v>-9.1</v>
       </c>
       <c r="E18" t="n">
-        <v>21.1</v>
+        <v>39.9</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -24753,10 +24765,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>3.03</v>
       </c>
     </row>
   </sheetData>

--- a/data/台股_拐點掃描.xlsx
+++ b/data/台股_拐點掃描.xlsx
@@ -4981,25 +4981,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>建準</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>🔥強拐點</t>
-        </is>
-      </c>
+          <t>高技</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="n">
         <v>3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -5009,7 +5005,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -5018,71 +5014,73 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>46.8</v>
+        <v>31.4</v>
       </c>
       <c r="J24" t="n">
-        <v>22.3</v>
+        <v>51.1</v>
       </c>
       <c r="K24" t="n">
-        <v>20.7</v>
+        <v>33.3</v>
       </c>
       <c r="L24" t="n">
         <v>19.9</v>
       </c>
       <c r="M24" t="n">
-        <v>14.9</v>
+        <v>58.3</v>
       </c>
       <c r="N24" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="O24" t="inlineStr"/>
+        <v>0.92</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="R24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="S24" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0.78</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
-        </is>
-      </c>
-      <c r="V24" t="n">
-        <v>22.3</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr"/>
       <c r="W24" t="n">
-        <v>3.49</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>高技</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>建準</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>🔥強拐點</t>
+        </is>
+      </c>
       <c r="D25" t="n">
         <v>3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5092,7 +5090,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -5101,49 +5099,51 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>31.4</v>
+        <v>46.8</v>
       </c>
       <c r="J25" t="n">
-        <v>51.1</v>
+        <v>22.3</v>
       </c>
       <c r="K25" t="n">
-        <v>33.3</v>
+        <v>20.7</v>
       </c>
       <c r="L25" t="n">
         <v>19.9</v>
       </c>
       <c r="M25" t="n">
-        <v>58.3</v>
+        <v>14.9</v>
       </c>
       <c r="N25" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+        <v>1.16</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="R25" t="n">
-        <v>21</v>
-      </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
+        <v>17.5</v>
+      </c>
+      <c r="S25" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.78</v>
+      </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr"/>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>22.3</v>
+      </c>
       <c r="W25" t="n">
-        <v>2.24</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="26">
@@ -5803,12 +5803,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5832,55 +5832,53 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>10.4</v>
+        <v>5.7</v>
       </c>
       <c r="J34" t="n">
-        <v>10.9</v>
+        <v>6</v>
       </c>
       <c r="K34" t="n">
-        <v>19.8</v>
+        <v>14.1</v>
       </c>
       <c r="L34" t="n">
         <v>18</v>
       </c>
       <c r="M34" t="n">
-        <v>0.6</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="O34" t="inlineStr"/>
+        <v>1.43</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="R34" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="S34" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1.56</v>
-      </c>
+        <v>83.40000000000001</v>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
-        </is>
-      </c>
-      <c r="V34" t="n">
-        <v>10.9</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="n">
-        <v>4.47</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="35">
@@ -5967,12 +5965,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6683</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -5991,31 +5989,31 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>45.7</v>
+        <v>-0.1</v>
       </c>
       <c r="J36" t="n">
-        <v>37.5</v>
+        <v>0.9</v>
       </c>
       <c r="K36" t="n">
-        <v>23.4</v>
+        <v>16.8</v>
       </c>
       <c r="L36" t="n">
         <v>19</v>
       </c>
       <c r="M36" t="n">
-        <v>57.8</v>
+        <v>12.3</v>
       </c>
       <c r="N36" t="n">
-        <v>0.63</v>
+        <v>1.45</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
@@ -6024,16 +6022,16 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="R36" t="n">
-        <v>167.3</v>
+        <v>89.7</v>
       </c>
       <c r="S36" t="n">
-        <v>121.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="T36" t="n">
-        <v>4.46</v>
+        <v>97.01000000000001</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -6041,10 +6039,10 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>37.5</v>
+        <v>0.9</v>
       </c>
       <c r="W36" t="n">
-        <v>0.34</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -6131,12 +6129,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6683</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -6155,31 +6153,31 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>-0.1</v>
+        <v>45.7</v>
       </c>
       <c r="J38" t="n">
-        <v>0.9</v>
+        <v>37.5</v>
       </c>
       <c r="K38" t="n">
-        <v>16.8</v>
+        <v>23.4</v>
       </c>
       <c r="L38" t="n">
         <v>19</v>
       </c>
       <c r="M38" t="n">
-        <v>12.3</v>
+        <v>57.8</v>
       </c>
       <c r="N38" t="n">
-        <v>1.45</v>
+        <v>0.63</v>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
@@ -6188,16 +6186,16 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="R38" t="n">
-        <v>89.7</v>
+        <v>167.3</v>
       </c>
       <c r="S38" t="n">
-        <v>88.90000000000001</v>
+        <v>121.7</v>
       </c>
       <c r="T38" t="n">
-        <v>97.01000000000001</v>
+        <v>4.46</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -6205,24 +6203,28 @@
         </is>
       </c>
       <c r="V38" t="n">
-        <v>0.9</v>
+        <v>37.5</v>
       </c>
       <c r="W38" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>王品</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>八方雲集</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>🔥強拐點</t>
+        </is>
+      </c>
       <c r="D39" t="n">
         <v>3</v>
       </c>
@@ -6246,66 +6248,66 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="n">
+        <v>10.1</v>
+      </c>
       <c r="J39" t="n">
-        <v>45.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>33.6</v>
+        <v>22.1</v>
       </c>
       <c r="L39" t="n">
         <v>17.9</v>
       </c>
       <c r="M39" t="n">
-        <v>15</v>
+        <v>13.3</v>
       </c>
       <c r="N39" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+        <v>1.93</v>
+      </c>
+      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="R39" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
+        <v>14.1</v>
+      </c>
+      <c r="S39" t="n">
+        <v>13</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.62</v>
+      </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr"/>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="V39" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="W39" t="n">
-        <v>6.54</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2727</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>八方雲集</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>🔥強拐點</t>
-        </is>
-      </c>
+          <t>王品</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="n">
         <v>3</v>
       </c>
@@ -6329,52 +6331,48 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I40" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>8.699999999999999</v>
+        <v>45.9</v>
       </c>
       <c r="K40" t="n">
-        <v>22.1</v>
+        <v>33.6</v>
       </c>
       <c r="L40" t="n">
         <v>17.9</v>
       </c>
       <c r="M40" t="n">
-        <v>13.3</v>
+        <v>15</v>
       </c>
       <c r="N40" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="O40" t="inlineStr"/>
+        <v>2.56</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="R40" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="S40" t="n">
-        <v>13</v>
-      </c>
-      <c r="T40" t="n">
-        <v>1.62</v>
-      </c>
+        <v>14.8</v>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
-        </is>
-      </c>
-      <c r="V40" t="n">
-        <v>8.699999999999999</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr"/>
       <c r="W40" t="n">
-        <v>6.32</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="41">
@@ -6791,12 +6789,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -6810,7 +6808,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6820,53 +6818,55 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5.7</v>
+        <v>10.4</v>
       </c>
       <c r="J46" t="n">
-        <v>6</v>
+        <v>10.9</v>
       </c>
       <c r="K46" t="n">
-        <v>14.1</v>
+        <v>19.8</v>
       </c>
       <c r="L46" t="n">
         <v>18</v>
       </c>
       <c r="M46" t="n">
-        <v>74.59999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="N46" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+        <v>1.28</v>
+      </c>
+      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="R46" t="n">
-        <v>83.40000000000001</v>
-      </c>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
+        <v>17.1</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1.56</v>
+      </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr"/>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="V46" t="n">
+        <v>10.9</v>
+      </c>
       <c r="W46" t="n">
-        <v>0.87</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="47">
@@ -7206,19 +7206,15 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6712</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>長聖</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>🔥強拐點</t>
-        </is>
-      </c>
+          <t>宜鼎</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="n">
         <v>3</v>
       </c>
@@ -7234,31 +7230,31 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>-4.6</v>
+        <v>3.6</v>
       </c>
       <c r="J51" t="n">
-        <v>19</v>
+        <v>0.1</v>
       </c>
       <c r="K51" t="n">
-        <v>16.7</v>
+        <v>48.8</v>
       </c>
       <c r="L51" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="M51" t="n">
-        <v>25</v>
+        <v>640.8</v>
       </c>
       <c r="N51" t="n">
-        <v>1.16</v>
+        <v>-0.36</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -7271,10 +7267,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="R51" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
@@ -7285,7 +7281,7 @@
       </c>
       <c r="V51" t="inlineStr"/>
       <c r="W51" t="n">
-        <v>2.81</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="52">
@@ -7374,15 +7370,19 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>6712</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>宜鼎</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>長聖</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>🔥強拐點</t>
+        </is>
+      </c>
       <c r="D53" t="n">
         <v>3</v>
       </c>
@@ -7398,31 +7398,31 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.6</v>
+        <v>-4.6</v>
       </c>
       <c r="J53" t="n">
-        <v>0.1</v>
+        <v>19</v>
       </c>
       <c r="K53" t="n">
-        <v>48.8</v>
+        <v>16.7</v>
       </c>
       <c r="L53" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="M53" t="n">
-        <v>640.8</v>
+        <v>25</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.36</v>
+        <v>1.16</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -7435,10 +7435,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="R53" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
@@ -7449,7 +7449,7 @@
       </c>
       <c r="V53" t="inlineStr"/>
       <c r="W53" t="n">
-        <v>0.87</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="54">
@@ -7866,15 +7866,19 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>臺慶科</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>漢來美食</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>🔥強拐點</t>
+        </is>
+      </c>
       <c r="D59" t="n">
         <v>3</v>
       </c>
@@ -7890,58 +7894,60 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>-3.9</v>
+        <v>49.8</v>
       </c>
       <c r="J59" t="n">
-        <v>0.5</v>
+        <v>48.7</v>
       </c>
       <c r="K59" t="n">
-        <v>10.8</v>
+        <v>19.2</v>
       </c>
       <c r="L59" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="M59" t="n">
-        <v>37.8</v>
+        <v>10.9</v>
       </c>
       <c r="N59" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+        <v>2.54</v>
+      </c>
+      <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>97</v>
+        <v>5</v>
       </c>
       <c r="R59" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr"/>
+        <v>14.7</v>
+      </c>
+      <c r="S59" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0.3</v>
+      </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr"/>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V59" t="n">
+        <v>48.7</v>
+      </c>
       <c r="W59" t="n">
-        <v>1.61</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="60">
@@ -8609,21 +8615,25 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>文曄</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>寶島科</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>🔥強拐點</t>
+        </is>
+      </c>
       <c r="D68" t="n">
         <v>3</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -8638,26 +8648,26 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.9</v>
+        <v>7.3</v>
       </c>
       <c r="J68" t="n">
-        <v>10.3</v>
+        <v>31.3</v>
       </c>
       <c r="K68" t="n">
-        <v>15.8</v>
+        <v>9.1</v>
       </c>
       <c r="L68" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="M68" t="n">
-        <v>152.7</v>
+        <v>17.4</v>
       </c>
       <c r="N68" t="n">
-        <v>-0.2</v>
+        <v>2.38</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -8670,10 +8680,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="R68" t="n">
-        <v>15.5</v>
+        <v>16.6</v>
       </c>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
@@ -8684,7 +8694,7 @@
       </c>
       <c r="V68" t="inlineStr"/>
       <c r="W68" t="n">
-        <v>3.47</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="69">
@@ -9166,12 +9176,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>亞昕</t>
+          <t>豐達科</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -9190,31 +9200,29 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="I75" t="n">
-        <v>43.5</v>
-      </c>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="n">
-        <v>67.3</v>
+        <v>27.1</v>
       </c>
       <c r="K75" t="n">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="L75" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="M75" t="n">
-        <v>211.3</v>
+        <v>56.2</v>
       </c>
       <c r="N75" t="n">
-        <v>-3.1</v>
+        <v>0.04</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -9227,10 +9235,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="R75" t="n">
-        <v>15.3</v>
+        <v>23.3</v>
       </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
@@ -9241,7 +9249,7 @@
       </c>
       <c r="V75" t="inlineStr"/>
       <c r="W75" t="n">
-        <v>12.47</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="76">
@@ -9415,21 +9423,25 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>豐達科</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+          <t>台汽電</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>🔥強拐點</t>
+        </is>
+      </c>
       <c r="D78" t="n">
         <v>3</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -9439,7 +9451,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -9447,48 +9459,52 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="n">
+        <v>12.5</v>
+      </c>
       <c r="J78" t="n">
-        <v>27.1</v>
+        <v>16.7</v>
       </c>
       <c r="K78" t="n">
-        <v>9.4</v>
+        <v>11.3</v>
       </c>
       <c r="L78" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M78" t="n">
-        <v>56.2</v>
+        <v>768.2</v>
       </c>
       <c r="N78" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+        <v>1.15</v>
+      </c>
+      <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="R78" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="S78" t="inlineStr"/>
-      <c r="T78" t="inlineStr"/>
+        <v>19.4</v>
+      </c>
+      <c r="S78" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1.16</v>
+      </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr"/>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="V78" t="n">
+        <v>16.7</v>
+      </c>
       <c r="W78" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="79">
@@ -9577,25 +9593,21 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>台汽電</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>🔥強拐點</t>
-        </is>
-      </c>
+          <t>亞昕</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="n">
         <v>3</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -9610,55 +9622,53 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>12.5</v>
+        <v>43.5</v>
       </c>
       <c r="J80" t="n">
-        <v>16.7</v>
+        <v>67.3</v>
       </c>
       <c r="K80" t="n">
-        <v>11.3</v>
+        <v>6.4</v>
       </c>
       <c r="L80" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="M80" t="n">
-        <v>768.2</v>
+        <v>211.3</v>
       </c>
       <c r="N80" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="O80" t="inlineStr"/>
+        <v>-3.1</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="R80" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="S80" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="T80" t="n">
-        <v>1.16</v>
-      </c>
+        <v>15.3</v>
+      </c>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
-        </is>
-      </c>
-      <c r="V80" t="n">
-        <v>16.7</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr"/>
       <c r="W80" t="n">
-        <v>3.05</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="81">
@@ -9741,19 +9751,15 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>漢來美食</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>🔥強拐點</t>
-        </is>
-      </c>
+          <t>臺慶科</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="n">
         <v>3</v>
       </c>
@@ -9769,71 +9775,69 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>49.8</v>
+        <v>-3.9</v>
       </c>
       <c r="J82" t="n">
-        <v>48.7</v>
+        <v>0.5</v>
       </c>
       <c r="K82" t="n">
-        <v>19.2</v>
+        <v>10.8</v>
       </c>
       <c r="L82" t="n">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
       <c r="M82" t="n">
-        <v>10.9</v>
+        <v>37.8</v>
       </c>
       <c r="N82" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="O82" t="inlineStr"/>
+        <v>0.76</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>5</v>
+        <v>97</v>
       </c>
       <c r="R82" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="S82" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="T82" t="n">
-        <v>0.3</v>
-      </c>
+        <v>29.8</v>
+      </c>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
-        </is>
-      </c>
-      <c r="V82" t="n">
-        <v>48.7</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr"/>
       <c r="W82" t="n">
-        <v>4.71</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>6449</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -9852,71 +9856,69 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>20.7</v>
+        <v>-3.3</v>
       </c>
       <c r="J83" t="n">
-        <v>24.4</v>
+        <v>-1.4</v>
       </c>
       <c r="K83" t="n">
-        <v>11.7</v>
+        <v>15.5</v>
       </c>
       <c r="L83" t="n">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="M83" t="n">
-        <v>12.3</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="N83" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="O83" t="inlineStr"/>
+        <v>-0.89</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R83" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="S83" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="T83" t="n">
-        <v>2.23</v>
-      </c>
+        <v>14.2</v>
+      </c>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
-        </is>
-      </c>
-      <c r="V83" t="n">
-        <v>24.4</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr"/>
       <c r="W83" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>6449</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -9935,82 +9937,80 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>-3.3</v>
+        <v>20.7</v>
       </c>
       <c r="J84" t="n">
-        <v>-1.4</v>
+        <v>24.4</v>
       </c>
       <c r="K84" t="n">
-        <v>15.5</v>
+        <v>11.7</v>
       </c>
       <c r="L84" t="n">
-        <v>12.1</v>
+        <v>12.5</v>
       </c>
       <c r="M84" t="n">
-        <v>82.90000000000001</v>
+        <v>12.3</v>
       </c>
       <c r="N84" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+        <v>1.24</v>
+      </c>
+      <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="R84" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="S84" t="inlineStr"/>
-      <c r="T84" t="inlineStr"/>
+        <v>54.5</v>
+      </c>
+      <c r="S84" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="T84" t="n">
+        <v>2.23</v>
+      </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr"/>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="V84" t="n">
+        <v>24.4</v>
+      </c>
       <c r="W84" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5312</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>寶島科</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>🔥強拐點</t>
-        </is>
-      </c>
+          <t>文曄</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="n">
         <v>3</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -10025,26 +10025,26 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>7.3</v>
+        <v>3.9</v>
       </c>
       <c r="J85" t="n">
-        <v>31.3</v>
+        <v>10.3</v>
       </c>
       <c r="K85" t="n">
-        <v>9.1</v>
+        <v>15.8</v>
       </c>
       <c r="L85" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="M85" t="n">
-        <v>17.4</v>
+        <v>152.7</v>
       </c>
       <c r="N85" t="n">
-        <v>2.38</v>
+        <v>-0.2</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -10057,10 +10057,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="R85" t="n">
-        <v>16.6</v>
+        <v>15.5</v>
       </c>
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr"/>
@@ -10071,18 +10071,18 @@
       </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" t="n">
-        <v>6.66</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>亞光</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -10091,7 +10091,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -10101,7 +10101,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -10110,22 +10110,22 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>5.4</v>
+        <v>-14.6</v>
       </c>
       <c r="J86" t="n">
-        <v>26.1</v>
+        <v>-5.5</v>
       </c>
       <c r="K86" t="n">
-        <v>13.1</v>
+        <v>12.4</v>
       </c>
       <c r="L86" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="M86" t="n">
-        <v>16.2</v>
+        <v>21.3</v>
       </c>
       <c r="N86" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
@@ -10138,10 +10138,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="R86" t="n">
-        <v>23.8</v>
+        <v>115.6</v>
       </c>
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="inlineStr"/>
@@ -10152,18 +10152,18 @@
       </c>
       <c r="V86" t="inlineStr"/>
       <c r="W86" t="n">
-        <v>2.82</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>世禾</t>
+          <t>亞光</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -10172,7 +10172,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -10187,66 +10187,64 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="J87" t="n">
-        <v>9.300000000000001</v>
+        <v>26.1</v>
       </c>
       <c r="K87" t="n">
-        <v>10</v>
+        <v>13.1</v>
       </c>
       <c r="L87" t="n">
         <v>10.5</v>
       </c>
       <c r="M87" t="n">
-        <v>21.5</v>
+        <v>16.2</v>
       </c>
       <c r="N87" t="n">
-        <v>-0.79</v>
-      </c>
-      <c r="O87" t="inlineStr"/>
+        <v>0.97</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="R87" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="S87" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="T87" t="n">
-        <v>2.63</v>
-      </c>
+        <v>23.8</v>
+      </c>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
       <c r="U87" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
-        </is>
-      </c>
-      <c r="V87" t="n">
-        <v>9.300000000000001</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr"/>
       <c r="W87" t="n">
-        <v>2.26</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>世禾</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -10255,7 +10253,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -10270,26 +10268,26 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>7.3</v>
+        <v>3.9</v>
       </c>
       <c r="J88" t="n">
-        <v>12.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K88" t="n">
-        <v>13.6</v>
+        <v>10</v>
       </c>
       <c r="L88" t="n">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
       <c r="M88" t="n">
-        <v>35.3</v>
+        <v>21.5</v>
       </c>
       <c r="N88" t="n">
-        <v>1.09</v>
+        <v>-0.79</v>
       </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
@@ -10298,16 +10296,16 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="R88" t="n">
-        <v>25.2</v>
+        <v>24.4</v>
       </c>
       <c r="S88" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="T88" t="n">
-        <v>2.08</v>
+        <v>2.63</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
@@ -10315,21 +10313,21 @@
         </is>
       </c>
       <c r="V88" t="n">
-        <v>12.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W88" t="n">
-        <v>3.03</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -10338,7 +10336,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -10348,7 +10346,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -10357,49 +10355,51 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>-14.6</v>
+        <v>7.3</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.5</v>
+        <v>12.1</v>
       </c>
       <c r="K89" t="n">
-        <v>12.4</v>
+        <v>13.6</v>
       </c>
       <c r="L89" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="M89" t="n">
-        <v>21.3</v>
+        <v>35.3</v>
       </c>
       <c r="N89" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+        <v>1.09</v>
+      </c>
+      <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="R89" t="n">
-        <v>115.6</v>
-      </c>
-      <c r="S89" t="inlineStr"/>
-      <c r="T89" t="inlineStr"/>
+        <v>25.2</v>
+      </c>
+      <c r="S89" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="T89" t="n">
+        <v>2.08</v>
+      </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr"/>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="V89" t="n">
+        <v>12.1</v>
+      </c>
       <c r="W89" t="n">
-        <v>0.65</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="90">
@@ -10954,12 +10954,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>6776</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -10973,12 +10973,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10987,22 +10987,22 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>-0.4</v>
+        <v>34.2</v>
       </c>
       <c r="J97" t="n">
-        <v>-6.2</v>
+        <v>39.1</v>
       </c>
       <c r="K97" t="n">
-        <v>12.1</v>
+        <v>12.9</v>
       </c>
       <c r="L97" t="n">
         <v>16.5</v>
       </c>
       <c r="M97" t="n">
-        <v>52.1</v>
+        <v>-33.5</v>
       </c>
       <c r="N97" t="n">
-        <v>-2.58</v>
+        <v>0.26</v>
       </c>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
@@ -11011,32 +11011,38 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="R97" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="S97" t="inlineStr"/>
-      <c r="T97" t="inlineStr"/>
+        <v>63.8</v>
+      </c>
+      <c r="S97" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="T97" t="n">
+        <v>1.63</v>
+      </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-6%)</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr"/>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="V97" t="n">
+        <v>39.1</v>
+      </c>
       <c r="W97" t="n">
-        <v>5.08</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5493</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>三聯</t>
+          <t>世豐</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -11064,22 +11070,22 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>-2.6</v>
+        <v>-32.9</v>
       </c>
       <c r="J98" t="n">
-        <v>-0.5</v>
+        <v>-45.3</v>
       </c>
       <c r="K98" t="n">
-        <v>13.1</v>
+        <v>4.4</v>
       </c>
       <c r="L98" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="M98" t="n">
         <v>18.6</v>
       </c>
       <c r="N98" t="n">
-        <v>1.03</v>
+        <v>1.53</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -11092,10 +11098,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="R98" t="n">
-        <v>22.3</v>
+        <v>27.6</v>
       </c>
       <c r="S98" t="inlineStr"/>
       <c r="T98" t="inlineStr"/>
@@ -11106,25 +11112,21 @@
       </c>
       <c r="V98" t="inlineStr"/>
       <c r="W98" t="n">
-        <v>2.94</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>信實</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>🌱初拐點</t>
-        </is>
-      </c>
+          <t>力成</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="n">
         <v>2</v>
       </c>
@@ -11135,7 +11137,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -11145,26 +11147,26 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>14.7</v>
+        <v>-10.3</v>
       </c>
       <c r="J99" t="n">
-        <v>14.7</v>
+        <v>-13.6</v>
       </c>
       <c r="K99" t="n">
-        <v>15.4</v>
+        <v>10.9</v>
       </c>
       <c r="L99" t="n">
         <v>14.5</v>
       </c>
       <c r="M99" t="n">
-        <v>9.199999999999999</v>
+        <v>30.2</v>
       </c>
       <c r="N99" t="n">
-        <v>0.87</v>
+        <v>2.01</v>
       </c>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
@@ -11173,27 +11175,21 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="R99" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="S99" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="T99" t="n">
-        <v>0.8</v>
-      </c>
+        <v>43.6</v>
+      </c>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
-        </is>
-      </c>
-      <c r="V99" t="n">
-        <v>14.7</v>
-      </c>
+          <t>⏸ 成長為負(-14%)</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr"/>
       <c r="W99" t="n">
-        <v>5.89</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="100">
@@ -11280,12 +11276,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>中碳</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -11313,22 +11309,22 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>-13.5</v>
+        <v>-10.9</v>
       </c>
       <c r="J101" t="n">
-        <v>-28.8</v>
+        <v>-13.6</v>
       </c>
       <c r="K101" t="n">
-        <v>7.2</v>
+        <v>12.8</v>
       </c>
       <c r="L101" t="n">
         <v>15.5</v>
       </c>
       <c r="M101" t="n">
-        <v>58.4</v>
+        <v>28.6</v>
       </c>
       <c r="N101" t="n">
-        <v>1.42</v>
+        <v>3.26</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -11341,10 +11337,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="R101" t="n">
-        <v>36.1</v>
+        <v>62.1</v>
       </c>
       <c r="S101" t="inlineStr"/>
       <c r="T101" t="inlineStr"/>
@@ -11355,18 +11351,18 @@
       </c>
       <c r="V101" t="inlineStr"/>
       <c r="W101" t="n">
-        <v>2.07</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>中碳</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -11394,22 +11390,22 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>-10.9</v>
+        <v>-13.5</v>
       </c>
       <c r="J102" t="n">
-        <v>-13.6</v>
+        <v>-28.8</v>
       </c>
       <c r="K102" t="n">
-        <v>12.8</v>
+        <v>7.2</v>
       </c>
       <c r="L102" t="n">
         <v>15.5</v>
       </c>
       <c r="M102" t="n">
-        <v>28.6</v>
+        <v>58.4</v>
       </c>
       <c r="N102" t="n">
-        <v>3.26</v>
+        <v>1.42</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
@@ -11422,10 +11418,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="R102" t="n">
-        <v>62.1</v>
+        <v>36.1</v>
       </c>
       <c r="S102" t="inlineStr"/>
       <c r="T102" t="inlineStr"/>
@@ -11436,7 +11432,7 @@
       </c>
       <c r="V102" t="inlineStr"/>
       <c r="W102" t="n">
-        <v>0.98</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="103">
@@ -11523,15 +11519,19 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6721</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>力成</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
+          <t>信實</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>🌱初拐點</t>
+        </is>
+      </c>
       <c r="D104" t="n">
         <v>2</v>
       </c>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -11552,26 +11552,26 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>-10.3</v>
+        <v>14.7</v>
       </c>
       <c r="J104" t="n">
-        <v>-13.6</v>
+        <v>14.7</v>
       </c>
       <c r="K104" t="n">
-        <v>10.9</v>
+        <v>15.4</v>
       </c>
       <c r="L104" t="n">
         <v>14.5</v>
       </c>
       <c r="M104" t="n">
-        <v>30.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="N104" t="n">
-        <v>2.01</v>
+        <v>0.87</v>
       </c>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
@@ -11580,21 +11580,27 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="R104" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="S104" t="inlineStr"/>
-      <c r="T104" t="inlineStr"/>
+        <v>11.8</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0.8</v>
+      </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-14%)</t>
-        </is>
-      </c>
-      <c r="V104" t="inlineStr"/>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="V104" t="n">
+        <v>14.7</v>
+      </c>
       <c r="W104" t="n">
-        <v>1.23</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="105">
@@ -11762,12 +11768,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -11776,7 +11782,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -11791,26 +11797,26 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>-14.7</v>
+        <v>97</v>
       </c>
       <c r="J107" t="n">
-        <v>-16.6</v>
+        <v>69.2</v>
       </c>
       <c r="K107" t="n">
-        <v>13.1</v>
+        <v>29.3</v>
       </c>
       <c r="L107" t="n">
         <v>17.1</v>
       </c>
       <c r="M107" t="n">
-        <v>35.3</v>
+        <v>116</v>
       </c>
       <c r="N107" t="n">
-        <v>1.95</v>
+        <v>1.02</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
@@ -11823,10 +11829,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="R107" t="n">
-        <v>16.9</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="S107" t="inlineStr"/>
       <c r="T107" t="inlineStr"/>
@@ -11837,7 +11843,7 @@
       </c>
       <c r="V107" t="inlineStr"/>
       <c r="W107" t="n">
-        <v>5.04</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="108">
@@ -12171,55 +12177,59 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>帆宣</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr"/>
+          <t>卜蜂</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>🌱初拐點</t>
+        </is>
+      </c>
       <c r="D112" t="n">
         <v>2</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>17</v>
+        <v>19.7</v>
       </c>
       <c r="J112" t="n">
-        <v>10.8</v>
+        <v>23.3</v>
       </c>
       <c r="K112" t="n">
-        <v>19.2</v>
+        <v>24.9</v>
       </c>
       <c r="L112" t="n">
         <v>19.8</v>
       </c>
       <c r="M112" t="n">
-        <v>64.90000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="N112" t="n">
-        <v>1.94</v>
+        <v>1.24</v>
       </c>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
@@ -12228,27 +12238,27 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="R112" t="n">
-        <v>34.7</v>
+        <v>12.4</v>
       </c>
       <c r="S112" t="n">
-        <v>31.3</v>
+        <v>10.1</v>
       </c>
       <c r="T112" t="n">
-        <v>3.22</v>
+        <v>0.53</v>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="V112" t="n">
-        <v>10.8</v>
+        <v>23.3</v>
       </c>
       <c r="W112" t="n">
-        <v>1.15</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="113">
@@ -12582,15 +12592,19 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>矽創</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr"/>
+          <t>大統益</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>🌱初拐點</t>
+        </is>
+      </c>
       <c r="D117" t="n">
         <v>2</v>
       </c>
@@ -12601,12 +12615,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -12615,49 +12629,51 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>-26.4</v>
+        <v>1.5</v>
       </c>
       <c r="J117" t="n">
-        <v>-21.3</v>
+        <v>2.5</v>
       </c>
       <c r="K117" t="n">
-        <v>15.4</v>
+        <v>22.2</v>
       </c>
       <c r="L117" t="n">
-        <v>24.7</v>
+        <v>24.5</v>
       </c>
       <c r="M117" t="n">
-        <v>39.8</v>
+        <v>9.9</v>
       </c>
       <c r="N117" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+        <v>1.39</v>
+      </c>
+      <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="R117" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="S117" t="inlineStr"/>
-      <c r="T117" t="inlineStr"/>
+        <v>16.4</v>
+      </c>
+      <c r="S117" t="n">
+        <v>16</v>
+      </c>
+      <c r="T117" t="n">
+        <v>6.56</v>
+      </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="V117" t="inlineStr"/>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="V117" t="n">
+        <v>2.5</v>
+      </c>
       <c r="W117" t="n">
-        <v>3.65</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="118">
@@ -12829,19 +12845,15 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>大統益</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>🌱初拐點</t>
-        </is>
-      </c>
+          <t>矽創</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="n">
         <v>2</v>
       </c>
@@ -12852,12 +12864,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -12866,51 +12878,49 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.5</v>
+        <v>-26.4</v>
       </c>
       <c r="J120" t="n">
-        <v>2.5</v>
+        <v>-21.3</v>
       </c>
       <c r="K120" t="n">
-        <v>22.2</v>
+        <v>15.4</v>
       </c>
       <c r="L120" t="n">
-        <v>24.5</v>
+        <v>24.7</v>
       </c>
       <c r="M120" t="n">
-        <v>9.9</v>
+        <v>39.8</v>
       </c>
       <c r="N120" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="O120" t="inlineStr"/>
+        <v>1.55</v>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="R120" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="S120" t="n">
-        <v>16</v>
-      </c>
-      <c r="T120" t="n">
-        <v>6.56</v>
-      </c>
+        <v>19.9</v>
+      </c>
+      <c r="S120" t="inlineStr"/>
+      <c r="T120" t="inlineStr"/>
       <c r="U120" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
-        </is>
-      </c>
-      <c r="V120" t="n">
-        <v>2.5</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr"/>
       <c r="W120" t="n">
-        <v>5.07</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="121">
@@ -13003,59 +13013,55 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>卜蜂</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>🌱初拐點</t>
-        </is>
-      </c>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
       <c r="D122" t="n">
         <v>2</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>19.7</v>
+        <v>17</v>
       </c>
       <c r="J122" t="n">
-        <v>23.3</v>
+        <v>10.8</v>
       </c>
       <c r="K122" t="n">
-        <v>24.9</v>
+        <v>19.2</v>
       </c>
       <c r="L122" t="n">
         <v>19.8</v>
       </c>
       <c r="M122" t="n">
-        <v>1.7</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="N122" t="n">
-        <v>1.24</v>
+        <v>1.94</v>
       </c>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
@@ -13064,27 +13070,27 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="R122" t="n">
-        <v>12.4</v>
+        <v>34.7</v>
       </c>
       <c r="S122" t="n">
-        <v>10.1</v>
+        <v>31.3</v>
       </c>
       <c r="T122" t="n">
-        <v>0.53</v>
+        <v>3.22</v>
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
       <c r="V122" t="n">
-        <v>23.3</v>
+        <v>10.8</v>
       </c>
       <c r="W122" t="n">
-        <v>6.09</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="123">
@@ -13424,12 +13430,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -13457,60 +13463,56 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>34.2</v>
+        <v>3.5</v>
       </c>
       <c r="J127" t="n">
-        <v>13.4</v>
+        <v>-4</v>
       </c>
       <c r="K127" t="n">
-        <v>27.1</v>
+        <v>22.4</v>
       </c>
       <c r="L127" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="M127" t="n">
-        <v>119.8</v>
+        <v>32.1</v>
       </c>
       <c r="N127" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="O127" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+        <v>0.77</v>
+      </c>
+      <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="R127" t="n">
-        <v>192</v>
+        <v>38.6</v>
       </c>
       <c r="S127" t="inlineStr"/>
       <c r="T127" t="inlineStr"/>
       <c r="U127" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 成長為負(-4%)</t>
         </is>
       </c>
       <c r="V127" t="inlineStr"/>
       <c r="W127" t="n">
-        <v>0.53</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -13538,45 +13540,49 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.5</v>
+        <v>34.2</v>
       </c>
       <c r="J128" t="n">
-        <v>-4</v>
+        <v>13.4</v>
       </c>
       <c r="K128" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="L128" t="n">
         <v>22.4</v>
       </c>
-      <c r="L128" t="n">
-        <v>21.7</v>
-      </c>
       <c r="M128" t="n">
-        <v>32.1</v>
+        <v>119.8</v>
       </c>
       <c r="N128" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="O128" t="inlineStr"/>
+        <v>0.63</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="R128" t="n">
-        <v>38.6</v>
+        <v>192</v>
       </c>
       <c r="S128" t="inlineStr"/>
       <c r="T128" t="inlineStr"/>
       <c r="U128" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-4%)</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
       <c r="V128" t="inlineStr"/>
       <c r="W128" t="n">
-        <v>2.24</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="129">
@@ -14668,12 +14674,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>7730</t>
+          <t>3016</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>嘉晶</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -14687,7 +14693,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -14697,43 +14703,53 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>-52.3</v>
+      </c>
+      <c r="J143" t="n">
+        <v>-69.09999999999999</v>
+      </c>
       <c r="K143" t="n">
-        <v>7.3</v>
+        <v>2.4</v>
       </c>
       <c r="L143" t="n">
         <v>6.1</v>
       </c>
-      <c r="M143" t="inlineStr"/>
+      <c r="M143" t="n">
+        <v>37.3</v>
+      </c>
       <c r="N143" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="O143" t="inlineStr"/>
+        <v>5.23</v>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="R143" t="n">
-        <v>93.3</v>
+        <v>339</v>
       </c>
       <c r="S143" t="inlineStr"/>
       <c r="T143" t="inlineStr"/>
       <c r="U143" t="inlineStr">
         <is>
-          <t>⏸ 無成長率</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
       <c r="V143" t="inlineStr"/>
       <c r="W143" t="n">
-        <v>0.8</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="144">
@@ -14820,12 +14836,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>7730</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>嘉晶</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -14839,7 +14855,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -14849,53 +14865,43 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="I145" t="n">
-        <v>-52.3</v>
-      </c>
-      <c r="J145" t="n">
-        <v>-69.09999999999999</v>
-      </c>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
       <c r="K145" t="n">
-        <v>2.4</v>
+        <v>7.3</v>
       </c>
       <c r="L145" t="n">
         <v>6.1</v>
       </c>
-      <c r="M145" t="n">
-        <v>37.3</v>
-      </c>
+      <c r="M145" t="inlineStr"/>
       <c r="N145" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="O145" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+        <v>0.51</v>
+      </c>
+      <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="R145" t="n">
-        <v>339</v>
+        <v>93.3</v>
       </c>
       <c r="S145" t="inlineStr"/>
       <c r="T145" t="inlineStr"/>
       <c r="U145" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 無成長率</t>
         </is>
       </c>
       <c r="V145" t="inlineStr"/>
       <c r="W145" t="n">
-        <v>0.36</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="146">
@@ -15227,12 +15233,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>系統電</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -15260,22 +15266,22 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>-8.6</v>
+        <v>-18.4</v>
       </c>
       <c r="J150" t="n">
-        <v>-1.6</v>
+        <v>-49.9</v>
       </c>
       <c r="K150" t="n">
-        <v>6.4</v>
+        <v>-0.1</v>
       </c>
       <c r="L150" t="n">
-        <v>9.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="M150" t="n">
-        <v>12</v>
+        <v>15.3</v>
       </c>
       <c r="N150" t="n">
-        <v>2.28</v>
+        <v>-15.71</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
@@ -15288,10 +15294,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="R150" t="n">
-        <v>19.8</v>
+        <v>275</v>
       </c>
       <c r="S150" t="inlineStr"/>
       <c r="T150" t="inlineStr"/>
@@ -15302,18 +15308,18 @@
       </c>
       <c r="V150" t="inlineStr"/>
       <c r="W150" t="n">
-        <v>4.66</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>晟銘電</t>
+          <t>漢翔</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -15327,7 +15333,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -15337,24 +15343,26 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>7.2</v>
+      </c>
       <c r="J151" t="n">
-        <v>65.59999999999999</v>
+        <v>-23.3</v>
       </c>
       <c r="K151" t="n">
-        <v>17</v>
+        <v>4.2</v>
       </c>
       <c r="L151" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M151" t="n">
-        <v>1.7</v>
+        <v>18.9</v>
       </c>
       <c r="N151" t="n">
-        <v>0.68</v>
+        <v>3.15</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
@@ -15367,10 +15375,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="R151" t="n">
-        <v>20.2</v>
+        <v>61.9</v>
       </c>
       <c r="S151" t="inlineStr"/>
       <c r="T151" t="inlineStr"/>
@@ -15381,7 +15389,7 @@
       </c>
       <c r="V151" t="inlineStr"/>
       <c r="W151" t="n">
-        <v>0.7</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="152">
@@ -15462,15 +15470,19 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>9933</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr"/>
+          <t>家登</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>🌱初拐點</t>
+        </is>
+      </c>
       <c r="D153" t="n">
         <v>2</v>
       </c>
@@ -15481,7 +15493,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -15491,26 +15503,26 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>-4.5</v>
+        <v>23.6</v>
       </c>
       <c r="J153" t="n">
-        <v>-16.5</v>
+        <v>-5.3</v>
       </c>
       <c r="K153" t="n">
-        <v>18.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L153" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="M153" t="n">
-        <v>-2.6</v>
+        <v>16</v>
       </c>
       <c r="N153" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
@@ -15523,10 +15535,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="R153" t="n">
-        <v>10.2</v>
+        <v>51.6</v>
       </c>
       <c r="S153" t="inlineStr"/>
       <c r="T153" t="inlineStr"/>
@@ -15537,7 +15549,7 @@
       </c>
       <c r="V153" t="inlineStr"/>
       <c r="W153" t="n">
-        <v>2.29</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="154">
@@ -15875,12 +15887,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -15889,7 +15901,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -15904,26 +15916,26 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>97</v>
+        <v>-14.7</v>
       </c>
       <c r="J158" t="n">
-        <v>69.2</v>
+        <v>-16.6</v>
       </c>
       <c r="K158" t="n">
-        <v>29.3</v>
+        <v>13.1</v>
       </c>
       <c r="L158" t="n">
         <v>17.1</v>
       </c>
       <c r="M158" t="n">
-        <v>116</v>
+        <v>35.3</v>
       </c>
       <c r="N158" t="n">
-        <v>1.02</v>
+        <v>1.95</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
@@ -15936,10 +15948,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="R158" t="n">
-        <v>77.09999999999999</v>
+        <v>16.9</v>
       </c>
       <c r="S158" t="inlineStr"/>
       <c r="T158" t="inlineStr"/>
@@ -15950,7 +15962,7 @@
       </c>
       <c r="V158" t="inlineStr"/>
       <c r="W158" t="n">
-        <v>0.57</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="159">
@@ -16039,12 +16051,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>5493</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>世豐</t>
+          <t>三聯</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -16072,22 +16084,22 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>-32.9</v>
+        <v>-2.6</v>
       </c>
       <c r="J160" t="n">
-        <v>-45.3</v>
+        <v>-0.5</v>
       </c>
       <c r="K160" t="n">
-        <v>4.4</v>
+        <v>13.1</v>
       </c>
       <c r="L160" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="M160" t="n">
         <v>18.6</v>
       </c>
       <c r="N160" t="n">
-        <v>1.53</v>
+        <v>1.03</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
@@ -16100,10 +16112,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="R160" t="n">
-        <v>27.6</v>
+        <v>22.3</v>
       </c>
       <c r="S160" t="inlineStr"/>
       <c r="T160" t="inlineStr"/>
@@ -16114,7 +16126,7 @@
       </c>
       <c r="V160" t="inlineStr"/>
       <c r="W160" t="n">
-        <v>4.45</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="161">
@@ -16699,12 +16711,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6776</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -16718,12 +16730,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -16732,22 +16744,22 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>34.2</v>
+        <v>-0.4</v>
       </c>
       <c r="J168" t="n">
-        <v>39.1</v>
+        <v>-6.2</v>
       </c>
       <c r="K168" t="n">
-        <v>12.9</v>
+        <v>12.1</v>
       </c>
       <c r="L168" t="n">
         <v>16.5</v>
       </c>
       <c r="M168" t="n">
-        <v>-33.5</v>
+        <v>52.1</v>
       </c>
       <c r="N168" t="n">
-        <v>0.26</v>
+        <v>-2.58</v>
       </c>
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
@@ -16756,27 +16768,21 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="R168" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="S168" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="T168" t="n">
-        <v>1.63</v>
-      </c>
+        <v>13.7</v>
+      </c>
+      <c r="S168" t="inlineStr"/>
+      <c r="T168" t="inlineStr"/>
       <c r="U168" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
-        </is>
-      </c>
-      <c r="V168" t="n">
-        <v>39.1</v>
-      </c>
+          <t>⏸ 成長為負(-6%)</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr"/>
       <c r="W168" t="n">
-        <v>0.78</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="169">
@@ -16944,25 +16950,21 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>欣高</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>🌱初拐點</t>
-        </is>
-      </c>
+          <t>和碩</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
       <c r="D171" t="n">
         <v>2</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -16972,7 +16974,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -16981,22 +16983,22 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>3.4</v>
+        <v>-8.6</v>
       </c>
       <c r="J171" t="n">
-        <v>15.7</v>
+        <v>-1.6</v>
       </c>
       <c r="K171" t="n">
-        <v>8.300000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="L171" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M171" t="n">
-        <v>13.2</v>
+        <v>12</v>
       </c>
       <c r="N171" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="O171" t="inlineStr">
         <is>
@@ -17009,10 +17011,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="R171" t="n">
-        <v>14.8</v>
+        <v>19.8</v>
       </c>
       <c r="S171" t="inlineStr"/>
       <c r="T171" t="inlineStr"/>
@@ -17023,27 +17025,31 @@
       </c>
       <c r="V171" t="inlineStr"/>
       <c r="W171" t="n">
-        <v>5.13</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>9931</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>漢翔</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr"/>
+          <t>欣高</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>🌱初拐點</t>
+        </is>
+      </c>
       <c r="D172" t="n">
         <v>2</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -17053,7 +17059,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -17062,22 +17068,22 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>7.2</v>
+        <v>3.4</v>
       </c>
       <c r="J172" t="n">
-        <v>-23.3</v>
+        <v>15.7</v>
       </c>
       <c r="K172" t="n">
-        <v>4.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L172" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="M172" t="n">
-        <v>18.9</v>
+        <v>13.2</v>
       </c>
       <c r="N172" t="n">
-        <v>3.15</v>
+        <v>2.04</v>
       </c>
       <c r="O172" t="inlineStr">
         <is>
@@ -17090,10 +17096,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="R172" t="n">
-        <v>61.9</v>
+        <v>14.8</v>
       </c>
       <c r="S172" t="inlineStr"/>
       <c r="T172" t="inlineStr"/>
@@ -17104,18 +17110,18 @@
       </c>
       <c r="V172" t="inlineStr"/>
       <c r="W172" t="n">
-        <v>1.56</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2947</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>振宇五金</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -17143,22 +17149,22 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>-23.3</v>
+        <v>-14.9</v>
       </c>
       <c r="J173" t="n">
-        <v>-9</v>
+        <v>-1.8</v>
       </c>
       <c r="K173" t="n">
-        <v>6.6</v>
+        <v>7.9</v>
       </c>
       <c r="L173" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="M173" t="n">
-        <v>36.5</v>
+        <v>10.9</v>
       </c>
       <c r="N173" t="n">
-        <v>-2.99</v>
+        <v>4.84</v>
       </c>
       <c r="O173" t="inlineStr">
         <is>
@@ -17171,10 +17177,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="R173" t="n">
-        <v>25.8</v>
+        <v>26.6</v>
       </c>
       <c r="S173" t="inlineStr"/>
       <c r="T173" t="inlineStr"/>
@@ -17185,18 +17191,18 @@
       </c>
       <c r="V173" t="inlineStr"/>
       <c r="W173" t="n">
-        <v>3.82</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -17210,12 +17216,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -17224,62 +17230,60 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2</v>
+        <v>-23.3</v>
       </c>
       <c r="J174" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
       <c r="K174" t="n">
-        <v>9.9</v>
+        <v>6.6</v>
       </c>
       <c r="L174" t="n">
-        <v>9.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M174" t="n">
-        <v>5.4</v>
+        <v>36.5</v>
       </c>
       <c r="N174" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="O174" t="inlineStr"/>
+        <v>-2.99</v>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="R174" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="S174" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="T174" t="n">
-        <v>14.25</v>
-      </c>
+        <v>25.8</v>
+      </c>
+      <c r="S174" t="inlineStr"/>
+      <c r="T174" t="inlineStr"/>
       <c r="U174" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
-        </is>
-      </c>
-      <c r="V174" t="n">
-        <v>2</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr"/>
       <c r="W174" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>振宇五金</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -17293,12 +17297,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -17307,49 +17311,51 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>-14.9</v>
+        <v>2</v>
       </c>
       <c r="J175" t="n">
-        <v>-1.8</v>
+        <v>2</v>
       </c>
       <c r="K175" t="n">
-        <v>7.9</v>
+        <v>9.9</v>
       </c>
       <c r="L175" t="n">
-        <v>9.5</v>
+        <v>9.9</v>
       </c>
       <c r="M175" t="n">
-        <v>10.9</v>
+        <v>5.4</v>
       </c>
       <c r="N175" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="O175" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+        <v>1.85</v>
+      </c>
+      <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="R175" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="S175" t="inlineStr"/>
-      <c r="T175" t="inlineStr"/>
+        <v>28.7</v>
+      </c>
+      <c r="S175" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="T175" t="n">
+        <v>14.25</v>
+      </c>
       <c r="U175" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="V175" t="inlineStr"/>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="V175" t="n">
+        <v>2</v>
+      </c>
       <c r="W175" t="n">
-        <v>3.92</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="176">
@@ -17758,12 +17764,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>系統電</t>
+          <t>晟銘電</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -17777,7 +17783,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -17787,26 +17793,24 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="I181" t="n">
-        <v>-18.4</v>
-      </c>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
       <c r="J181" t="n">
-        <v>-49.9</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="K181" t="n">
-        <v>-0.1</v>
+        <v>17</v>
       </c>
       <c r="L181" t="n">
         <v>8.6</v>
       </c>
       <c r="M181" t="n">
-        <v>15.3</v>
+        <v>1.7</v>
       </c>
       <c r="N181" t="n">
-        <v>-15.71</v>
+        <v>0.68</v>
       </c>
       <c r="O181" t="inlineStr">
         <is>
@@ -17819,10 +17823,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="R181" t="n">
-        <v>275</v>
+        <v>20.2</v>
       </c>
       <c r="S181" t="inlineStr"/>
       <c r="T181" t="inlineStr"/>
@@ -17833,18 +17837,18 @@
       </c>
       <c r="V181" t="inlineStr"/>
       <c r="W181" t="n">
-        <v>0.76</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>台星科</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -17858,12 +17862,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -17872,56 +17876,60 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>17.3</v>
+        <v>0</v>
       </c>
       <c r="J182" t="n">
-        <v>-6.6</v>
+        <v>44.7</v>
       </c>
       <c r="K182" t="n">
-        <v>12.9</v>
+        <v>14.4</v>
       </c>
       <c r="L182" t="n">
-        <v>12.8</v>
+        <v>12.3</v>
       </c>
       <c r="M182" t="n">
-        <v>22.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="N182" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O182" t="inlineStr"/>
+        <v>-0.64</v>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="R182" t="n">
-        <v>34</v>
+        <v>14.1</v>
       </c>
       <c r="S182" t="inlineStr"/>
       <c r="T182" t="inlineStr"/>
       <c r="U182" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-7%)</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
       <c r="V182" t="inlineStr"/>
       <c r="W182" t="n">
-        <v>2.12</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>台星科</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -17935,12 +17943,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -17949,67 +17957,59 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0</v>
+        <v>17.3</v>
       </c>
       <c r="J183" t="n">
-        <v>44.7</v>
+        <v>-6.6</v>
       </c>
       <c r="K183" t="n">
-        <v>14.4</v>
+        <v>12.9</v>
       </c>
       <c r="L183" t="n">
-        <v>12.3</v>
+        <v>12.8</v>
       </c>
       <c r="M183" t="n">
-        <v>9.300000000000001</v>
+        <v>22.1</v>
       </c>
       <c r="N183" t="n">
-        <v>-0.64</v>
-      </c>
-      <c r="O183" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+        <v>1.67</v>
+      </c>
+      <c r="O183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="R183" t="n">
-        <v>14.1</v>
+        <v>34</v>
       </c>
       <c r="S183" t="inlineStr"/>
       <c r="T183" t="inlineStr"/>
       <c r="U183" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 成長為負(-7%)</t>
         </is>
       </c>
       <c r="V183" t="inlineStr"/>
       <c r="W183" t="n">
-        <v>5.33</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>家登</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>🌱初拐點</t>
-        </is>
-      </c>
+          <t>台半</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
       <c r="D184" t="n">
         <v>2</v>
       </c>
@@ -18034,22 +18034,22 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>23.6</v>
+        <v>-12.5</v>
       </c>
       <c r="J184" t="n">
-        <v>-5.3</v>
+        <v>-30.8</v>
       </c>
       <c r="K184" t="n">
-        <v>8.199999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="L184" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="M184" t="n">
-        <v>16</v>
+        <v>11.8</v>
       </c>
       <c r="N184" t="n">
-        <v>1.4</v>
+        <v>2.14</v>
       </c>
       <c r="O184" t="inlineStr">
         <is>
@@ -18062,10 +18062,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="R184" t="n">
-        <v>51.6</v>
+        <v>58</v>
       </c>
       <c r="S184" t="inlineStr"/>
       <c r="T184" t="inlineStr"/>
@@ -18076,18 +18076,18 @@
       </c>
       <c r="V184" t="inlineStr"/>
       <c r="W184" t="n">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>9933</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>台半</t>
+          <t>中鼎</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -18101,7 +18101,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -18111,26 +18111,26 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I185" t="n">
-        <v>-12.5</v>
+        <v>-4.5</v>
       </c>
       <c r="J185" t="n">
-        <v>-30.8</v>
+        <v>-16.5</v>
       </c>
       <c r="K185" t="n">
-        <v>10.4</v>
+        <v>18.9</v>
       </c>
       <c r="L185" t="n">
-        <v>13.5</v>
+        <v>12.6</v>
       </c>
       <c r="M185" t="n">
-        <v>11.8</v>
+        <v>-2.6</v>
       </c>
       <c r="N185" t="n">
-        <v>2.14</v>
+        <v>3.9</v>
       </c>
       <c r="O185" t="inlineStr">
         <is>
@@ -18143,10 +18143,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="R185" t="n">
-        <v>58</v>
+        <v>10.2</v>
       </c>
       <c r="S185" t="inlineStr"/>
       <c r="T185" t="inlineStr"/>
@@ -18157,7 +18157,7 @@
       </c>
       <c r="V185" t="inlineStr"/>
       <c r="W185" t="n">
-        <v>1.51</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="186">
@@ -18331,12 +18331,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -18345,7 +18345,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -18355,7 +18355,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -18364,22 +18364,22 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>-19.8</v>
+        <v>18.4</v>
       </c>
       <c r="J188" t="n">
-        <v>-23.7</v>
+        <v>56</v>
       </c>
       <c r="K188" t="n">
-        <v>5.4</v>
+        <v>10.7</v>
       </c>
       <c r="L188" t="n">
-        <v>10.9</v>
+        <v>11.4</v>
       </c>
       <c r="M188" t="n">
-        <v>19.1</v>
+        <v>49.9</v>
       </c>
       <c r="N188" t="n">
-        <v>1.05</v>
+        <v>1.73</v>
       </c>
       <c r="O188" t="inlineStr">
         <is>
@@ -18392,10 +18392,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="R188" t="n">
-        <v>75.40000000000001</v>
+        <v>165.8</v>
       </c>
       <c r="S188" t="inlineStr"/>
       <c r="T188" t="inlineStr"/>
@@ -18406,18 +18406,18 @@
       </c>
       <c r="V188" t="inlineStr"/>
       <c r="W188" t="n">
-        <v>1.09</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -18426,7 +18426,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -18436,7 +18436,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -18445,22 +18445,22 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>18.4</v>
+        <v>-19.8</v>
       </c>
       <c r="J189" t="n">
-        <v>56</v>
+        <v>-23.7</v>
       </c>
       <c r="K189" t="n">
-        <v>10.7</v>
+        <v>5.4</v>
       </c>
       <c r="L189" t="n">
-        <v>11.4</v>
+        <v>10.9</v>
       </c>
       <c r="M189" t="n">
-        <v>49.9</v>
+        <v>19.1</v>
       </c>
       <c r="N189" t="n">
-        <v>1.73</v>
+        <v>1.05</v>
       </c>
       <c r="O189" t="inlineStr">
         <is>
@@ -18473,10 +18473,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R189" t="n">
-        <v>165.8</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="S189" t="inlineStr"/>
       <c r="T189" t="inlineStr"/>
@@ -18487,7 +18487,7 @@
       </c>
       <c r="V189" t="inlineStr"/>
       <c r="W189" t="n">
-        <v>0.18</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="190">
@@ -20733,12 +20733,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>三福化</t>
+          <t>定穎投控</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -20747,12 +20747,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -20766,22 +20766,20 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>-13.8</v>
-      </c>
-      <c r="J218" t="n">
-        <v>-24</v>
-      </c>
+        <v>-13.4</v>
+      </c>
+      <c r="J218" t="inlineStr"/>
       <c r="K218" t="n">
-        <v>5.9</v>
+        <v>2</v>
       </c>
       <c r="L218" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="M218" t="n">
-        <v>-5.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="N218" t="n">
-        <v>2.91</v>
+        <v>-1.6</v>
       </c>
       <c r="O218" t="inlineStr">
         <is>
@@ -20794,10 +20792,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="R218" t="n">
-        <v>38.4</v>
+        <v>194.5</v>
       </c>
       <c r="S218" t="inlineStr"/>
       <c r="T218" t="inlineStr"/>
@@ -20808,18 +20806,18 @@
       </c>
       <c r="V218" t="inlineStr"/>
       <c r="W218" t="n">
-        <v>2.67</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>凌群</t>
+          <t>三福化</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -20828,7 +20826,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -20843,55 +20841,53 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="I219" t="n">
-        <v>9.699999999999999</v>
+        <v>-13.8</v>
       </c>
       <c r="J219" t="n">
-        <v>7.6</v>
+        <v>-24</v>
       </c>
       <c r="K219" t="n">
-        <v>15.2</v>
+        <v>5.9</v>
       </c>
       <c r="L219" t="n">
-        <v>13.1</v>
+        <v>12.2</v>
       </c>
       <c r="M219" t="n">
-        <v>6.8</v>
+        <v>-5.8</v>
       </c>
       <c r="N219" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O219" t="inlineStr"/>
+        <v>2.91</v>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="R219" t="n">
-        <v>18</v>
-      </c>
-      <c r="S219" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="T219" t="n">
-        <v>2.36</v>
-      </c>
+        <v>38.4</v>
+      </c>
+      <c r="S219" t="inlineStr"/>
+      <c r="T219" t="inlineStr"/>
       <c r="U219" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
-        </is>
-      </c>
-      <c r="V219" t="n">
-        <v>7.6</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr"/>
       <c r="W219" t="n">
-        <v>3.61</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="220">
@@ -20978,12 +20974,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -20997,7 +20993,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -21007,53 +21003,53 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I221" t="n">
-        <v>-43.2</v>
-      </c>
-      <c r="J221" t="n">
-        <v>-39.2</v>
-      </c>
+        <v>17.7</v>
+      </c>
+      <c r="J221" t="inlineStr"/>
       <c r="K221" t="n">
-        <v>7.6</v>
+        <v>13.8</v>
       </c>
       <c r="L221" t="n">
-        <v>11.7</v>
+        <v>12.9</v>
       </c>
       <c r="M221" t="n">
-        <v>31.6</v>
+        <v>-5.3</v>
       </c>
       <c r="N221" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="O221" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+        <v>0.58</v>
+      </c>
+      <c r="O221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="R221" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="S221" t="inlineStr"/>
-      <c r="T221" t="inlineStr"/>
+        <v>27.2</v>
+      </c>
+      <c r="S221" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="T221" t="n">
+        <v>1.54</v>
+      </c>
       <c r="U221" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="V221" t="inlineStr"/>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="V221" t="n">
+        <v>17.7</v>
+      </c>
       <c r="W221" t="n">
-        <v>0.4</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="222">
@@ -21142,12 +21138,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>3715</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>定穎投控</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -21175,20 +21171,22 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>-13.4</v>
-      </c>
-      <c r="J223" t="inlineStr"/>
+        <v>-43.2</v>
+      </c>
+      <c r="J223" t="n">
+        <v>-39.2</v>
+      </c>
       <c r="K223" t="n">
-        <v>2</v>
+        <v>7.6</v>
       </c>
       <c r="L223" t="n">
-        <v>12.1</v>
+        <v>11.7</v>
       </c>
       <c r="M223" t="n">
-        <v>69.09999999999999</v>
+        <v>31.6</v>
       </c>
       <c r="N223" t="n">
-        <v>-1.6</v>
+        <v>0.36</v>
       </c>
       <c r="O223" t="inlineStr">
         <is>
@@ -21201,10 +21199,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="R223" t="n">
-        <v>194.5</v>
+        <v>86.5</v>
       </c>
       <c r="S223" t="inlineStr"/>
       <c r="T223" t="inlineStr"/>
@@ -21215,7 +21213,7 @@
       </c>
       <c r="V223" t="inlineStr"/>
       <c r="W223" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="224">
@@ -21302,12 +21300,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>2453</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>凌群</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -21335,20 +21333,22 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="J225" t="inlineStr"/>
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J225" t="n">
+        <v>7.6</v>
+      </c>
       <c r="K225" t="n">
-        <v>13.8</v>
+        <v>15.2</v>
       </c>
       <c r="L225" t="n">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
       <c r="M225" t="n">
-        <v>-5.3</v>
+        <v>6.8</v>
       </c>
       <c r="N225" t="n">
-        <v>0.58</v>
+        <v>0.9</v>
       </c>
       <c r="O225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
@@ -21357,27 +21357,27 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="R225" t="n">
-        <v>27.2</v>
+        <v>18</v>
       </c>
       <c r="S225" t="n">
-        <v>23.1</v>
+        <v>16.7</v>
       </c>
       <c r="T225" t="n">
-        <v>1.54</v>
+        <v>2.36</v>
       </c>
       <c r="U225" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="V225" t="n">
-        <v>17.7</v>
+        <v>7.6</v>
       </c>
       <c r="W225" t="n">
-        <v>3.29</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="226">
@@ -24459,20 +24459,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>8.1</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>12.1</v>
+        <v>20.6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -24495,29 +24495,29 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>20.2</v>
+        <v>16.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.27</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>10.6</v>
       </c>
       <c r="E13" t="n">
-        <v>20.6</v>
+        <v>38.1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -24540,10 +24540,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>16.8</v>
+        <v>17.3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.43</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="14">
@@ -24594,20 +24594,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>-7.1</v>
+        <v>-9.1</v>
       </c>
       <c r="E15" t="n">
-        <v>21.1</v>
+        <v>39.9</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -24630,29 +24630,29 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>-9.5</v>
+        <v>8.1</v>
       </c>
       <c r="E16" t="n">
-        <v>33.2</v>
+        <v>12.1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -24675,29 +24675,29 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>16.6</v>
+        <v>20.2</v>
       </c>
       <c r="M16" t="n">
-        <v>3.08</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>10.6</v>
+        <v>-9.5</v>
       </c>
       <c r="E17" t="n">
-        <v>38.1</v>
+        <v>33.2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -24720,29 +24720,29 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>17.3</v>
+        <v>16.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.55</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>-9.1</v>
+        <v>-7.1</v>
       </c>
       <c r="E18" t="n">
-        <v>39.9</v>
+        <v>21.1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -24765,10 +24765,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="M18" t="n">
-        <v>3.03</v>
+        <v>3.25</v>
       </c>
     </row>
   </sheetData>
